--- a/simulations/lab2/measured/Lab2-數據記錄.xlsx
+++ b/simulations/lab2/measured/Lab2-數據記錄.xlsx
@@ -233,7 +233,7 @@
           <idx val="0"/>
           <order val="0"/>
           <tx>
-            <v>實測 V_BB = 1.5 V</v>
+            <v>實測 1.5 V</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -271,7 +271,7 @@
           <idx val="1"/>
           <order val="1"/>
           <tx>
-            <v>實測 V_BB = 2.0 V</v>
+            <v>實測 2.0 V</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -296,12 +296,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'實驗一 特性曲線'!$F$13:$F$43</f>
+              <f>'實驗一 特性曲線'!$G$13:$G$43</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'實驗一 特性曲線'!$H$13:$H$43</f>
+              <f>'實驗一 特性曲線'!$I$13:$I$43</f>
             </numRef>
           </yVal>
         </ser>
@@ -309,7 +309,7 @@
           <idx val="2"/>
           <order val="2"/>
           <tx>
-            <v>實測 V_BB = 2.2 V</v>
+            <v>實測 2.2 V</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -334,12 +334,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'實驗一 特性曲線'!$J$13:$J$43</f>
+              <f>'實驗一 特性曲線'!$L$13:$L$43</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'實驗一 特性曲線'!$L$13:$L$43</f>
+              <f>'實驗一 特性曲線'!$N$13:$N$43</f>
             </numRef>
           </yVal>
         </ser>
@@ -347,7 +347,7 @@
           <idx val="3"/>
           <order val="3"/>
           <tx>
-            <v>實測 V_BB = 2.4 V</v>
+            <v>實測 2.4 V</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -372,12 +372,132 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'實驗一 特性曲線'!$N$13:$N$43</f>
+              <f>'實驗一 特性曲線'!$Q$13:$Q$43</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'實驗一 特性曲線'!$S$13:$S$43</f>
+            </numRef>
+          </yVal>
+        </ser>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <tx>
+            <v>LTspice 1.5 V</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'實驗一 特性曲線'!$E$13:$E$43</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'實驗一 特性曲線'!$F$13:$F$43</f>
+            </numRef>
+          </yVal>
+        </ser>
+        <ser>
+          <idx val="5"/>
+          <order val="5"/>
+          <tx>
+            <v>LTspice 2.0 V</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'實驗一 特性曲線'!$J$13:$J$43</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'實驗一 特性曲線'!$K$13:$K$43</f>
+            </numRef>
+          </yVal>
+        </ser>
+        <ser>
+          <idx val="6"/>
+          <order val="6"/>
+          <tx>
+            <v>LTspice 2.2 V</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'實驗一 特性曲線'!$O$13:$O$43</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
               <f>'實驗一 特性曲線'!$P$13:$P$43</f>
+            </numRef>
+          </yVal>
+        </ser>
+        <ser>
+          <idx val="7"/>
+          <order val="7"/>
+          <tx>
+            <v>LTspice 2.4 V</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'實驗一 特性曲線'!$T$13:$T$43</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'實驗一 特性曲線'!$U$13:$U$43</f>
             </numRef>
           </yVal>
         </ser>
@@ -446,16 +566,409 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>實驗二：四個電流的實測 vs LTspice 預報</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'實驗二 beta'!$A$11:$A$14</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'實驗二 beta'!$B$11:$B$14</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'實驗二 beta'!$A$11:$A$14</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'實驗二 beta'!$E$11:$E$14</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>電流 (mA)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>β：板子上算出來的 vs 電表 hFE 檔量到的</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'實驗二 beta'!$A$15:$A$16</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'實驗二 beta'!$B$15:$B$16</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>β</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>第二部分：四種組合的電壓增益（實測 vs LTspice）</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'第二部分 CE 放大器'!$A$14:$A$17</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'第二部分 CE 放大器'!$D$14:$D$17</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'第二部分 CE 放大器'!$A$14:$A$17</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'第二部分 CE 放大器'!$E$14:$E$17</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>|A_v|</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>18</col>
+      <col>22</col>
       <colOff>0</colOff>
       <row>10</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7200000" cy="3960000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6120000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>24</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6120000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>11</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6840000" cy="3240000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -983,7 +1496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q53"/>
+  <dimension ref="A1:U53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -991,18 +1504,22 @@
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
     <col width="15" customWidth="1" min="16" max="16"/>
-    <col width="15" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="15" customWidth="1" min="20" max="20"/>
+    <col width="15" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1114,30 +1631,34 @@
       <c r="C11" s="14" t="n"/>
       <c r="D11" s="14" t="n"/>
       <c r="E11" s="14" t="n"/>
-      <c r="F11" s="13" t="inlineStr">
+      <c r="F11" s="14" t="n"/>
+      <c r="G11" s="13" t="inlineStr">
         <is>
           <t>V_BB = 2.0 V</t>
         </is>
       </c>
-      <c r="G11" s="14" t="n"/>
       <c r="H11" s="14" t="n"/>
       <c r="I11" s="14" t="n"/>
-      <c r="J11" s="13" t="inlineStr">
+      <c r="J11" s="14" t="n"/>
+      <c r="K11" s="14" t="n"/>
+      <c r="L11" s="13" t="inlineStr">
         <is>
           <t>V_BB = 2.2 V</t>
         </is>
       </c>
-      <c r="K11" s="14" t="n"/>
-      <c r="L11" s="14" t="n"/>
       <c r="M11" s="14" t="n"/>
-      <c r="N11" s="13" t="inlineStr">
-        <is>
-          <t>V_BB = 2.4 V</t>
-        </is>
-      </c>
+      <c r="N11" s="14" t="n"/>
       <c r="O11" s="14" t="n"/>
       <c r="P11" s="14" t="n"/>
-      <c r="Q11" s="14" t="n"/>
+      <c r="Q11" s="13" t="inlineStr">
+        <is>
+          <t>V_BB = 2.4 V</t>
+        </is>
+      </c>
+      <c r="R11" s="14" t="n"/>
+      <c r="S11" s="14" t="n"/>
+      <c r="T11" s="14" t="n"/>
+      <c r="U11" s="14" t="n"/>
     </row>
     <row r="12" ht="34" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
@@ -1162,65 +1683,85 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
+          <t>LTspice V_CE (V)</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
           <t>LTspice I_C (mA)</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>實測 V_CE (V)</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>實測 V_RC (V)</t>
         </is>
       </c>
-      <c r="H12" s="5" t="inlineStr">
+      <c r="I12" s="5" t="inlineStr">
         <is>
           <t>I_C = V_RC/R_C (mA)</t>
         </is>
       </c>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>LTspice V_CE (V)</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
         <is>
           <t>LTspice I_C (mA)</t>
         </is>
       </c>
-      <c r="J12" s="5" t="inlineStr">
+      <c r="L12" s="5" t="inlineStr">
         <is>
           <t>實測 V_CE (V)</t>
         </is>
       </c>
-      <c r="K12" s="5" t="inlineStr">
+      <c r="M12" s="5" t="inlineStr">
         <is>
           <t>實測 V_RC (V)</t>
         </is>
       </c>
-      <c r="L12" s="5" t="inlineStr">
+      <c r="N12" s="5" t="inlineStr">
         <is>
           <t>I_C = V_RC/R_C (mA)</t>
         </is>
       </c>
-      <c r="M12" s="5" t="inlineStr">
+      <c r="O12" s="5" t="inlineStr">
+        <is>
+          <t>LTspice V_CE (V)</t>
+        </is>
+      </c>
+      <c r="P12" s="5" t="inlineStr">
         <is>
           <t>LTspice I_C (mA)</t>
         </is>
       </c>
-      <c r="N12" s="5" t="inlineStr">
+      <c r="Q12" s="5" t="inlineStr">
         <is>
           <t>實測 V_CE (V)</t>
         </is>
       </c>
-      <c r="O12" s="5" t="inlineStr">
+      <c r="R12" s="5" t="inlineStr">
         <is>
           <t>實測 V_RC (V)</t>
         </is>
       </c>
-      <c r="P12" s="5" t="inlineStr">
+      <c r="S12" s="5" t="inlineStr">
         <is>
           <t>I_C = V_RC/R_C (mA)</t>
         </is>
       </c>
-      <c r="Q12" s="5" t="inlineStr">
+      <c r="T12" s="5" t="inlineStr">
+        <is>
+          <t>LTspice V_CE (V)</t>
+        </is>
+      </c>
+      <c r="U12" s="5" t="inlineStr">
         <is>
           <t>LTspice I_C (mA)</t>
         </is>
@@ -1237,33 +1778,45 @@
         <v/>
       </c>
       <c r="E13" s="9" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="F13" s="9" t="n">
         <v>-0.0003</v>
       </c>
-      <c r="F13" s="7" t="n"/>
       <c r="G13" s="7" t="n"/>
-      <c r="H13" s="8">
-        <f>IF(G13="","",G13/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="I13" s="9" t="n">
+      <c r="H13" s="7" t="n"/>
+      <c r="I13" s="8">
+        <f>IF(H13="","",H13/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="J13" s="9" t="n">
+        <v>0.0054</v>
+      </c>
+      <c r="K13" s="9" t="n">
         <v>-0.0054</v>
       </c>
-      <c r="J13" s="7" t="n"/>
-      <c r="K13" s="7" t="n"/>
-      <c r="L13" s="8">
-        <f>IF(K13="","",K13/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="M13" s="9" t="n">
+      <c r="L13" s="7" t="n"/>
+      <c r="M13" s="7" t="n"/>
+      <c r="N13" s="8">
+        <f>IF(M13="","",M13/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="O13" s="9" t="n">
+        <v>0.0062</v>
+      </c>
+      <c r="P13" s="9" t="n">
         <v>-0.0062</v>
       </c>
-      <c r="N13" s="7" t="n"/>
-      <c r="O13" s="7" t="n"/>
-      <c r="P13" s="8">
-        <f>IF(O13="","",O13/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="Q13" s="9" t="n">
+      <c r="Q13" s="7" t="n"/>
+      <c r="R13" s="7" t="n"/>
+      <c r="S13" s="8">
+        <f>IF(R13="","",R13/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="T13" s="9" t="n">
+        <v>0.0066</v>
+      </c>
+      <c r="U13" s="9" t="n">
         <v>-0.0066</v>
       </c>
     </row>
@@ -1278,33 +1831,45 @@
         <v/>
       </c>
       <c r="E14" s="9" t="n">
+        <v>0.4989</v>
+      </c>
+      <c r="F14" s="9" t="n">
         <v>0.0011</v>
       </c>
-      <c r="F14" s="7" t="n"/>
       <c r="G14" s="7" t="n"/>
-      <c r="H14" s="8">
-        <f>IF(G14="","",G14/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="I14" s="9" t="n">
+      <c r="H14" s="7" t="n"/>
+      <c r="I14" s="8">
+        <f>IF(H14="","",H14/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="J14" s="9" t="n">
+        <v>0.1259</v>
+      </c>
+      <c r="K14" s="9" t="n">
         <v>0.3741</v>
       </c>
-      <c r="J14" s="7" t="n"/>
-      <c r="K14" s="7" t="n"/>
-      <c r="L14" s="8">
-        <f>IF(K14="","",K14/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="M14" s="9" t="n">
+      <c r="L14" s="7" t="n"/>
+      <c r="M14" s="7" t="n"/>
+      <c r="N14" s="8">
+        <f>IF(M14="","",M14/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="O14" s="9" t="n">
+        <v>0.0589</v>
+      </c>
+      <c r="P14" s="9" t="n">
         <v>0.4411</v>
       </c>
-      <c r="N14" s="7" t="n"/>
-      <c r="O14" s="7" t="n"/>
-      <c r="P14" s="8">
-        <f>IF(O14="","",O14/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="Q14" s="9" t="n">
+      <c r="Q14" s="7" t="n"/>
+      <c r="R14" s="7" t="n"/>
+      <c r="S14" s="8">
+        <f>IF(R14="","",R14/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="T14" s="9" t="n">
+        <v>0.0447</v>
+      </c>
+      <c r="U14" s="9" t="n">
         <v>0.4553</v>
       </c>
     </row>
@@ -1319,33 +1884,45 @@
         <v/>
       </c>
       <c r="E15" s="9" t="n">
+        <v>0.9989</v>
+      </c>
+      <c r="F15" s="9" t="n">
         <v>0.0011</v>
       </c>
-      <c r="F15" s="7" t="n"/>
       <c r="G15" s="7" t="n"/>
-      <c r="H15" s="8">
-        <f>IF(G15="","",G15/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="I15" s="9" t="n">
+      <c r="H15" s="7" t="n"/>
+      <c r="I15" s="8">
+        <f>IF(H15="","",H15/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="J15" s="9" t="n">
+        <v>0.5814</v>
+      </c>
+      <c r="K15" s="9" t="n">
         <v>0.4186</v>
       </c>
-      <c r="J15" s="7" t="n"/>
-      <c r="K15" s="7" t="n"/>
-      <c r="L15" s="8">
-        <f>IF(K15="","",K15/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="M15" s="9" t="n">
+      <c r="L15" s="7" t="n"/>
+      <c r="M15" s="7" t="n"/>
+      <c r="N15" s="8">
+        <f>IF(M15="","",M15/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="O15" s="9" t="n">
+        <v>0.08890000000000001</v>
+      </c>
+      <c r="P15" s="9" t="n">
         <v>0.9111</v>
       </c>
-      <c r="N15" s="7" t="n"/>
-      <c r="O15" s="7" t="n"/>
-      <c r="P15" s="8">
-        <f>IF(O15="","",O15/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="Q15" s="9" t="n">
+      <c r="Q15" s="7" t="n"/>
+      <c r="R15" s="7" t="n"/>
+      <c r="S15" s="8">
+        <f>IF(R15="","",R15/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="T15" s="9" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="U15" s="9" t="n">
         <v>0.9350000000000001</v>
       </c>
     </row>
@@ -1360,33 +1937,45 @@
         <v/>
       </c>
       <c r="E16" s="9" t="n">
+        <v>1.4989</v>
+      </c>
+      <c r="F16" s="9" t="n">
         <v>0.0011</v>
       </c>
-      <c r="F16" s="7" t="n"/>
       <c r="G16" s="7" t="n"/>
-      <c r="H16" s="8">
-        <f>IF(G16="","",G16/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="I16" s="9" t="n">
+      <c r="H16" s="7" t="n"/>
+      <c r="I16" s="8">
+        <f>IF(H16="","",H16/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="J16" s="9" t="n">
+        <v>1.0793</v>
+      </c>
+      <c r="K16" s="9" t="n">
         <v>0.4207</v>
       </c>
-      <c r="J16" s="7" t="n"/>
-      <c r="K16" s="7" t="n"/>
-      <c r="L16" s="8">
-        <f>IF(K16="","",K16/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="M16" s="9" t="n">
+      <c r="L16" s="7" t="n"/>
+      <c r="M16" s="7" t="n"/>
+      <c r="N16" s="8">
+        <f>IF(M16="","",M16/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="O16" s="9" t="n">
+        <v>0.1179</v>
+      </c>
+      <c r="P16" s="9" t="n">
         <v>1.3821</v>
       </c>
-      <c r="N16" s="7" t="n"/>
-      <c r="O16" s="7" t="n"/>
-      <c r="P16" s="8">
-        <f>IF(O16="","",O16/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="Q16" s="9" t="n">
+      <c r="Q16" s="7" t="n"/>
+      <c r="R16" s="7" t="n"/>
+      <c r="S16" s="8">
+        <f>IF(R16="","",R16/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="T16" s="9" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="U16" s="9" t="n">
         <v>1.42</v>
       </c>
     </row>
@@ -1401,33 +1990,45 @@
         <v/>
       </c>
       <c r="E17" s="9" t="n">
+        <v>1.9989</v>
+      </c>
+      <c r="F17" s="9" t="n">
         <v>0.0011</v>
       </c>
-      <c r="F17" s="7" t="n"/>
       <c r="G17" s="7" t="n"/>
-      <c r="H17" s="8">
-        <f>IF(G17="","",G17/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="I17" s="9" t="n">
+      <c r="H17" s="7" t="n"/>
+      <c r="I17" s="8">
+        <f>IF(H17="","",H17/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="J17" s="9" t="n">
+        <v>1.5772</v>
+      </c>
+      <c r="K17" s="9" t="n">
         <v>0.4228</v>
       </c>
-      <c r="J17" s="7" t="n"/>
-      <c r="K17" s="7" t="n"/>
-      <c r="L17" s="8">
-        <f>IF(K17="","",K17/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="M17" s="9" t="n">
+      <c r="L17" s="7" t="n"/>
+      <c r="M17" s="7" t="n"/>
+      <c r="N17" s="8">
+        <f>IF(M17="","",M17/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="O17" s="9" t="n">
+        <v>0.1748</v>
+      </c>
+      <c r="P17" s="9" t="n">
         <v>1.8252</v>
       </c>
-      <c r="N17" s="7" t="n"/>
-      <c r="O17" s="7" t="n"/>
-      <c r="P17" s="8">
-        <f>IF(O17="","",O17/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="Q17" s="9" t="n">
+      <c r="Q17" s="7" t="n"/>
+      <c r="R17" s="7" t="n"/>
+      <c r="S17" s="8">
+        <f>IF(R17="","",R17/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="T17" s="9" t="n">
+        <v>0.09279999999999999</v>
+      </c>
+      <c r="U17" s="9" t="n">
         <v>1.9072</v>
       </c>
     </row>
@@ -1442,33 +2043,45 @@
         <v/>
       </c>
       <c r="E18" s="9" t="n">
+        <v>2.4988</v>
+      </c>
+      <c r="F18" s="9" t="n">
         <v>0.0012</v>
       </c>
-      <c r="F18" s="7" t="n"/>
       <c r="G18" s="7" t="n"/>
-      <c r="H18" s="8">
-        <f>IF(G18="","",G18/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="I18" s="9" t="n">
+      <c r="H18" s="7" t="n"/>
+      <c r="I18" s="8">
+        <f>IF(H18="","",H18/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="J18" s="9" t="n">
+        <v>2.0751</v>
+      </c>
+      <c r="K18" s="9" t="n">
         <v>0.4249</v>
       </c>
-      <c r="J18" s="7" t="n"/>
-      <c r="K18" s="7" t="n"/>
-      <c r="L18" s="8">
-        <f>IF(K18="","",K18/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="M18" s="9" t="n">
+      <c r="L18" s="7" t="n"/>
+      <c r="M18" s="7" t="n"/>
+      <c r="N18" s="8">
+        <f>IF(M18="","",M18/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="O18" s="9" t="n">
+        <v>0.5859</v>
+      </c>
+      <c r="P18" s="9" t="n">
         <v>1.9141</v>
       </c>
-      <c r="N18" s="7" t="n"/>
-      <c r="O18" s="7" t="n"/>
-      <c r="P18" s="8">
-        <f>IF(O18="","",O18/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="Q18" s="9" t="n">
+      <c r="Q18" s="7" t="n"/>
+      <c r="R18" s="7" t="n"/>
+      <c r="S18" s="8">
+        <f>IF(R18="","",R18/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="T18" s="9" t="n">
+        <v>0.1049</v>
+      </c>
+      <c r="U18" s="9" t="n">
         <v>2.3951</v>
       </c>
     </row>
@@ -1483,33 +2096,45 @@
         <v/>
       </c>
       <c r="E19" s="9" t="n">
+        <v>2.9988</v>
+      </c>
+      <c r="F19" s="9" t="n">
         <v>0.0012</v>
       </c>
-      <c r="F19" s="7" t="n"/>
       <c r="G19" s="7" t="n"/>
-      <c r="H19" s="8">
-        <f>IF(G19="","",G19/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="I19" s="9" t="n">
+      <c r="H19" s="7" t="n"/>
+      <c r="I19" s="8">
+        <f>IF(H19="","",H19/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="J19" s="9" t="n">
+        <v>2.5731</v>
+      </c>
+      <c r="K19" s="9" t="n">
         <v>0.4269</v>
       </c>
-      <c r="J19" s="7" t="n"/>
-      <c r="K19" s="7" t="n"/>
-      <c r="L19" s="8">
-        <f>IF(K19="","",K19/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="M19" s="9" t="n">
+      <c r="L19" s="7" t="n"/>
+      <c r="M19" s="7" t="n"/>
+      <c r="N19" s="8">
+        <f>IF(M19="","",M19/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="O19" s="9" t="n">
+        <v>1.0766</v>
+      </c>
+      <c r="P19" s="9" t="n">
         <v>1.9234</v>
       </c>
-      <c r="N19" s="7" t="n"/>
-      <c r="O19" s="7" t="n"/>
-      <c r="P19" s="8">
-        <f>IF(O19="","",O19/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="Q19" s="9" t="n">
+      <c r="Q19" s="7" t="n"/>
+      <c r="R19" s="7" t="n"/>
+      <c r="S19" s="8">
+        <f>IF(R19="","",R19/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="T19" s="9" t="n">
+        <v>0.1175</v>
+      </c>
+      <c r="U19" s="9" t="n">
         <v>2.8825</v>
       </c>
     </row>
@@ -1524,33 +2149,45 @@
         <v/>
       </c>
       <c r="E20" s="9" t="n">
+        <v>3.4988</v>
+      </c>
+      <c r="F20" s="9" t="n">
         <v>0.0012</v>
       </c>
-      <c r="F20" s="7" t="n"/>
       <c r="G20" s="7" t="n"/>
-      <c r="H20" s="8">
-        <f>IF(G20="","",G20/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="I20" s="9" t="n">
+      <c r="H20" s="7" t="n"/>
+      <c r="I20" s="8">
+        <f>IF(H20="","",H20/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="J20" s="9" t="n">
+        <v>3.071</v>
+      </c>
+      <c r="K20" s="9" t="n">
         <v>0.429</v>
       </c>
-      <c r="J20" s="7" t="n"/>
-      <c r="K20" s="7" t="n"/>
-      <c r="L20" s="8">
-        <f>IF(K20="","",K20/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="M20" s="9" t="n">
+      <c r="L20" s="7" t="n"/>
+      <c r="M20" s="7" t="n"/>
+      <c r="N20" s="8">
+        <f>IF(M20="","",M20/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="O20" s="9" t="n">
+        <v>1.5672</v>
+      </c>
+      <c r="P20" s="9" t="n">
         <v>1.9328</v>
       </c>
-      <c r="N20" s="7" t="n"/>
-      <c r="O20" s="7" t="n"/>
-      <c r="P20" s="8">
-        <f>IF(O20="","",O20/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="Q20" s="9" t="n">
+      <c r="Q20" s="7" t="n"/>
+      <c r="R20" s="7" t="n"/>
+      <c r="S20" s="8">
+        <f>IF(R20="","",R20/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="T20" s="9" t="n">
+        <v>0.1319</v>
+      </c>
+      <c r="U20" s="9" t="n">
         <v>3.3681</v>
       </c>
     </row>
@@ -1565,33 +2202,45 @@
         <v/>
       </c>
       <c r="E21" s="9" t="n">
+        <v>3.9988</v>
+      </c>
+      <c r="F21" s="9" t="n">
         <v>0.0012</v>
       </c>
-      <c r="F21" s="7" t="n"/>
       <c r="G21" s="7" t="n"/>
-      <c r="H21" s="8">
-        <f>IF(G21="","",G21/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="I21" s="9" t="n">
+      <c r="H21" s="7" t="n"/>
+      <c r="I21" s="8">
+        <f>IF(H21="","",H21/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="J21" s="9" t="n">
+        <v>3.5689</v>
+      </c>
+      <c r="K21" s="9" t="n">
         <v>0.4311</v>
       </c>
-      <c r="J21" s="7" t="n"/>
-      <c r="K21" s="7" t="n"/>
-      <c r="L21" s="8">
-        <f>IF(K21="","",K21/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="M21" s="9" t="n">
+      <c r="L21" s="7" t="n"/>
+      <c r="M21" s="7" t="n"/>
+      <c r="N21" s="8">
+        <f>IF(M21="","",M21/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="O21" s="9" t="n">
+        <v>2.0579</v>
+      </c>
+      <c r="P21" s="9" t="n">
         <v>1.9421</v>
       </c>
-      <c r="N21" s="7" t="n"/>
-      <c r="O21" s="7" t="n"/>
-      <c r="P21" s="8">
-        <f>IF(O21="","",O21/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="Q21" s="9" t="n">
+      <c r="Q21" s="7" t="n"/>
+      <c r="R21" s="7" t="n"/>
+      <c r="S21" s="8">
+        <f>IF(R21="","",R21/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="T21" s="9" t="n">
+        <v>0.1516</v>
+      </c>
+      <c r="U21" s="9" t="n">
         <v>3.8484</v>
       </c>
     </row>
@@ -1606,33 +2255,45 @@
         <v/>
       </c>
       <c r="E22" s="9" t="n">
+        <v>4.4988</v>
+      </c>
+      <c r="F22" s="9" t="n">
         <v>0.0012</v>
       </c>
-      <c r="F22" s="7" t="n"/>
       <c r="G22" s="7" t="n"/>
-      <c r="H22" s="8">
-        <f>IF(G22="","",G22/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="I22" s="9" t="n">
+      <c r="H22" s="7" t="n"/>
+      <c r="I22" s="8">
+        <f>IF(H22="","",H22/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="J22" s="9" t="n">
+        <v>4.0668</v>
+      </c>
+      <c r="K22" s="9" t="n">
         <v>0.4332</v>
       </c>
-      <c r="J22" s="7" t="n"/>
-      <c r="K22" s="7" t="n"/>
-      <c r="L22" s="8">
-        <f>IF(K22="","",K22/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="M22" s="9" t="n">
+      <c r="L22" s="7" t="n"/>
+      <c r="M22" s="7" t="n"/>
+      <c r="N22" s="8">
+        <f>IF(M22="","",M22/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="O22" s="9" t="n">
+        <v>2.5486</v>
+      </c>
+      <c r="P22" s="9" t="n">
         <v>1.9514</v>
       </c>
-      <c r="N22" s="7" t="n"/>
-      <c r="O22" s="7" t="n"/>
-      <c r="P22" s="8">
-        <f>IF(O22="","",O22/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="Q22" s="9" t="n">
+      <c r="Q22" s="7" t="n"/>
+      <c r="R22" s="7" t="n"/>
+      <c r="S22" s="8">
+        <f>IF(R22="","",R22/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="T22" s="9" t="n">
+        <v>0.1955</v>
+      </c>
+      <c r="U22" s="9" t="n">
         <v>4.3045</v>
       </c>
     </row>
@@ -1647,33 +2308,45 @@
         <v/>
       </c>
       <c r="E23" s="9" t="n">
+        <v>4.9988</v>
+      </c>
+      <c r="F23" s="9" t="n">
         <v>0.0012</v>
       </c>
-      <c r="F23" s="7" t="n"/>
       <c r="G23" s="7" t="n"/>
-      <c r="H23" s="8">
-        <f>IF(G23="","",G23/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="I23" s="9" t="n">
+      <c r="H23" s="7" t="n"/>
+      <c r="I23" s="8">
+        <f>IF(H23="","",H23/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="J23" s="9" t="n">
+        <v>4.5647</v>
+      </c>
+      <c r="K23" s="9" t="n">
         <v>0.4353</v>
       </c>
-      <c r="J23" s="7" t="n"/>
-      <c r="K23" s="7" t="n"/>
-      <c r="L23" s="8">
-        <f>IF(K23="","",K23/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="M23" s="9" t="n">
+      <c r="L23" s="7" t="n"/>
+      <c r="M23" s="7" t="n"/>
+      <c r="N23" s="8">
+        <f>IF(M23="","",M23/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="O23" s="9" t="n">
+        <v>3.0392</v>
+      </c>
+      <c r="P23" s="9" t="n">
         <v>1.9608</v>
       </c>
-      <c r="N23" s="7" t="n"/>
-      <c r="O23" s="7" t="n"/>
-      <c r="P23" s="8">
-        <f>IF(O23="","",O23/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="Q23" s="9" t="n">
+      <c r="Q23" s="7" t="n"/>
+      <c r="R23" s="7" t="n"/>
+      <c r="S23" s="8">
+        <f>IF(R23="","",R23/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="T23" s="9" t="n">
+        <v>0.5596</v>
+      </c>
+      <c r="U23" s="9" t="n">
         <v>4.4404</v>
       </c>
     </row>
@@ -1688,33 +2361,45 @@
         <v/>
       </c>
       <c r="E24" s="9" t="n">
+        <v>5.4988</v>
+      </c>
+      <c r="F24" s="9" t="n">
         <v>0.0012</v>
       </c>
-      <c r="F24" s="7" t="n"/>
       <c r="G24" s="7" t="n"/>
-      <c r="H24" s="8">
-        <f>IF(G24="","",G24/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="I24" s="9" t="n">
+      <c r="H24" s="7" t="n"/>
+      <c r="I24" s="8">
+        <f>IF(H24="","",H24/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="J24" s="9" t="n">
+        <v>5.0627</v>
+      </c>
+      <c r="K24" s="9" t="n">
         <v>0.4373</v>
       </c>
-      <c r="J24" s="7" t="n"/>
-      <c r="K24" s="7" t="n"/>
-      <c r="L24" s="8">
-        <f>IF(K24="","",K24/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="M24" s="9" t="n">
+      <c r="L24" s="7" t="n"/>
+      <c r="M24" s="7" t="n"/>
+      <c r="N24" s="8">
+        <f>IF(M24="","",M24/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="O24" s="9" t="n">
+        <v>3.5299</v>
+      </c>
+      <c r="P24" s="9" t="n">
         <v>1.9701</v>
       </c>
-      <c r="N24" s="7" t="n"/>
-      <c r="O24" s="7" t="n"/>
-      <c r="P24" s="8">
-        <f>IF(O24="","",O24/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="Q24" s="9" t="n">
+      <c r="Q24" s="7" t="n"/>
+      <c r="R24" s="7" t="n"/>
+      <c r="S24" s="8">
+        <f>IF(R24="","",R24/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="T24" s="9" t="n">
+        <v>1.0385</v>
+      </c>
+      <c r="U24" s="9" t="n">
         <v>4.4615</v>
       </c>
     </row>
@@ -1729,33 +2414,45 @@
         <v/>
       </c>
       <c r="E25" s="9" t="n">
+        <v>5.9988</v>
+      </c>
+      <c r="F25" s="9" t="n">
         <v>0.0012</v>
       </c>
-      <c r="F25" s="7" t="n"/>
       <c r="G25" s="7" t="n"/>
-      <c r="H25" s="8">
-        <f>IF(G25="","",G25/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="I25" s="9" t="n">
+      <c r="H25" s="7" t="n"/>
+      <c r="I25" s="8">
+        <f>IF(H25="","",H25/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="J25" s="9" t="n">
+        <v>5.5606</v>
+      </c>
+      <c r="K25" s="9" t="n">
         <v>0.4394</v>
       </c>
-      <c r="J25" s="7" t="n"/>
-      <c r="K25" s="7" t="n"/>
-      <c r="L25" s="8">
-        <f>IF(K25="","",K25/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="M25" s="9" t="n">
+      <c r="L25" s="7" t="n"/>
+      <c r="M25" s="7" t="n"/>
+      <c r="N25" s="8">
+        <f>IF(M25="","",M25/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="O25" s="9" t="n">
+        <v>4.0206</v>
+      </c>
+      <c r="P25" s="9" t="n">
         <v>1.9794</v>
       </c>
-      <c r="N25" s="7" t="n"/>
-      <c r="O25" s="7" t="n"/>
-      <c r="P25" s="8">
-        <f>IF(O25="","",O25/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="Q25" s="9" t="n">
+      <c r="Q25" s="7" t="n"/>
+      <c r="R25" s="7" t="n"/>
+      <c r="S25" s="8">
+        <f>IF(R25="","",R25/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="T25" s="9" t="n">
+        <v>1.5174</v>
+      </c>
+      <c r="U25" s="9" t="n">
         <v>4.4826</v>
       </c>
     </row>
@@ -1770,33 +2467,45 @@
         <v/>
       </c>
       <c r="E26" s="9" t="n">
+        <v>6.4988</v>
+      </c>
+      <c r="F26" s="9" t="n">
         <v>0.0012</v>
       </c>
-      <c r="F26" s="7" t="n"/>
       <c r="G26" s="7" t="n"/>
-      <c r="H26" s="8">
-        <f>IF(G26="","",G26/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="I26" s="9" t="n">
+      <c r="H26" s="7" t="n"/>
+      <c r="I26" s="8">
+        <f>IF(H26="","",H26/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="J26" s="9" t="n">
+        <v>6.0585</v>
+      </c>
+      <c r="K26" s="9" t="n">
         <v>0.4415</v>
       </c>
-      <c r="J26" s="7" t="n"/>
-      <c r="K26" s="7" t="n"/>
-      <c r="L26" s="8">
-        <f>IF(K26="","",K26/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="M26" s="9" t="n">
+      <c r="L26" s="7" t="n"/>
+      <c r="M26" s="7" t="n"/>
+      <c r="N26" s="8">
+        <f>IF(M26="","",M26/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="O26" s="9" t="n">
+        <v>4.5112</v>
+      </c>
+      <c r="P26" s="9" t="n">
         <v>1.9888</v>
       </c>
-      <c r="N26" s="7" t="n"/>
-      <c r="O26" s="7" t="n"/>
-      <c r="P26" s="8">
-        <f>IF(O26="","",O26/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="Q26" s="9" t="n">
+      <c r="Q26" s="7" t="n"/>
+      <c r="R26" s="7" t="n"/>
+      <c r="S26" s="8">
+        <f>IF(R26="","",R26/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="T26" s="9" t="n">
+        <v>1.9963</v>
+      </c>
+      <c r="U26" s="9" t="n">
         <v>4.5037</v>
       </c>
     </row>
@@ -1811,33 +2520,45 @@
         <v/>
       </c>
       <c r="E27" s="9" t="n">
+        <v>6.9988</v>
+      </c>
+      <c r="F27" s="9" t="n">
         <v>0.0012</v>
       </c>
-      <c r="F27" s="7" t="n"/>
       <c r="G27" s="7" t="n"/>
-      <c r="H27" s="8">
-        <f>IF(G27="","",G27/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="I27" s="9" t="n">
+      <c r="H27" s="7" t="n"/>
+      <c r="I27" s="8">
+        <f>IF(H27="","",H27/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="J27" s="9" t="n">
+        <v>6.5564</v>
+      </c>
+      <c r="K27" s="9" t="n">
         <v>0.4436</v>
       </c>
-      <c r="J27" s="7" t="n"/>
-      <c r="K27" s="7" t="n"/>
-      <c r="L27" s="8">
-        <f>IF(K27="","",K27/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="M27" s="9" t="n">
+      <c r="L27" s="7" t="n"/>
+      <c r="M27" s="7" t="n"/>
+      <c r="N27" s="8">
+        <f>IF(M27="","",M27/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="O27" s="9" t="n">
+        <v>5.0019</v>
+      </c>
+      <c r="P27" s="9" t="n">
         <v>1.9981</v>
       </c>
-      <c r="N27" s="7" t="n"/>
-      <c r="O27" s="7" t="n"/>
-      <c r="P27" s="8">
-        <f>IF(O27="","",O27/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="Q27" s="9" t="n">
+      <c r="Q27" s="7" t="n"/>
+      <c r="R27" s="7" t="n"/>
+      <c r="S27" s="8">
+        <f>IF(R27="","",R27/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="T27" s="9" t="n">
+        <v>2.4752</v>
+      </c>
+      <c r="U27" s="9" t="n">
         <v>4.5248</v>
       </c>
     </row>
@@ -1852,33 +2573,45 @@
         <v/>
       </c>
       <c r="E28" s="9" t="n">
+        <v>7.4988</v>
+      </c>
+      <c r="F28" s="9" t="n">
         <v>0.0012</v>
       </c>
-      <c r="F28" s="7" t="n"/>
       <c r="G28" s="7" t="n"/>
-      <c r="H28" s="8">
-        <f>IF(G28="","",G28/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="I28" s="9" t="n">
+      <c r="H28" s="7" t="n"/>
+      <c r="I28" s="8">
+        <f>IF(H28="","",H28/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="J28" s="9" t="n">
+        <v>7.0543</v>
+      </c>
+      <c r="K28" s="9" t="n">
         <v>0.4457</v>
       </c>
-      <c r="J28" s="7" t="n"/>
-      <c r="K28" s="7" t="n"/>
-      <c r="L28" s="8">
-        <f>IF(K28="","",K28/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="M28" s="9" t="n">
+      <c r="L28" s="7" t="n"/>
+      <c r="M28" s="7" t="n"/>
+      <c r="N28" s="8">
+        <f>IF(M28="","",M28/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="O28" s="9" t="n">
+        <v>5.4926</v>
+      </c>
+      <c r="P28" s="9" t="n">
         <v>2.0074</v>
       </c>
-      <c r="N28" s="7" t="n"/>
-      <c r="O28" s="7" t="n"/>
-      <c r="P28" s="8">
-        <f>IF(O28="","",O28/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="Q28" s="9" t="n">
+      <c r="Q28" s="7" t="n"/>
+      <c r="R28" s="7" t="n"/>
+      <c r="S28" s="8">
+        <f>IF(R28="","",R28/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="T28" s="9" t="n">
+        <v>2.9541</v>
+      </c>
+      <c r="U28" s="9" t="n">
         <v>4.5459</v>
       </c>
     </row>
@@ -1893,33 +2626,45 @@
         <v/>
       </c>
       <c r="E29" s="9" t="n">
+        <v>7.9988</v>
+      </c>
+      <c r="F29" s="9" t="n">
         <v>0.0012</v>
       </c>
-      <c r="F29" s="7" t="n"/>
       <c r="G29" s="7" t="n"/>
-      <c r="H29" s="8">
-        <f>IF(G29="","",G29/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="I29" s="9" t="n">
+      <c r="H29" s="7" t="n"/>
+      <c r="I29" s="8">
+        <f>IF(H29="","",H29/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="J29" s="9" t="n">
+        <v>7.5523</v>
+      </c>
+      <c r="K29" s="9" t="n">
         <v>0.4477</v>
       </c>
-      <c r="J29" s="7" t="n"/>
-      <c r="K29" s="7" t="n"/>
-      <c r="L29" s="8">
-        <f>IF(K29="","",K29/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="M29" s="9" t="n">
+      <c r="L29" s="7" t="n"/>
+      <c r="M29" s="7" t="n"/>
+      <c r="N29" s="8">
+        <f>IF(M29="","",M29/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="O29" s="9" t="n">
+        <v>5.9832</v>
+      </c>
+      <c r="P29" s="9" t="n">
         <v>2.0168</v>
       </c>
-      <c r="N29" s="7" t="n"/>
-      <c r="O29" s="7" t="n"/>
-      <c r="P29" s="8">
-        <f>IF(O29="","",O29/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="Q29" s="9" t="n">
+      <c r="Q29" s="7" t="n"/>
+      <c r="R29" s="7" t="n"/>
+      <c r="S29" s="8">
+        <f>IF(R29="","",R29/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="T29" s="9" t="n">
+        <v>3.433</v>
+      </c>
+      <c r="U29" s="9" t="n">
         <v>4.567</v>
       </c>
     </row>
@@ -1934,33 +2679,45 @@
         <v/>
       </c>
       <c r="E30" s="9" t="n">
+        <v>8.498799999999999</v>
+      </c>
+      <c r="F30" s="9" t="n">
         <v>0.0012</v>
       </c>
-      <c r="F30" s="7" t="n"/>
       <c r="G30" s="7" t="n"/>
-      <c r="H30" s="8">
-        <f>IF(G30="","",G30/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="I30" s="9" t="n">
+      <c r="H30" s="7" t="n"/>
+      <c r="I30" s="8">
+        <f>IF(H30="","",H30/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="J30" s="9" t="n">
+        <v>8.0502</v>
+      </c>
+      <c r="K30" s="9" t="n">
         <v>0.4498</v>
       </c>
-      <c r="J30" s="7" t="n"/>
-      <c r="K30" s="7" t="n"/>
-      <c r="L30" s="8">
-        <f>IF(K30="","",K30/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="M30" s="9" t="n">
+      <c r="L30" s="7" t="n"/>
+      <c r="M30" s="7" t="n"/>
+      <c r="N30" s="8">
+        <f>IF(M30="","",M30/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="O30" s="9" t="n">
+        <v>6.4739</v>
+      </c>
+      <c r="P30" s="9" t="n">
         <v>2.0261</v>
       </c>
-      <c r="N30" s="7" t="n"/>
-      <c r="O30" s="7" t="n"/>
-      <c r="P30" s="8">
-        <f>IF(O30="","",O30/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="Q30" s="9" t="n">
+      <c r="Q30" s="7" t="n"/>
+      <c r="R30" s="7" t="n"/>
+      <c r="S30" s="8">
+        <f>IF(R30="","",R30/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="T30" s="9" t="n">
+        <v>3.9119</v>
+      </c>
+      <c r="U30" s="9" t="n">
         <v>4.5881</v>
       </c>
     </row>
@@ -1975,33 +2732,45 @@
         <v/>
       </c>
       <c r="E31" s="9" t="n">
+        <v>8.998799999999999</v>
+      </c>
+      <c r="F31" s="9" t="n">
         <v>0.0012</v>
       </c>
-      <c r="F31" s="7" t="n"/>
       <c r="G31" s="7" t="n"/>
-      <c r="H31" s="8">
-        <f>IF(G31="","",G31/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="I31" s="9" t="n">
+      <c r="H31" s="7" t="n"/>
+      <c r="I31" s="8">
+        <f>IF(H31="","",H31/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="J31" s="9" t="n">
+        <v>8.5481</v>
+      </c>
+      <c r="K31" s="9" t="n">
         <v>0.4519</v>
       </c>
-      <c r="J31" s="7" t="n"/>
-      <c r="K31" s="7" t="n"/>
-      <c r="L31" s="8">
-        <f>IF(K31="","",K31/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="M31" s="9" t="n">
+      <c r="L31" s="7" t="n"/>
+      <c r="M31" s="7" t="n"/>
+      <c r="N31" s="8">
+        <f>IF(M31="","",M31/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="O31" s="9" t="n">
+        <v>6.9646</v>
+      </c>
+      <c r="P31" s="9" t="n">
         <v>2.0354</v>
       </c>
-      <c r="N31" s="7" t="n"/>
-      <c r="O31" s="7" t="n"/>
-      <c r="P31" s="8">
-        <f>IF(O31="","",O31/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="Q31" s="9" t="n">
+      <c r="Q31" s="7" t="n"/>
+      <c r="R31" s="7" t="n"/>
+      <c r="S31" s="8">
+        <f>IF(R31="","",R31/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="T31" s="9" t="n">
+        <v>4.3908</v>
+      </c>
+      <c r="U31" s="9" t="n">
         <v>4.6092</v>
       </c>
     </row>
@@ -2016,33 +2785,45 @@
         <v/>
       </c>
       <c r="E32" s="9" t="n">
+        <v>9.498799999999999</v>
+      </c>
+      <c r="F32" s="9" t="n">
         <v>0.0012</v>
       </c>
-      <c r="F32" s="7" t="n"/>
       <c r="G32" s="7" t="n"/>
-      <c r="H32" s="8">
-        <f>IF(G32="","",G32/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="I32" s="9" t="n">
+      <c r="H32" s="7" t="n"/>
+      <c r="I32" s="8">
+        <f>IF(H32="","",H32/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="J32" s="9" t="n">
+        <v>9.045999999999999</v>
+      </c>
+      <c r="K32" s="9" t="n">
         <v>0.454</v>
       </c>
-      <c r="J32" s="7" t="n"/>
-      <c r="K32" s="7" t="n"/>
-      <c r="L32" s="8">
-        <f>IF(K32="","",K32/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="M32" s="9" t="n">
+      <c r="L32" s="7" t="n"/>
+      <c r="M32" s="7" t="n"/>
+      <c r="N32" s="8">
+        <f>IF(M32="","",M32/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="O32" s="9" t="n">
+        <v>7.4552</v>
+      </c>
+      <c r="P32" s="9" t="n">
         <v>2.0448</v>
       </c>
-      <c r="N32" s="7" t="n"/>
-      <c r="O32" s="7" t="n"/>
-      <c r="P32" s="8">
-        <f>IF(O32="","",O32/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="Q32" s="9" t="n">
+      <c r="Q32" s="7" t="n"/>
+      <c r="R32" s="7" t="n"/>
+      <c r="S32" s="8">
+        <f>IF(R32="","",R32/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="T32" s="9" t="n">
+        <v>4.8698</v>
+      </c>
+      <c r="U32" s="9" t="n">
         <v>4.6302</v>
       </c>
     </row>
@@ -2057,33 +2838,45 @@
         <v/>
       </c>
       <c r="E33" s="9" t="n">
+        <v>9.998799999999999</v>
+      </c>
+      <c r="F33" s="9" t="n">
         <v>0.0012</v>
       </c>
-      <c r="F33" s="7" t="n"/>
       <c r="G33" s="7" t="n"/>
-      <c r="H33" s="8">
-        <f>IF(G33="","",G33/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="I33" s="9" t="n">
+      <c r="H33" s="7" t="n"/>
+      <c r="I33" s="8">
+        <f>IF(H33="","",H33/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="J33" s="9" t="n">
+        <v>9.543900000000001</v>
+      </c>
+      <c r="K33" s="9" t="n">
         <v>0.4561</v>
       </c>
-      <c r="J33" s="7" t="n"/>
-      <c r="K33" s="7" t="n"/>
-      <c r="L33" s="8">
-        <f>IF(K33="","",K33/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="M33" s="9" t="n">
+      <c r="L33" s="7" t="n"/>
+      <c r="M33" s="7" t="n"/>
+      <c r="N33" s="8">
+        <f>IF(M33="","",M33/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="O33" s="9" t="n">
+        <v>7.9459</v>
+      </c>
+      <c r="P33" s="9" t="n">
         <v>2.0541</v>
       </c>
-      <c r="N33" s="7" t="n"/>
-      <c r="O33" s="7" t="n"/>
-      <c r="P33" s="8">
-        <f>IF(O33="","",O33/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="Q33" s="9" t="n">
+      <c r="Q33" s="7" t="n"/>
+      <c r="R33" s="7" t="n"/>
+      <c r="S33" s="8">
+        <f>IF(R33="","",R33/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="T33" s="9" t="n">
+        <v>5.3487</v>
+      </c>
+      <c r="U33" s="9" t="n">
         <v>4.6513</v>
       </c>
     </row>
@@ -2098,33 +2891,45 @@
         <v/>
       </c>
       <c r="E34" s="9" t="n">
+        <v>10.4988</v>
+      </c>
+      <c r="F34" s="9" t="n">
         <v>0.0012</v>
       </c>
-      <c r="F34" s="7" t="n"/>
       <c r="G34" s="7" t="n"/>
-      <c r="H34" s="8">
-        <f>IF(G34="","",G34/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="I34" s="9" t="n">
+      <c r="H34" s="7" t="n"/>
+      <c r="I34" s="8">
+        <f>IF(H34="","",H34/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="J34" s="9" t="n">
+        <v>10.0419</v>
+      </c>
+      <c r="K34" s="9" t="n">
         <v>0.4581</v>
       </c>
-      <c r="J34" s="7" t="n"/>
-      <c r="K34" s="7" t="n"/>
-      <c r="L34" s="8">
-        <f>IF(K34="","",K34/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="M34" s="9" t="n">
+      <c r="L34" s="7" t="n"/>
+      <c r="M34" s="7" t="n"/>
+      <c r="N34" s="8">
+        <f>IF(M34="","",M34/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="O34" s="9" t="n">
+        <v>8.4366</v>
+      </c>
+      <c r="P34" s="9" t="n">
         <v>2.0634</v>
       </c>
-      <c r="N34" s="7" t="n"/>
-      <c r="O34" s="7" t="n"/>
-      <c r="P34" s="8">
-        <f>IF(O34="","",O34/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="Q34" s="9" t="n">
+      <c r="Q34" s="7" t="n"/>
+      <c r="R34" s="7" t="n"/>
+      <c r="S34" s="8">
+        <f>IF(R34="","",R34/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="T34" s="9" t="n">
+        <v>5.8276</v>
+      </c>
+      <c r="U34" s="9" t="n">
         <v>4.6724</v>
       </c>
     </row>
@@ -2139,33 +2944,45 @@
         <v/>
       </c>
       <c r="E35" s="9" t="n">
+        <v>10.9988</v>
+      </c>
+      <c r="F35" s="9" t="n">
         <v>0.0012</v>
       </c>
-      <c r="F35" s="7" t="n"/>
       <c r="G35" s="7" t="n"/>
-      <c r="H35" s="8">
-        <f>IF(G35="","",G35/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="I35" s="9" t="n">
+      <c r="H35" s="7" t="n"/>
+      <c r="I35" s="8">
+        <f>IF(H35="","",H35/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="J35" s="9" t="n">
+        <v>10.5398</v>
+      </c>
+      <c r="K35" s="9" t="n">
         <v>0.4602</v>
       </c>
-      <c r="J35" s="7" t="n"/>
-      <c r="K35" s="7" t="n"/>
-      <c r="L35" s="8">
-        <f>IF(K35="","",K35/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="M35" s="9" t="n">
+      <c r="L35" s="7" t="n"/>
+      <c r="M35" s="7" t="n"/>
+      <c r="N35" s="8">
+        <f>IF(M35="","",M35/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="O35" s="9" t="n">
+        <v>8.927300000000001</v>
+      </c>
+      <c r="P35" s="9" t="n">
         <v>2.0727</v>
       </c>
-      <c r="N35" s="7" t="n"/>
-      <c r="O35" s="7" t="n"/>
-      <c r="P35" s="8">
-        <f>IF(O35="","",O35/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="Q35" s="9" t="n">
+      <c r="Q35" s="7" t="n"/>
+      <c r="R35" s="7" t="n"/>
+      <c r="S35" s="8">
+        <f>IF(R35="","",R35/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="T35" s="9" t="n">
+        <v>6.3065</v>
+      </c>
+      <c r="U35" s="9" t="n">
         <v>4.6935</v>
       </c>
     </row>
@@ -2180,33 +2997,45 @@
         <v/>
       </c>
       <c r="E36" s="9" t="n">
+        <v>11.4987</v>
+      </c>
+      <c r="F36" s="9" t="n">
         <v>0.0013</v>
       </c>
-      <c r="F36" s="7" t="n"/>
       <c r="G36" s="7" t="n"/>
-      <c r="H36" s="8">
-        <f>IF(G36="","",G36/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="I36" s="9" t="n">
+      <c r="H36" s="7" t="n"/>
+      <c r="I36" s="8">
+        <f>IF(H36="","",H36/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="J36" s="9" t="n">
+        <v>11.0377</v>
+      </c>
+      <c r="K36" s="9" t="n">
         <v>0.4623</v>
       </c>
-      <c r="J36" s="7" t="n"/>
-      <c r="K36" s="7" t="n"/>
-      <c r="L36" s="8">
-        <f>IF(K36="","",K36/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="M36" s="9" t="n">
+      <c r="L36" s="7" t="n"/>
+      <c r="M36" s="7" t="n"/>
+      <c r="N36" s="8">
+        <f>IF(M36="","",M36/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="O36" s="9" t="n">
+        <v>9.417899999999999</v>
+      </c>
+      <c r="P36" s="9" t="n">
         <v>2.0821</v>
       </c>
-      <c r="N36" s="7" t="n"/>
-      <c r="O36" s="7" t="n"/>
-      <c r="P36" s="8">
-        <f>IF(O36="","",O36/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="Q36" s="9" t="n">
+      <c r="Q36" s="7" t="n"/>
+      <c r="R36" s="7" t="n"/>
+      <c r="S36" s="8">
+        <f>IF(R36="","",R36/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="T36" s="9" t="n">
+        <v>6.7854</v>
+      </c>
+      <c r="U36" s="9" t="n">
         <v>4.7146</v>
       </c>
     </row>
@@ -2221,33 +3050,45 @@
         <v/>
       </c>
       <c r="E37" s="9" t="n">
+        <v>11.9987</v>
+      </c>
+      <c r="F37" s="9" t="n">
         <v>0.0013</v>
       </c>
-      <c r="F37" s="7" t="n"/>
       <c r="G37" s="7" t="n"/>
-      <c r="H37" s="8">
-        <f>IF(G37="","",G37/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="I37" s="9" t="n">
+      <c r="H37" s="7" t="n"/>
+      <c r="I37" s="8">
+        <f>IF(H37="","",H37/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="J37" s="9" t="n">
+        <v>11.5356</v>
+      </c>
+      <c r="K37" s="9" t="n">
         <v>0.4644</v>
       </c>
-      <c r="J37" s="7" t="n"/>
-      <c r="K37" s="7" t="n"/>
-      <c r="L37" s="8">
-        <f>IF(K37="","",K37/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="M37" s="9" t="n">
+      <c r="L37" s="7" t="n"/>
+      <c r="M37" s="7" t="n"/>
+      <c r="N37" s="8">
+        <f>IF(M37="","",M37/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="O37" s="9" t="n">
+        <v>9.9086</v>
+      </c>
+      <c r="P37" s="9" t="n">
         <v>2.0914</v>
       </c>
-      <c r="N37" s="7" t="n"/>
-      <c r="O37" s="7" t="n"/>
-      <c r="P37" s="8">
-        <f>IF(O37="","",O37/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="Q37" s="9" t="n">
+      <c r="Q37" s="7" t="n"/>
+      <c r="R37" s="7" t="n"/>
+      <c r="S37" s="8">
+        <f>IF(R37="","",R37/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="T37" s="9" t="n">
+        <v>7.2643</v>
+      </c>
+      <c r="U37" s="9" t="n">
         <v>4.7357</v>
       </c>
     </row>
@@ -2262,33 +3103,45 @@
         <v/>
       </c>
       <c r="E38" s="9" t="n">
+        <v>12.4987</v>
+      </c>
+      <c r="F38" s="9" t="n">
         <v>0.0013</v>
       </c>
-      <c r="F38" s="7" t="n"/>
       <c r="G38" s="7" t="n"/>
-      <c r="H38" s="8">
-        <f>IF(G38="","",G38/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="I38" s="9" t="n">
+      <c r="H38" s="7" t="n"/>
+      <c r="I38" s="8">
+        <f>IF(H38="","",H38/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="J38" s="9" t="n">
+        <v>12.0335</v>
+      </c>
+      <c r="K38" s="9" t="n">
         <v>0.4665</v>
       </c>
-      <c r="J38" s="7" t="n"/>
-      <c r="K38" s="7" t="n"/>
-      <c r="L38" s="8">
-        <f>IF(K38="","",K38/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="M38" s="9" t="n">
+      <c r="L38" s="7" t="n"/>
+      <c r="M38" s="7" t="n"/>
+      <c r="N38" s="8">
+        <f>IF(M38="","",M38/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="O38" s="9" t="n">
+        <v>10.3993</v>
+      </c>
+      <c r="P38" s="9" t="n">
         <v>2.1007</v>
       </c>
-      <c r="N38" s="7" t="n"/>
-      <c r="O38" s="7" t="n"/>
-      <c r="P38" s="8">
-        <f>IF(O38="","",O38/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="Q38" s="9" t="n">
+      <c r="Q38" s="7" t="n"/>
+      <c r="R38" s="7" t="n"/>
+      <c r="S38" s="8">
+        <f>IF(R38="","",R38/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="T38" s="9" t="n">
+        <v>7.7432</v>
+      </c>
+      <c r="U38" s="9" t="n">
         <v>4.7568</v>
       </c>
     </row>
@@ -2303,33 +3156,45 @@
         <v/>
       </c>
       <c r="E39" s="9" t="n">
+        <v>12.9987</v>
+      </c>
+      <c r="F39" s="9" t="n">
         <v>0.0013</v>
       </c>
-      <c r="F39" s="7" t="n"/>
       <c r="G39" s="7" t="n"/>
-      <c r="H39" s="8">
-        <f>IF(G39="","",G39/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="I39" s="9" t="n">
+      <c r="H39" s="7" t="n"/>
+      <c r="I39" s="8">
+        <f>IF(H39="","",H39/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="J39" s="9" t="n">
+        <v>12.5315</v>
+      </c>
+      <c r="K39" s="9" t="n">
         <v>0.4685</v>
       </c>
-      <c r="J39" s="7" t="n"/>
-      <c r="K39" s="7" t="n"/>
-      <c r="L39" s="8">
-        <f>IF(K39="","",K39/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="M39" s="9" t="n">
+      <c r="L39" s="7" t="n"/>
+      <c r="M39" s="7" t="n"/>
+      <c r="N39" s="8">
+        <f>IF(M39="","",M39/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="O39" s="9" t="n">
+        <v>10.89</v>
+      </c>
+      <c r="P39" s="9" t="n">
         <v>2.11</v>
       </c>
-      <c r="N39" s="7" t="n"/>
-      <c r="O39" s="7" t="n"/>
-      <c r="P39" s="8">
-        <f>IF(O39="","",O39/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="Q39" s="9" t="n">
+      <c r="Q39" s="7" t="n"/>
+      <c r="R39" s="7" t="n"/>
+      <c r="S39" s="8">
+        <f>IF(R39="","",R39/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="T39" s="9" t="n">
+        <v>8.222200000000001</v>
+      </c>
+      <c r="U39" s="9" t="n">
         <v>4.7778</v>
       </c>
     </row>
@@ -2344,33 +3209,45 @@
         <v/>
       </c>
       <c r="E40" s="9" t="n">
+        <v>13.4987</v>
+      </c>
+      <c r="F40" s="9" t="n">
         <v>0.0013</v>
       </c>
-      <c r="F40" s="7" t="n"/>
       <c r="G40" s="7" t="n"/>
-      <c r="H40" s="8">
-        <f>IF(G40="","",G40/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="I40" s="9" t="n">
+      <c r="H40" s="7" t="n"/>
+      <c r="I40" s="8">
+        <f>IF(H40="","",H40/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="J40" s="9" t="n">
+        <v>13.0294</v>
+      </c>
+      <c r="K40" s="9" t="n">
         <v>0.4706</v>
       </c>
-      <c r="J40" s="7" t="n"/>
-      <c r="K40" s="7" t="n"/>
-      <c r="L40" s="8">
-        <f>IF(K40="","",K40/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="M40" s="9" t="n">
+      <c r="L40" s="7" t="n"/>
+      <c r="M40" s="7" t="n"/>
+      <c r="N40" s="8">
+        <f>IF(M40="","",M40/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="O40" s="9" t="n">
+        <v>11.3806</v>
+      </c>
+      <c r="P40" s="9" t="n">
         <v>2.1194</v>
       </c>
-      <c r="N40" s="7" t="n"/>
-      <c r="O40" s="7" t="n"/>
-      <c r="P40" s="8">
-        <f>IF(O40="","",O40/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="Q40" s="9" t="n">
+      <c r="Q40" s="7" t="n"/>
+      <c r="R40" s="7" t="n"/>
+      <c r="S40" s="8">
+        <f>IF(R40="","",R40/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="T40" s="9" t="n">
+        <v>8.7011</v>
+      </c>
+      <c r="U40" s="9" t="n">
         <v>4.7989</v>
       </c>
     </row>
@@ -2385,33 +3262,45 @@
         <v/>
       </c>
       <c r="E41" s="9" t="n">
+        <v>13.9987</v>
+      </c>
+      <c r="F41" s="9" t="n">
         <v>0.0013</v>
       </c>
-      <c r="F41" s="7" t="n"/>
       <c r="G41" s="7" t="n"/>
-      <c r="H41" s="8">
-        <f>IF(G41="","",G41/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="I41" s="9" t="n">
+      <c r="H41" s="7" t="n"/>
+      <c r="I41" s="8">
+        <f>IF(H41="","",H41/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="J41" s="9" t="n">
+        <v>13.5273</v>
+      </c>
+      <c r="K41" s="9" t="n">
         <v>0.4727</v>
       </c>
-      <c r="J41" s="7" t="n"/>
-      <c r="K41" s="7" t="n"/>
-      <c r="L41" s="8">
-        <f>IF(K41="","",K41/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="M41" s="9" t="n">
+      <c r="L41" s="7" t="n"/>
+      <c r="M41" s="7" t="n"/>
+      <c r="N41" s="8">
+        <f>IF(M41="","",M41/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="O41" s="9" t="n">
+        <v>11.8713</v>
+      </c>
+      <c r="P41" s="9" t="n">
         <v>2.1287</v>
       </c>
-      <c r="N41" s="7" t="n"/>
-      <c r="O41" s="7" t="n"/>
-      <c r="P41" s="8">
-        <f>IF(O41="","",O41/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="Q41" s="9" t="n">
+      <c r="Q41" s="7" t="n"/>
+      <c r="R41" s="7" t="n"/>
+      <c r="S41" s="8">
+        <f>IF(R41="","",R41/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="T41" s="9" t="n">
+        <v>9.18</v>
+      </c>
+      <c r="U41" s="9" t="n">
         <v>4.82</v>
       </c>
     </row>
@@ -2426,33 +3315,45 @@
         <v/>
       </c>
       <c r="E42" s="9" t="n">
+        <v>14.4987</v>
+      </c>
+      <c r="F42" s="9" t="n">
         <v>0.0013</v>
       </c>
-      <c r="F42" s="7" t="n"/>
       <c r="G42" s="7" t="n"/>
-      <c r="H42" s="8">
-        <f>IF(G42="","",G42/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="I42" s="9" t="n">
+      <c r="H42" s="7" t="n"/>
+      <c r="I42" s="8">
+        <f>IF(H42="","",H42/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="J42" s="9" t="n">
+        <v>14.0252</v>
+      </c>
+      <c r="K42" s="9" t="n">
         <v>0.4748</v>
       </c>
-      <c r="J42" s="7" t="n"/>
-      <c r="K42" s="7" t="n"/>
-      <c r="L42" s="8">
-        <f>IF(K42="","",K42/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="M42" s="9" t="n">
+      <c r="L42" s="7" t="n"/>
+      <c r="M42" s="7" t="n"/>
+      <c r="N42" s="8">
+        <f>IF(M42="","",M42/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="O42" s="9" t="n">
+        <v>12.362</v>
+      </c>
+      <c r="P42" s="9" t="n">
         <v>2.138</v>
       </c>
-      <c r="N42" s="7" t="n"/>
-      <c r="O42" s="7" t="n"/>
-      <c r="P42" s="8">
-        <f>IF(O42="","",O42/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="Q42" s="9" t="n">
+      <c r="Q42" s="7" t="n"/>
+      <c r="R42" s="7" t="n"/>
+      <c r="S42" s="8">
+        <f>IF(R42="","",R42/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="T42" s="9" t="n">
+        <v>9.658899999999999</v>
+      </c>
+      <c r="U42" s="9" t="n">
         <v>4.8411</v>
       </c>
     </row>
@@ -2467,33 +3368,45 @@
         <v/>
       </c>
       <c r="E43" s="9" t="n">
+        <v>14.9987</v>
+      </c>
+      <c r="F43" s="9" t="n">
         <v>0.0013</v>
       </c>
-      <c r="F43" s="7" t="n"/>
       <c r="G43" s="7" t="n"/>
-      <c r="H43" s="8">
-        <f>IF(G43="","",G43/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="I43" s="9" t="n">
+      <c r="H43" s="7" t="n"/>
+      <c r="I43" s="8">
+        <f>IF(H43="","",H43/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="J43" s="9" t="n">
+        <v>14.5232</v>
+      </c>
+      <c r="K43" s="9" t="n">
         <v>0.4768</v>
       </c>
-      <c r="J43" s="7" t="n"/>
-      <c r="K43" s="7" t="n"/>
-      <c r="L43" s="8">
-        <f>IF(K43="","",K43/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="M43" s="9" t="n">
+      <c r="L43" s="7" t="n"/>
+      <c r="M43" s="7" t="n"/>
+      <c r="N43" s="8">
+        <f>IF(M43="","",M43/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="O43" s="9" t="n">
+        <v>12.8527</v>
+      </c>
+      <c r="P43" s="9" t="n">
         <v>2.1473</v>
       </c>
-      <c r="N43" s="7" t="n"/>
-      <c r="O43" s="7" t="n"/>
-      <c r="P43" s="8">
-        <f>IF(O43="","",O43/$B$4*1000)</f>
-        <v/>
-      </c>
-      <c r="Q43" s="9" t="n">
+      <c r="Q43" s="7" t="n"/>
+      <c r="R43" s="7" t="n"/>
+      <c r="S43" s="8">
+        <f>IF(R43="","",R43/$B$4*1000)</f>
+        <v/>
+      </c>
+      <c r="T43" s="9" t="n">
+        <v>10.1379</v>
+      </c>
+      <c r="U43" s="9" t="n">
         <v>4.8621</v>
       </c>
     </row>
@@ -2595,11 +3508,11 @@
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="F11:I11"/>
-    <mergeCell ref="J11:M11"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="Q11:U11"/>
     <mergeCell ref="A2:Q2"/>
-    <mergeCell ref="N11:Q11"/>
-    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="G11:K11"/>
+    <mergeCell ref="L11:P11"/>
     <mergeCell ref="A1:Q1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3071,6 +3984,7 @@
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3660,5 +4574,6 @@
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/simulations/lab2/measured/Lab2-數據記錄.xlsx
+++ b/simulations/lab2/measured/Lab2-數據記錄.xlsx
@@ -9,8 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="說明" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="實驗一 特性曲線" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="實驗二 beta" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="第二部分 CE 放大器" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交報告用 Table 1" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="實驗二 beta" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="第二部分 CE 放大器" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,7 +25,7 @@
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -53,8 +54,13 @@
       <name val="Arial"/>
       <color rgb="000000FF"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -76,8 +82,13 @@
         <fgColor rgb="00EDF1F9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="003C7FB1"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -99,11 +110,44 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -118,20 +162,27 @@
     <xf numFmtId="165" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1552,7 +1603,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>各組的 V_BE（導通後幾乎不變，量一次即可）與 ON/OFF 判定</t>
+          <t>各組的預報值（實測 V_BE 與 ON/OFF 填在下面各組的標題列，比照講義 Table 1）</t>
         </is>
       </c>
     </row>
@@ -1568,17 +1619,17 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>實測 V_BE (V)</t>
+          <t>LTspice V_BE (V)</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>LTspice V_BE (V)</t>
+          <t>LTspice I_C @ 15 V (mA)</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>ON / OFF</t>
+          <t>ON/OFF（預期）</t>
         </is>
       </c>
     </row>
@@ -1586,79 +1637,110 @@
       <c r="E6" s="6" t="n">
         <v>1.5</v>
       </c>
-      <c r="F6" s="7" t="n"/>
+      <c r="F6" s="9" t="n">
+        <v>0.48</v>
+      </c>
       <c r="G6" s="9" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="H6" s="12" t="n"/>
+        <v>0.001</v>
+      </c>
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="E7" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F7" s="7" t="n"/>
+      <c r="F7" s="9" t="n">
+        <v>0.633</v>
+      </c>
       <c r="G7" s="9" t="n">
-        <v>0.633</v>
-      </c>
-      <c r="H7" s="12" t="n"/>
+        <v>0.477</v>
+      </c>
+      <c r="H7" s="12" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="E8" s="6" t="n">
         <v>2.2</v>
       </c>
-      <c r="F8" s="7" t="n"/>
+      <c r="F8" s="9" t="n">
+        <v>0.673</v>
+      </c>
       <c r="G8" s="9" t="n">
-        <v>0.673</v>
-      </c>
-      <c r="H8" s="12" t="n"/>
+        <v>2.147</v>
+      </c>
+      <c r="H8" s="12" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="E9" s="6" t="n">
         <v>2.4</v>
       </c>
-      <c r="F9" s="7" t="n"/>
+      <c r="F9" s="9" t="n">
+        <v>0.695</v>
+      </c>
       <c r="G9" s="9" t="n">
-        <v>0.695</v>
-      </c>
-      <c r="H9" s="12" t="n"/>
+        <v>4.862</v>
+      </c>
+      <c r="H9" s="12" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>↓ 各組標題列右邊兩個黃格：左邊填該組量到的 V_BE、右邊填 ON 或 OFF（對應講義 Table 1 的區塊標題）</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>V_BB = 1.5 V</t>
+          <t>V_BB = 1.5 V　V_BE =</t>
         </is>
       </c>
       <c r="C11" s="14" t="n"/>
       <c r="D11" s="14" t="n"/>
-      <c r="E11" s="14" t="n"/>
-      <c r="F11" s="14" t="n"/>
+      <c r="E11" s="7" t="n"/>
+      <c r="F11" s="15" t="n"/>
       <c r="G11" s="13" t="inlineStr">
         <is>
-          <t>V_BB = 2.0 V</t>
+          <t>V_BB = 2.0 V　V_BE =</t>
         </is>
       </c>
       <c r="H11" s="14" t="n"/>
       <c r="I11" s="14" t="n"/>
-      <c r="J11" s="14" t="n"/>
-      <c r="K11" s="14" t="n"/>
+      <c r="J11" s="7" t="n"/>
+      <c r="K11" s="15" t="n"/>
       <c r="L11" s="13" t="inlineStr">
         <is>
-          <t>V_BB = 2.2 V</t>
+          <t>V_BB = 2.2 V　V_BE =</t>
         </is>
       </c>
       <c r="M11" s="14" t="n"/>
       <c r="N11" s="14" t="n"/>
-      <c r="O11" s="14" t="n"/>
-      <c r="P11" s="14" t="n"/>
+      <c r="O11" s="7" t="n"/>
+      <c r="P11" s="15" t="n"/>
       <c r="Q11" s="13" t="inlineStr">
         <is>
-          <t>V_BB = 2.4 V</t>
+          <t>V_BB = 2.4 V　V_BE =</t>
         </is>
       </c>
       <c r="R11" s="14" t="n"/>
       <c r="S11" s="14" t="n"/>
-      <c r="T11" s="14" t="n"/>
-      <c r="U11" s="14" t="n"/>
+      <c r="T11" s="7" t="n"/>
+      <c r="U11" s="15" t="n"/>
     </row>
     <row r="12" ht="34" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
@@ -3425,82 +3507,82 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="15" t="inlineStr">
+      <c r="A48" s="16" t="inlineStr">
         <is>
           <t>要留的證據</t>
         </is>
       </c>
-      <c r="B48" s="15" t="inlineStr">
+      <c r="B48" s="16" t="inlineStr">
         <is>
           <t>打勾</t>
         </is>
       </c>
-      <c r="C48" s="15" t="inlineStr">
+      <c r="C48" s="16" t="inlineStr">
         <is>
           <t>備註</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="16" t="inlineStr">
+      <c r="A49" s="17" t="inlineStr">
         <is>
           <t>麵包板全景照 1 張</t>
         </is>
       </c>
-      <c r="B49" s="12" t="n"/>
-      <c r="C49" s="17" t="inlineStr">
+      <c r="B49" s="18" t="n"/>
+      <c r="C49" s="19" t="inlineStr">
         <is>
           <t>看得出 R1／R2／RC 各插在第幾欄、電晶體三腳的 E／B／C 方向</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="16" t="inlineStr">
+      <c r="A50" s="17" t="inlineStr">
         <is>
           <t>電表接線特寫 1 張</t>
         </is>
       </c>
-      <c r="B50" s="12" t="n"/>
-      <c r="C50" s="17" t="inlineStr">
+      <c r="B50" s="18" t="n"/>
+      <c r="C50" s="19" t="inlineStr">
         <is>
           <t>左表跨 B-E、中表跨 C-E、右表串在 VCC 與 RC 之間</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="16" t="inlineStr">
+      <c r="A51" s="17" t="inlineStr">
         <is>
           <t>兩台電源面板各 1 張</t>
         </is>
       </c>
-      <c r="B51" s="12" t="n"/>
-      <c r="C51" s="17" t="inlineStr">
+      <c r="B51" s="18" t="n"/>
+      <c r="C51" s="19" t="inlineStr">
         <is>
           <t>V_BB 與 V_CC 的設定值要和記錄表對得上</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="16" t="inlineStr">
+      <c r="A52" s="17" t="inlineStr">
         <is>
           <t>四組 V_BB 的 V_BE 都記到</t>
         </is>
       </c>
-      <c r="B52" s="12" t="n"/>
-      <c r="C52" s="17" t="inlineStr">
+      <c r="B52" s="18" t="n"/>
+      <c r="C52" s="19" t="inlineStr">
         <is>
           <t>導通後 V_BE 幾乎不動，沒記到就無法回答「ON/OFF 怎麼判定」</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="16" t="inlineStr">
+      <c r="A53" s="17" t="inlineStr">
         <is>
           <t>特性曲線當場畫一次</t>
         </is>
       </c>
-      <c r="B53" s="12" t="n"/>
-      <c r="C53" s="17" t="inlineStr">
+      <c r="B53" s="18" t="n"/>
+      <c r="C53" s="19" t="inlineStr">
         <is>
           <t>四條線要看得出平坦的主動區；不平坦代表還沒離開飽和區</t>
         </is>
@@ -3508,12 +3590,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="Q11:U11"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="Q11:S11"/>
+    <mergeCell ref="L11:N11"/>
     <mergeCell ref="A2:Q2"/>
-    <mergeCell ref="G11:K11"/>
-    <mergeCell ref="L11:P11"/>
     <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="G11:I11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -3521,6 +3603,336 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Table 1（交報告用版面）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>欄位與版面照 App_Lab2.pdf 第 8 頁；數值自動從「實驗一 特性曲線」工作表抓，不要直接在這裡填</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="20">
+        <f>"V_BB = 1.5 V 、 V_BE = "&amp;IF('實驗一 特性曲線'!E$11="","____",TEXT('實驗一 特性曲線'!E$11,"0.000"))&amp;" V 、 "&amp;IF('實驗一 特性曲線'!F$11="","ON/OFF",'實驗一 特性曲線'!F$11)</f>
+        <v/>
+      </c>
+      <c r="B5" s="14" t="n"/>
+      <c r="D5" s="20">
+        <f>"V_BB = 2.0 V 、 V_BE = "&amp;IF('實驗一 特性曲線'!J$11="","____",TEXT('實驗一 特性曲線'!J$11,"0.000"))&amp;" V 、 "&amp;IF('實驗一 特性曲線'!K$11="","ON/OFF",'實驗一 特性曲線'!K$11)</f>
+        <v/>
+      </c>
+      <c r="E5" s="14" t="n"/>
+      <c r="H5" s="21" t="inlineStr">
+        <is>
+          <t>取樣的 V_CC (V)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>V_CE (experimental setting)</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>I_C (measure)  ( = V_C / R_C )</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>V_CE (experimental setting)</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>I_C (measure)  ( = V_C / R_C )</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8">
+        <f>IFERROR(INDEX('實驗一 特性曲線'!$B$13:$B$43,MATCH($H$6,'實驗一 特性曲線'!$A$13:$A$43,0)),"")</f>
+        <v/>
+      </c>
+      <c r="B7" s="8">
+        <f>IFERROR(INDEX('實驗一 特性曲線'!$D$13:$D$43,MATCH($H$6,'實驗一 特性曲線'!$A$13:$A$43,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D7" s="8">
+        <f>IFERROR(INDEX('實驗一 特性曲線'!$G$13:$G$43,MATCH($H$6,'實驗一 特性曲線'!$A$13:$A$43,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E7" s="8">
+        <f>IFERROR(INDEX('實驗一 特性曲線'!$I$13:$I$43,MATCH($H$6,'實驗一 特性曲線'!$A$13:$A$43,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8">
+        <f>IFERROR(INDEX('實驗一 特性曲線'!$B$13:$B$43,MATCH($H$7,'實驗一 特性曲線'!$A$13:$A$43,0)),"")</f>
+        <v/>
+      </c>
+      <c r="B8" s="8">
+        <f>IFERROR(INDEX('實驗一 特性曲線'!$D$13:$D$43,MATCH($H$7,'實驗一 特性曲線'!$A$13:$A$43,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D8" s="8">
+        <f>IFERROR(INDEX('實驗一 特性曲線'!$G$13:$G$43,MATCH($H$7,'實驗一 特性曲線'!$A$13:$A$43,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E8" s="8">
+        <f>IFERROR(INDEX('實驗一 特性曲線'!$I$13:$I$43,MATCH($H$7,'實驗一 特性曲線'!$A$13:$A$43,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8">
+        <f>IFERROR(INDEX('實驗一 特性曲線'!$B$13:$B$43,MATCH($H$8,'實驗一 特性曲線'!$A$13:$A$43,0)),"")</f>
+        <v/>
+      </c>
+      <c r="B9" s="8">
+        <f>IFERROR(INDEX('實驗一 特性曲線'!$D$13:$D$43,MATCH($H$8,'實驗一 特性曲線'!$A$13:$A$43,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D9" s="8">
+        <f>IFERROR(INDEX('實驗一 特性曲線'!$G$13:$G$43,MATCH($H$8,'實驗一 特性曲線'!$A$13:$A$43,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E9" s="8">
+        <f>IFERROR(INDEX('實驗一 特性曲線'!$I$13:$I$43,MATCH($H$8,'實驗一 特性曲線'!$A$13:$A$43,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8">
+        <f>IFERROR(INDEX('實驗一 特性曲線'!$B$13:$B$43,MATCH($H$9,'實驗一 特性曲線'!$A$13:$A$43,0)),"")</f>
+        <v/>
+      </c>
+      <c r="B10" s="8">
+        <f>IFERROR(INDEX('實驗一 特性曲線'!$D$13:$D$43,MATCH($H$9,'實驗一 特性曲線'!$A$13:$A$43,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="8">
+        <f>IFERROR(INDEX('實驗一 特性曲線'!$G$13:$G$43,MATCH($H$9,'實驗一 特性曲線'!$A$13:$A$43,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E10" s="8">
+        <f>IFERROR(INDEX('實驗一 特性曲線'!$I$13:$I$43,MATCH($H$9,'實驗一 特性曲線'!$A$13:$A$43,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8">
+        <f>IFERROR(INDEX('實驗一 特性曲線'!$B$13:$B$43,MATCH($H$10,'實驗一 特性曲線'!$A$13:$A$43,0)),"")</f>
+        <v/>
+      </c>
+      <c r="B11" s="8">
+        <f>IFERROR(INDEX('實驗一 特性曲線'!$D$13:$D$43,MATCH($H$10,'實驗一 特性曲線'!$A$13:$A$43,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D11" s="8">
+        <f>IFERROR(INDEX('實驗一 特性曲線'!$G$13:$G$43,MATCH($H$10,'實驗一 特性曲線'!$A$13:$A$43,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E11" s="8">
+        <f>IFERROR(INDEX('實驗一 特性曲線'!$I$13:$I$43,MATCH($H$10,'實驗一 特性曲線'!$A$13:$A$43,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>↑ 想換成別的 V_CC 就改這五格</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="20">
+        <f>"V_BB = 2.2 V 、 V_BE = "&amp;IF('實驗一 特性曲線'!O$11="","____",TEXT('實驗一 特性曲線'!O$11,"0.000"))&amp;" V 、 "&amp;IF('實驗一 特性曲線'!P$11="","ON/OFF",'實驗一 特性曲線'!P$11)</f>
+        <v/>
+      </c>
+      <c r="B14" s="14" t="n"/>
+      <c r="D14" s="20">
+        <f>"V_BB = 2.4 V 、 V_BE = "&amp;IF('實驗一 特性曲線'!T$11="","____",TEXT('實驗一 特性曲線'!T$11,"0.000"))&amp;" V 、 "&amp;IF('實驗一 特性曲線'!U$11="","ON/OFF",'實驗一 特性曲線'!U$11)</f>
+        <v/>
+      </c>
+      <c r="E14" s="14" t="n"/>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>V_CE (experimental setting)</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>I_C (measure)  ( = V_C / R_C )</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>V_CE (experimental setting)</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>I_C (measure)  ( = V_C / R_C )</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8">
+        <f>IFERROR(INDEX('實驗一 特性曲線'!$L$13:$L$43,MATCH($H$6,'實驗一 特性曲線'!$A$13:$A$43,0)),"")</f>
+        <v/>
+      </c>
+      <c r="B16" s="8">
+        <f>IFERROR(INDEX('實驗一 特性曲線'!$N$13:$N$43,MATCH($H$6,'實驗一 特性曲線'!$A$13:$A$43,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D16" s="8">
+        <f>IFERROR(INDEX('實驗一 特性曲線'!$Q$13:$Q$43,MATCH($H$6,'實驗一 特性曲線'!$A$13:$A$43,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E16" s="8">
+        <f>IFERROR(INDEX('實驗一 特性曲線'!$S$13:$S$43,MATCH($H$6,'實驗一 特性曲線'!$A$13:$A$43,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8">
+        <f>IFERROR(INDEX('實驗一 特性曲線'!$L$13:$L$43,MATCH($H$7,'實驗一 特性曲線'!$A$13:$A$43,0)),"")</f>
+        <v/>
+      </c>
+      <c r="B17" s="8">
+        <f>IFERROR(INDEX('實驗一 特性曲線'!$N$13:$N$43,MATCH($H$7,'實驗一 特性曲線'!$A$13:$A$43,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D17" s="8">
+        <f>IFERROR(INDEX('實驗一 特性曲線'!$Q$13:$Q$43,MATCH($H$7,'實驗一 特性曲線'!$A$13:$A$43,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E17" s="8">
+        <f>IFERROR(INDEX('實驗一 特性曲線'!$S$13:$S$43,MATCH($H$7,'實驗一 特性曲線'!$A$13:$A$43,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8">
+        <f>IFERROR(INDEX('實驗一 特性曲線'!$L$13:$L$43,MATCH($H$8,'實驗一 特性曲線'!$A$13:$A$43,0)),"")</f>
+        <v/>
+      </c>
+      <c r="B18" s="8">
+        <f>IFERROR(INDEX('實驗一 特性曲線'!$N$13:$N$43,MATCH($H$8,'實驗一 特性曲線'!$A$13:$A$43,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D18" s="8">
+        <f>IFERROR(INDEX('實驗一 特性曲線'!$Q$13:$Q$43,MATCH($H$8,'實驗一 特性曲線'!$A$13:$A$43,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E18" s="8">
+        <f>IFERROR(INDEX('實驗一 特性曲線'!$S$13:$S$43,MATCH($H$8,'實驗一 特性曲線'!$A$13:$A$43,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8">
+        <f>IFERROR(INDEX('實驗一 特性曲線'!$L$13:$L$43,MATCH($H$9,'實驗一 特性曲線'!$A$13:$A$43,0)),"")</f>
+        <v/>
+      </c>
+      <c r="B19" s="8">
+        <f>IFERROR(INDEX('實驗一 特性曲線'!$N$13:$N$43,MATCH($H$9,'實驗一 特性曲線'!$A$13:$A$43,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D19" s="8">
+        <f>IFERROR(INDEX('實驗一 特性曲線'!$Q$13:$Q$43,MATCH($H$9,'實驗一 特性曲線'!$A$13:$A$43,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E19" s="8">
+        <f>IFERROR(INDEX('實驗一 特性曲線'!$S$13:$S$43,MATCH($H$9,'實驗一 特性曲線'!$A$13:$A$43,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8">
+        <f>IFERROR(INDEX('實驗一 特性曲線'!$L$13:$L$43,MATCH($H$10,'實驗一 特性曲線'!$A$13:$A$43,0)),"")</f>
+        <v/>
+      </c>
+      <c r="B20" s="8">
+        <f>IFERROR(INDEX('實驗一 特性曲線'!$N$13:$N$43,MATCH($H$10,'實驗一 特性曲線'!$A$13:$A$43,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D20" s="8">
+        <f>IFERROR(INDEX('實驗一 特性曲線'!$Q$13:$Q$43,MATCH($H$10,'實驗一 特性曲線'!$A$13:$A$43,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E20" s="8">
+        <f>IFERROR(INDEX('實驗一 特性曲線'!$S$13:$S$43,MATCH($H$10,'實驗一 特性曲線'!$A$13:$A$43,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>I_C 的單位是 mA（講義表頭寫 A，抄進報告時記得換算或標註單位）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>區塊標題的 V_BE 與 ON/OFF 會跟著「實驗一 特性曲線」各組標題列的黃格自動帶過來。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="A14:B14"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3558,7 +3970,7 @@
           <t>電阻值 (Ω)</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
@@ -3566,7 +3978,7 @@
       <c r="C4" s="11" t="n">
         <v>10000</v>
       </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="D4" s="17" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
@@ -3574,7 +3986,7 @@
       <c r="E4" s="11" t="n">
         <v>4700</v>
       </c>
-      <c r="F4" s="16" t="inlineStr">
+      <c r="F4" s="17" t="inlineStr">
         <is>
           <t>R_C</t>
         </is>
@@ -3621,18 +4033,18 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>R1 兩端壓降 V_R1</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr"/>
+      <c r="D7" s="19" t="inlineStr"/>
       <c r="E7" s="9" t="n">
         <v>14.251</v>
       </c>
@@ -3640,25 +4052,25 @@
         <f>IF(OR(B7="",E7="",E7=0),"",(B7-E7)/E7)</f>
         <v/>
       </c>
-      <c r="G7" s="17" t="inlineStr">
+      <c r="G7" s="19" t="inlineStr">
         <is>
           <t>量 V_BB 對基極</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>R2 兩端壓降 V_R2</t>
         </is>
       </c>
       <c r="B8" s="7" t="n"/>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr"/>
+      <c r="D8" s="19" t="inlineStr"/>
       <c r="E8" s="9" t="n">
         <v>0.749</v>
       </c>
@@ -3666,25 +4078,25 @@
         <f>IF(OR(B8="",E8="",E8=0),"",(B8-E8)/E8)</f>
         <v/>
       </c>
-      <c r="G8" s="17" t="inlineStr">
+      <c r="G8" s="19" t="inlineStr">
         <is>
           <t>等於 V_BE（R2 與 B-E 並聯）</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>R_C 兩端壓降 V_RC</t>
         </is>
       </c>
       <c r="B9" s="7" t="n"/>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C9" s="17" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr"/>
+      <c r="D9" s="19" t="inlineStr"/>
       <c r="E9" s="9" t="n">
         <v>14.946</v>
       </c>
@@ -3692,25 +4104,25 @@
         <f>IF(OR(B9="",E9="",E9=0),"",(B9-E9)/E9)</f>
         <v/>
       </c>
-      <c r="G9" s="17" t="inlineStr">
+      <c r="G9" s="19" t="inlineStr">
         <is>
           <t>量 V_CC 對集極</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>V_CE</t>
         </is>
       </c>
       <c r="B10" s="7" t="n"/>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr"/>
+      <c r="D10" s="19" t="inlineStr"/>
       <c r="E10" s="9" t="n">
         <v>0.054</v>
       </c>
@@ -3718,14 +4130,14 @@
         <f>IF(OR(B10="",E10="",E10=0),"",(B10-E10)/E10)</f>
         <v/>
       </c>
-      <c r="G10" s="17" t="inlineStr">
+      <c r="G10" s="19" t="inlineStr">
         <is>
           <t>集極對射極；深度飽和時只剩幾十 mV</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>I_R1 = V_R1 / R1</t>
         </is>
@@ -3734,12 +4146,12 @@
         <f>IF(B7="","",B7/$C$4*1000)</f>
         <v/>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>mA</t>
         </is>
       </c>
-      <c r="D11" s="17">
+      <c r="D11" s="19">
         <f>IF(B7="","",B7/$C$4*1000)</f>
         <v/>
       </c>
@@ -3750,14 +4162,14 @@
         <f>IF(OR(B11="",E11="",E11=0),"",(B11-E11)/E11)</f>
         <v/>
       </c>
-      <c r="G11" s="17" t="inlineStr">
+      <c r="G11" s="19" t="inlineStr">
         <is>
           <t>流進基極節點的總電流</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="inlineStr">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>I_R2 = V_R2 / R2</t>
         </is>
@@ -3766,12 +4178,12 @@
         <f>IF(B8="","",B8/$E$4*1000)</f>
         <v/>
       </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>mA</t>
         </is>
       </c>
-      <c r="D12" s="17">
+      <c r="D12" s="19">
         <f>IF(B8="","",B8/$E$4*1000)</f>
         <v/>
       </c>
@@ -3782,14 +4194,14 @@
         <f>IF(OR(B12="",E12="",E12=0),"",(B12-E12)/E12)</f>
         <v/>
       </c>
-      <c r="G12" s="17" t="inlineStr">
+      <c r="G12" s="19" t="inlineStr">
         <is>
           <t>被 R2 分掉、沒進基極的那一份</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="16" t="inlineStr">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>I_B = I_R1 − I_R2</t>
         </is>
@@ -3798,12 +4210,12 @@
         <f>IF(OR(B7="",B8=""),"",B11-B12)</f>
         <v/>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C13" s="17" t="inlineStr">
         <is>
           <t>mA</t>
         </is>
       </c>
-      <c r="D13" s="17">
+      <c r="D13" s="19">
         <f>IF(OR(B7="",B8=""),"",B11-B12)</f>
         <v/>
       </c>
@@ -3814,14 +4226,14 @@
         <f>IF(OR(B13="",E13="",E13=0),"",(B13-E13)/E13)</f>
         <v/>
       </c>
-      <c r="G13" s="17" t="inlineStr">
+      <c r="G13" s="19" t="inlineStr">
         <is>
           <t>KCL：講義第 9 頁第 3 步</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="16" t="inlineStr">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>I_C = V_RC / R_C</t>
         </is>
@@ -3830,12 +4242,12 @@
         <f>IF(B9="","",B9/$G$4*1000)</f>
         <v/>
       </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="C14" s="17" t="inlineStr">
         <is>
           <t>mA</t>
         </is>
       </c>
-      <c r="D14" s="17">
+      <c r="D14" s="19">
         <f>IF(B9="","",B9/$G$4*1000)</f>
         <v/>
       </c>
@@ -3846,14 +4258,14 @@
         <f>IF(OR(B14="",E14="",E14=0),"",(B14-E14)/E14)</f>
         <v/>
       </c>
-      <c r="G14" s="17" t="inlineStr">
+      <c r="G14" s="19" t="inlineStr">
         <is>
           <t>不必串電流表就能得到</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="16" t="inlineStr">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>β_calculate = I_C / I_B</t>
         </is>
@@ -3862,12 +4274,12 @@
         <f>IF(OR(B13="",B13=0,B14=""),"",B14/B13)</f>
         <v/>
       </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="C15" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D15" s="17">
+      <c r="D15" s="19">
         <f>IF(OR(B13="",B13=0,B14=""),"",B14/B13)</f>
         <v/>
       </c>
@@ -3878,31 +4290,31 @@
         <f>IF(OR(B15="",E15="",E15=0),"",(B15-E15)/E15)</f>
         <v/>
       </c>
-      <c r="G15" s="17" t="inlineStr">
+      <c r="G15" s="19" t="inlineStr">
         <is>
           <t>這是「強迫 β」，飽和時遠小於真正的 β</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="16" t="inlineStr">
+      <c r="A16" s="17" t="inlineStr">
         <is>
           <t>β_measure（三用電表 hFE 檔）</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="C16" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D16" s="17" t="inlineStr"/>
+      <c r="D16" s="19" t="inlineStr"/>
       <c r="E16" s="9" t="n"/>
       <c r="F16" s="10">
         <f>IF(OR(B16="",E16="",E16=0),"",(B16-E16)/E16)</f>
         <v/>
       </c>
-      <c r="G16" s="17" t="inlineStr">
+      <c r="G16" s="19" t="inlineStr">
         <is>
           <t>把電晶體拔下來插 hFE 座；這才是主動區的 β</t>
         </is>
@@ -3923,56 +4335,56 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>要留的證據</t>
         </is>
       </c>
-      <c r="B21" s="15" t="inlineStr">
+      <c r="B21" s="16" t="inlineStr">
         <is>
           <t>打勾</t>
         </is>
       </c>
-      <c r="C21" s="15" t="inlineStr">
+      <c r="C21" s="16" t="inlineStr">
         <is>
           <t>備註</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="16" t="inlineStr">
+      <c r="A22" s="17" t="inlineStr">
         <is>
           <t>Table 2 五個量都填完</t>
         </is>
       </c>
-      <c r="B22" s="12" t="n"/>
-      <c r="C22" s="17" t="inlineStr">
+      <c r="B22" s="18" t="n"/>
+      <c r="C22" s="19" t="inlineStr">
         <is>
           <t>V_R1、V_R2、V_RC、V_CE、β_measure</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="16" t="inlineStr">
+      <c r="A23" s="17" t="inlineStr">
         <is>
           <t>電晶體 hFE 讀值照片 1 張</t>
         </is>
       </c>
-      <c r="B23" s="12" t="n"/>
-      <c r="C23" s="17" t="inlineStr">
+      <c r="B23" s="18" t="n"/>
+      <c r="C23" s="19" t="inlineStr">
         <is>
           <t>拔下來插 hFE 座量到的 β，結報要對照</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="16" t="inlineStr">
+      <c r="A24" s="17" t="inlineStr">
         <is>
           <t>飽和的證據 1 張</t>
         </is>
       </c>
-      <c r="B24" s="12" t="n"/>
-      <c r="C24" s="17" t="inlineStr">
+      <c r="B24" s="18" t="n"/>
+      <c r="C24" s="19" t="inlineStr">
         <is>
           <t>V_CE 只剩幾十 mV 的電表畫面</t>
         </is>
@@ -3988,7 +4400,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4061,7 +4473,7 @@
       <c r="G5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>V_B（基極對地）</t>
         </is>
@@ -4077,14 +4489,14 @@
         <f>IF(OR(B6="",C6=0),"",(B6-C6)/C6)</f>
         <v/>
       </c>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="F6" s="19" t="inlineStr">
         <is>
           <t>分壓器給的 6 V 附近</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>V_E（射極對地）</t>
         </is>
@@ -4100,14 +4512,14 @@
         <f>IF(OR(B7="",C7=0),"",(B7-C7)/C7)</f>
         <v/>
       </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="F7" s="19" t="inlineStr">
         <is>
           <t>約 V_B − 0.7</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>V_C（集極對地）</t>
         </is>
@@ -4123,14 +4535,14 @@
         <f>IF(OR(B8="",C8=0),"",(B8-C8)/C8)</f>
         <v/>
       </c>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="F8" s="19" t="inlineStr">
         <is>
           <t>R_C1 越大這裡越低</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>V_CE = V_C − V_E</t>
         </is>
@@ -4146,14 +4558,14 @@
         <f>IF(OR(B9="",C9=0),"",(B9-C9)/C9)</f>
         <v/>
       </c>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="F9" s="19" t="inlineStr">
         <is>
           <t>小於 1 V 就代表快飽和，訊號會削波</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>I_C = (V_CC − V_C) / R_C1</t>
         </is>
@@ -4168,8 +4580,8 @@
       <c r="D10" s="9" t="n">
         <v>5.146</v>
       </c>
-      <c r="E10" s="16" t="n"/>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="E10" s="17" t="n"/>
+      <c r="F10" s="19" t="inlineStr">
         <is>
           <t>單位 mA；式子裡的 100 要跟著實際用的 R_C1 改</t>
         </is>
@@ -4220,88 +4632,88 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="16" t="inlineStr">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>RC1 100 Ω、有 C3</t>
         </is>
       </c>
-      <c r="B14" s="18" t="n"/>
-      <c r="C14" s="18" t="n"/>
-      <c r="D14" s="19">
+      <c r="B14" s="22" t="n"/>
+      <c r="C14" s="22" t="n"/>
+      <c r="D14" s="23">
         <f>IF(OR(B14="",B14=0,C14=""),"",C14/B14)</f>
         <v/>
       </c>
-      <c r="E14" s="20" t="n">
+      <c r="E14" s="24" t="n">
         <v>5.54</v>
       </c>
       <c r="F14" s="10">
         <f>IF(OR(D14="",E14=0),"",(D14-E14)/E14)</f>
         <v/>
       </c>
-      <c r="G14" s="12" t="n"/>
+      <c r="G14" s="18" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="16" t="inlineStr">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>RC1 1 kΩ、有 C3</t>
         </is>
       </c>
-      <c r="B15" s="18" t="n"/>
-      <c r="C15" s="18" t="n"/>
-      <c r="D15" s="19">
+      <c r="B15" s="22" t="n"/>
+      <c r="C15" s="22" t="n"/>
+      <c r="D15" s="23">
         <f>IF(OR(B15="",B15=0,C15=""),"",C15/B15)</f>
         <v/>
       </c>
-      <c r="E15" s="20" t="n">
+      <c r="E15" s="24" t="n">
         <v>41.13</v>
       </c>
       <c r="F15" s="10">
         <f>IF(OR(D15="",E15=0),"",(D15-E15)/E15)</f>
         <v/>
       </c>
-      <c r="G15" s="12" t="n"/>
+      <c r="G15" s="18" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="16" t="inlineStr">
+      <c r="A16" s="17" t="inlineStr">
         <is>
           <t>RC1 100 Ω、無 C3</t>
         </is>
       </c>
-      <c r="B16" s="18" t="n"/>
-      <c r="C16" s="18" t="n"/>
-      <c r="D16" s="19">
+      <c r="B16" s="22" t="n"/>
+      <c r="C16" s="22" t="n"/>
+      <c r="D16" s="23">
         <f>IF(OR(B16="",B16=0,C16=""),"",C16/B16)</f>
         <v/>
       </c>
-      <c r="E16" s="20" t="n">
+      <c r="E16" s="24" t="n">
         <v>0.1</v>
       </c>
       <c r="F16" s="10">
         <f>IF(OR(D16="",E16=0),"",(D16-E16)/E16)</f>
         <v/>
       </c>
-      <c r="G16" s="12" t="n"/>
+      <c r="G16" s="18" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="16" t="inlineStr">
+      <c r="A17" s="17" t="inlineStr">
         <is>
           <t>RC1 1 kΩ、無 C3</t>
         </is>
       </c>
-      <c r="B17" s="18" t="n"/>
-      <c r="C17" s="18" t="n"/>
-      <c r="D17" s="19">
+      <c r="B17" s="22" t="n"/>
+      <c r="C17" s="22" t="n"/>
+      <c r="D17" s="23">
         <f>IF(OR(B17="",B17=0,C17=""),"",C17/B17)</f>
         <v/>
       </c>
-      <c r="E17" s="20" t="n">
+      <c r="E17" s="24" t="n">
         <v>0.88</v>
       </c>
       <c r="F17" s="10">
         <f>IF(OR(D17="",E17=0),"",(D17-E17)/E17)</f>
         <v/>
       </c>
-      <c r="G17" s="12" t="n"/>
+      <c r="G17" s="18" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4347,141 +4759,141 @@
       <c r="G21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="16" t="inlineStr">
+      <c r="A22" s="17" t="inlineStr">
         <is>
           <t>R_C1</t>
         </is>
       </c>
-      <c r="B22" s="21" t="inlineStr">
+      <c r="B22" s="12" t="inlineStr">
         <is>
           <t>620 Ω</t>
         </is>
       </c>
-      <c r="C22" s="17" t="inlineStr">
+      <c r="C22" s="19" t="inlineStr">
         <is>
           <t>增益正比於集極端總電阻；620 Ω 剛好把 |A_v| 拉到 20</t>
         </is>
       </c>
-      <c r="D22" s="12" t="n"/>
-      <c r="E22" s="21" t="n"/>
+      <c r="D22" s="18" t="n"/>
+      <c r="E22" s="12" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="16" t="inlineStr">
+      <c r="A23" s="17" t="inlineStr">
         <is>
           <t>R_E1a（不旁路）</t>
         </is>
       </c>
-      <c r="B23" s="21" t="inlineStr">
+      <c r="B23" s="12" t="inlineStr">
         <is>
           <t>22 Ω</t>
         </is>
       </c>
-      <c r="C23" s="17" t="inlineStr">
+      <c r="C23" s="19" t="inlineStr">
         <is>
           <t>留一小段不被旁路，增益改由電阻比決定，對 β 與溫度不敏感</t>
         </is>
       </c>
-      <c r="D23" s="12" t="n"/>
-      <c r="E23" s="21" t="n"/>
+      <c r="D23" s="18" t="n"/>
+      <c r="E23" s="12" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="16" t="inlineStr">
+      <c r="A24" s="17" t="inlineStr">
         <is>
           <t>R_E1b（被旁路）</t>
         </is>
       </c>
-      <c r="B24" s="21" t="inlineStr">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>1 kΩ</t>
         </is>
       </c>
-      <c r="C24" s="17" t="inlineStr">
+      <c r="C24" s="19" t="inlineStr">
         <is>
           <t>直流偏壓照舊由它決定，工作點不動</t>
         </is>
       </c>
-      <c r="D24" s="12" t="n"/>
-      <c r="E24" s="21" t="n"/>
+      <c r="D24" s="18" t="n"/>
+      <c r="E24" s="12" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="16" t="inlineStr">
+      <c r="A25" s="17" t="inlineStr">
         <is>
           <t>C3</t>
         </is>
       </c>
-      <c r="B25" s="21" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>100 µF</t>
         </is>
       </c>
-      <c r="C25" s="17" t="inlineStr">
+      <c r="C25" s="19" t="inlineStr">
         <is>
           <t>10 kHz 時容抗 0.16 Ω，遠小於 R_E1a，才算真的旁路掉</t>
         </is>
       </c>
-      <c r="D25" s="12" t="n"/>
-      <c r="E25" s="21" t="n"/>
+      <c r="D25" s="18" t="n"/>
+      <c r="E25" s="12" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="16" t="inlineStr">
+      <c r="A26" s="17" t="inlineStr">
         <is>
           <t>C1、C2</t>
         </is>
       </c>
-      <c r="B26" s="21" t="inlineStr">
+      <c r="B26" s="12" t="inlineStr">
         <is>
           <t>1 µF</t>
         </is>
       </c>
-      <c r="C26" s="17" t="inlineStr">
+      <c r="C26" s="19" t="inlineStr">
         <is>
           <t>耦合電容維持講義原值即可，截止頻率遠低於 10 kHz</t>
         </is>
       </c>
-      <c r="D26" s="12" t="n"/>
-      <c r="E26" s="21" t="n"/>
+      <c r="D26" s="18" t="n"/>
+      <c r="E26" s="12" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="16" t="inlineStr">
+      <c r="A27" s="17" t="inlineStr">
         <is>
           <t>V_B / V_E / V_C</t>
         </is>
       </c>
-      <c r="B27" s="21" t="inlineStr">
+      <c r="B27" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C27" s="17" t="inlineStr">
+      <c r="C27" s="19" t="inlineStr">
         <is>
           <t>工作點</t>
         </is>
       </c>
-      <c r="D27" s="12" t="n"/>
-      <c r="E27" s="21" t="inlineStr">
+      <c r="D27" s="18" t="n"/>
+      <c r="E27" s="12" t="inlineStr">
         <is>
           <t>5.88 / 5.18 / 8.87 V</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="16" t="inlineStr">
+      <c r="A28" s="17" t="inlineStr">
         <is>
           <t>實測 |A_v|</t>
         </is>
       </c>
-      <c r="B28" s="21" t="inlineStr">
+      <c r="B28" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C28" s="17" t="inlineStr">
+      <c r="C28" s="19" t="inlineStr">
         <is>
           <t>目標 20，±10% 以內都算達標</t>
         </is>
       </c>
-      <c r="D28" s="12" t="n"/>
-      <c r="E28" s="21" t="n">
+      <c r="D28" s="18" t="n"/>
+      <c r="E28" s="12" t="n">
         <v>20.13</v>
       </c>
     </row>
@@ -4500,69 +4912,69 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="15" t="inlineStr">
+      <c r="A32" s="16" t="inlineStr">
         <is>
           <t>要留的證據</t>
         </is>
       </c>
-      <c r="B32" s="15" t="inlineStr">
+      <c r="B32" s="16" t="inlineStr">
         <is>
           <t>打勾</t>
         </is>
       </c>
-      <c r="C32" s="15" t="inlineStr">
+      <c r="C32" s="16" t="inlineStr">
         <is>
           <t>備註</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="16" t="inlineStr">
+      <c r="A33" s="17" t="inlineStr">
         <is>
           <t>示波器雙軌畫面 4 張</t>
         </is>
       </c>
-      <c r="B33" s="12" t="n"/>
-      <c r="C33" s="17" t="inlineStr">
+      <c r="B33" s="18" t="n"/>
+      <c r="C33" s="19" t="inlineStr">
         <is>
           <t>四種組合各一張，CH1／CH2 同時入鏡才看得出反相</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="16" t="inlineStr">
+      <c r="A34" s="17" t="inlineStr">
         <is>
           <t>削波的那張要放大</t>
         </is>
       </c>
-      <c r="B34" s="12" t="n"/>
-      <c r="C34" s="17" t="inlineStr">
+      <c r="B34" s="18" t="n"/>
+      <c r="C34" s="19" t="inlineStr">
         <is>
           <t>R_C1 = 1 kΩ 的輸出，削平的一邊要看得清楚</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="16" t="inlineStr">
+      <c r="A35" s="17" t="inlineStr">
         <is>
           <t>直流工作點電表照片 1 張</t>
         </is>
       </c>
-      <c r="B35" s="12" t="n"/>
-      <c r="C35" s="17" t="inlineStr">
+      <c r="B35" s="18" t="n"/>
+      <c r="C35" s="19" t="inlineStr">
         <is>
           <t>V_B、V_E、V_C 三個讀值</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="16" t="inlineStr">
+      <c r="A36" s="17" t="inlineStr">
         <is>
           <t>Bonus 電路的接線照與波形各 1 張</t>
         </is>
       </c>
-      <c r="B36" s="12" t="n"/>
-      <c r="C36" s="17" t="inlineStr">
+      <c r="B36" s="18" t="n"/>
+      <c r="C36" s="19" t="inlineStr">
         <is>
           <t>元件值改了要拍，結報要對照</t>
         </is>

--- a/simulations/lab2/measured/Lab2-數據記錄.xlsx
+++ b/simulations/lab2/measured/Lab2-數據記錄.xlsx
@@ -1547,7 +1547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U53"/>
+  <dimension ref="A1:U54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1856,7 +1856,7 @@
       <c r="B13" s="7" t="n"/>
       <c r="C13" s="7" t="n"/>
       <c r="D13" s="8">
-        <f>IF(C13="","",C13/$B$4*1000)</f>
+        <f>IF(C13&lt;&gt;"",C13/$B$4*1000,IF(B13&lt;&gt;"",($A13-B13)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="E13" s="9" t="n">
@@ -1868,7 +1868,7 @@
       <c r="G13" s="7" t="n"/>
       <c r="H13" s="7" t="n"/>
       <c r="I13" s="8">
-        <f>IF(H13="","",H13/$B$4*1000)</f>
+        <f>IF(H13&lt;&gt;"",H13/$B$4*1000,IF(G13&lt;&gt;"",($A13-G13)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="J13" s="9" t="n">
@@ -1880,7 +1880,7 @@
       <c r="L13" s="7" t="n"/>
       <c r="M13" s="7" t="n"/>
       <c r="N13" s="8">
-        <f>IF(M13="","",M13/$B$4*1000)</f>
+        <f>IF(M13&lt;&gt;"",M13/$B$4*1000,IF(L13&lt;&gt;"",($A13-L13)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="O13" s="9" t="n">
@@ -1892,7 +1892,7 @@
       <c r="Q13" s="7" t="n"/>
       <c r="R13" s="7" t="n"/>
       <c r="S13" s="8">
-        <f>IF(R13="","",R13/$B$4*1000)</f>
+        <f>IF(R13&lt;&gt;"",R13/$B$4*1000,IF(Q13&lt;&gt;"",($A13-Q13)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="T13" s="9" t="n">
@@ -1909,7 +1909,7 @@
       <c r="B14" s="7" t="n"/>
       <c r="C14" s="7" t="n"/>
       <c r="D14" s="8">
-        <f>IF(C14="","",C14/$B$4*1000)</f>
+        <f>IF(C14&lt;&gt;"",C14/$B$4*1000,IF(B14&lt;&gt;"",($A14-B14)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="E14" s="9" t="n">
@@ -1921,7 +1921,7 @@
       <c r="G14" s="7" t="n"/>
       <c r="H14" s="7" t="n"/>
       <c r="I14" s="8">
-        <f>IF(H14="","",H14/$B$4*1000)</f>
+        <f>IF(H14&lt;&gt;"",H14/$B$4*1000,IF(G14&lt;&gt;"",($A14-G14)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="J14" s="9" t="n">
@@ -1933,7 +1933,7 @@
       <c r="L14" s="7" t="n"/>
       <c r="M14" s="7" t="n"/>
       <c r="N14" s="8">
-        <f>IF(M14="","",M14/$B$4*1000)</f>
+        <f>IF(M14&lt;&gt;"",M14/$B$4*1000,IF(L14&lt;&gt;"",($A14-L14)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="O14" s="9" t="n">
@@ -1945,7 +1945,7 @@
       <c r="Q14" s="7" t="n"/>
       <c r="R14" s="7" t="n"/>
       <c r="S14" s="8">
-        <f>IF(R14="","",R14/$B$4*1000)</f>
+        <f>IF(R14&lt;&gt;"",R14/$B$4*1000,IF(Q14&lt;&gt;"",($A14-Q14)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="T14" s="9" t="n">
@@ -1962,7 +1962,7 @@
       <c r="B15" s="7" t="n"/>
       <c r="C15" s="7" t="n"/>
       <c r="D15" s="8">
-        <f>IF(C15="","",C15/$B$4*1000)</f>
+        <f>IF(C15&lt;&gt;"",C15/$B$4*1000,IF(B15&lt;&gt;"",($A15-B15)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="E15" s="9" t="n">
@@ -1974,7 +1974,7 @@
       <c r="G15" s="7" t="n"/>
       <c r="H15" s="7" t="n"/>
       <c r="I15" s="8">
-        <f>IF(H15="","",H15/$B$4*1000)</f>
+        <f>IF(H15&lt;&gt;"",H15/$B$4*1000,IF(G15&lt;&gt;"",($A15-G15)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="J15" s="9" t="n">
@@ -1986,7 +1986,7 @@
       <c r="L15" s="7" t="n"/>
       <c r="M15" s="7" t="n"/>
       <c r="N15" s="8">
-        <f>IF(M15="","",M15/$B$4*1000)</f>
+        <f>IF(M15&lt;&gt;"",M15/$B$4*1000,IF(L15&lt;&gt;"",($A15-L15)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="O15" s="9" t="n">
@@ -1998,7 +1998,7 @@
       <c r="Q15" s="7" t="n"/>
       <c r="R15" s="7" t="n"/>
       <c r="S15" s="8">
-        <f>IF(R15="","",R15/$B$4*1000)</f>
+        <f>IF(R15&lt;&gt;"",R15/$B$4*1000,IF(Q15&lt;&gt;"",($A15-Q15)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="T15" s="9" t="n">
@@ -2015,7 +2015,7 @@
       <c r="B16" s="7" t="n"/>
       <c r="C16" s="7" t="n"/>
       <c r="D16" s="8">
-        <f>IF(C16="","",C16/$B$4*1000)</f>
+        <f>IF(C16&lt;&gt;"",C16/$B$4*1000,IF(B16&lt;&gt;"",($A16-B16)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="E16" s="9" t="n">
@@ -2027,7 +2027,7 @@
       <c r="G16" s="7" t="n"/>
       <c r="H16" s="7" t="n"/>
       <c r="I16" s="8">
-        <f>IF(H16="","",H16/$B$4*1000)</f>
+        <f>IF(H16&lt;&gt;"",H16/$B$4*1000,IF(G16&lt;&gt;"",($A16-G16)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="J16" s="9" t="n">
@@ -2039,7 +2039,7 @@
       <c r="L16" s="7" t="n"/>
       <c r="M16" s="7" t="n"/>
       <c r="N16" s="8">
-        <f>IF(M16="","",M16/$B$4*1000)</f>
+        <f>IF(M16&lt;&gt;"",M16/$B$4*1000,IF(L16&lt;&gt;"",($A16-L16)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="O16" s="9" t="n">
@@ -2051,7 +2051,7 @@
       <c r="Q16" s="7" t="n"/>
       <c r="R16" s="7" t="n"/>
       <c r="S16" s="8">
-        <f>IF(R16="","",R16/$B$4*1000)</f>
+        <f>IF(R16&lt;&gt;"",R16/$B$4*1000,IF(Q16&lt;&gt;"",($A16-Q16)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="T16" s="9" t="n">
@@ -2068,7 +2068,7 @@
       <c r="B17" s="7" t="n"/>
       <c r="C17" s="7" t="n"/>
       <c r="D17" s="8">
-        <f>IF(C17="","",C17/$B$4*1000)</f>
+        <f>IF(C17&lt;&gt;"",C17/$B$4*1000,IF(B17&lt;&gt;"",($A17-B17)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="E17" s="9" t="n">
@@ -2080,7 +2080,7 @@
       <c r="G17" s="7" t="n"/>
       <c r="H17" s="7" t="n"/>
       <c r="I17" s="8">
-        <f>IF(H17="","",H17/$B$4*1000)</f>
+        <f>IF(H17&lt;&gt;"",H17/$B$4*1000,IF(G17&lt;&gt;"",($A17-G17)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="J17" s="9" t="n">
@@ -2092,7 +2092,7 @@
       <c r="L17" s="7" t="n"/>
       <c r="M17" s="7" t="n"/>
       <c r="N17" s="8">
-        <f>IF(M17="","",M17/$B$4*1000)</f>
+        <f>IF(M17&lt;&gt;"",M17/$B$4*1000,IF(L17&lt;&gt;"",($A17-L17)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="O17" s="9" t="n">
@@ -2104,7 +2104,7 @@
       <c r="Q17" s="7" t="n"/>
       <c r="R17" s="7" t="n"/>
       <c r="S17" s="8">
-        <f>IF(R17="","",R17/$B$4*1000)</f>
+        <f>IF(R17&lt;&gt;"",R17/$B$4*1000,IF(Q17&lt;&gt;"",($A17-Q17)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="T17" s="9" t="n">
@@ -2121,7 +2121,7 @@
       <c r="B18" s="7" t="n"/>
       <c r="C18" s="7" t="n"/>
       <c r="D18" s="8">
-        <f>IF(C18="","",C18/$B$4*1000)</f>
+        <f>IF(C18&lt;&gt;"",C18/$B$4*1000,IF(B18&lt;&gt;"",($A18-B18)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="E18" s="9" t="n">
@@ -2133,7 +2133,7 @@
       <c r="G18" s="7" t="n"/>
       <c r="H18" s="7" t="n"/>
       <c r="I18" s="8">
-        <f>IF(H18="","",H18/$B$4*1000)</f>
+        <f>IF(H18&lt;&gt;"",H18/$B$4*1000,IF(G18&lt;&gt;"",($A18-G18)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="J18" s="9" t="n">
@@ -2145,7 +2145,7 @@
       <c r="L18" s="7" t="n"/>
       <c r="M18" s="7" t="n"/>
       <c r="N18" s="8">
-        <f>IF(M18="","",M18/$B$4*1000)</f>
+        <f>IF(M18&lt;&gt;"",M18/$B$4*1000,IF(L18&lt;&gt;"",($A18-L18)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="O18" s="9" t="n">
@@ -2157,7 +2157,7 @@
       <c r="Q18" s="7" t="n"/>
       <c r="R18" s="7" t="n"/>
       <c r="S18" s="8">
-        <f>IF(R18="","",R18/$B$4*1000)</f>
+        <f>IF(R18&lt;&gt;"",R18/$B$4*1000,IF(Q18&lt;&gt;"",($A18-Q18)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="T18" s="9" t="n">
@@ -2174,7 +2174,7 @@
       <c r="B19" s="7" t="n"/>
       <c r="C19" s="7" t="n"/>
       <c r="D19" s="8">
-        <f>IF(C19="","",C19/$B$4*1000)</f>
+        <f>IF(C19&lt;&gt;"",C19/$B$4*1000,IF(B19&lt;&gt;"",($A19-B19)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="E19" s="9" t="n">
@@ -2186,7 +2186,7 @@
       <c r="G19" s="7" t="n"/>
       <c r="H19" s="7" t="n"/>
       <c r="I19" s="8">
-        <f>IF(H19="","",H19/$B$4*1000)</f>
+        <f>IF(H19&lt;&gt;"",H19/$B$4*1000,IF(G19&lt;&gt;"",($A19-G19)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="J19" s="9" t="n">
@@ -2198,7 +2198,7 @@
       <c r="L19" s="7" t="n"/>
       <c r="M19" s="7" t="n"/>
       <c r="N19" s="8">
-        <f>IF(M19="","",M19/$B$4*1000)</f>
+        <f>IF(M19&lt;&gt;"",M19/$B$4*1000,IF(L19&lt;&gt;"",($A19-L19)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="O19" s="9" t="n">
@@ -2210,7 +2210,7 @@
       <c r="Q19" s="7" t="n"/>
       <c r="R19" s="7" t="n"/>
       <c r="S19" s="8">
-        <f>IF(R19="","",R19/$B$4*1000)</f>
+        <f>IF(R19&lt;&gt;"",R19/$B$4*1000,IF(Q19&lt;&gt;"",($A19-Q19)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="T19" s="9" t="n">
@@ -2227,7 +2227,7 @@
       <c r="B20" s="7" t="n"/>
       <c r="C20" s="7" t="n"/>
       <c r="D20" s="8">
-        <f>IF(C20="","",C20/$B$4*1000)</f>
+        <f>IF(C20&lt;&gt;"",C20/$B$4*1000,IF(B20&lt;&gt;"",($A20-B20)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="E20" s="9" t="n">
@@ -2239,7 +2239,7 @@
       <c r="G20" s="7" t="n"/>
       <c r="H20" s="7" t="n"/>
       <c r="I20" s="8">
-        <f>IF(H20="","",H20/$B$4*1000)</f>
+        <f>IF(H20&lt;&gt;"",H20/$B$4*1000,IF(G20&lt;&gt;"",($A20-G20)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="J20" s="9" t="n">
@@ -2251,7 +2251,7 @@
       <c r="L20" s="7" t="n"/>
       <c r="M20" s="7" t="n"/>
       <c r="N20" s="8">
-        <f>IF(M20="","",M20/$B$4*1000)</f>
+        <f>IF(M20&lt;&gt;"",M20/$B$4*1000,IF(L20&lt;&gt;"",($A20-L20)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="O20" s="9" t="n">
@@ -2263,7 +2263,7 @@
       <c r="Q20" s="7" t="n"/>
       <c r="R20" s="7" t="n"/>
       <c r="S20" s="8">
-        <f>IF(R20="","",R20/$B$4*1000)</f>
+        <f>IF(R20&lt;&gt;"",R20/$B$4*1000,IF(Q20&lt;&gt;"",($A20-Q20)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="T20" s="9" t="n">
@@ -2280,7 +2280,7 @@
       <c r="B21" s="7" t="n"/>
       <c r="C21" s="7" t="n"/>
       <c r="D21" s="8">
-        <f>IF(C21="","",C21/$B$4*1000)</f>
+        <f>IF(C21&lt;&gt;"",C21/$B$4*1000,IF(B21&lt;&gt;"",($A21-B21)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="E21" s="9" t="n">
@@ -2292,7 +2292,7 @@
       <c r="G21" s="7" t="n"/>
       <c r="H21" s="7" t="n"/>
       <c r="I21" s="8">
-        <f>IF(H21="","",H21/$B$4*1000)</f>
+        <f>IF(H21&lt;&gt;"",H21/$B$4*1000,IF(G21&lt;&gt;"",($A21-G21)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="J21" s="9" t="n">
@@ -2304,7 +2304,7 @@
       <c r="L21" s="7" t="n"/>
       <c r="M21" s="7" t="n"/>
       <c r="N21" s="8">
-        <f>IF(M21="","",M21/$B$4*1000)</f>
+        <f>IF(M21&lt;&gt;"",M21/$B$4*1000,IF(L21&lt;&gt;"",($A21-L21)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="O21" s="9" t="n">
@@ -2316,7 +2316,7 @@
       <c r="Q21" s="7" t="n"/>
       <c r="R21" s="7" t="n"/>
       <c r="S21" s="8">
-        <f>IF(R21="","",R21/$B$4*1000)</f>
+        <f>IF(R21&lt;&gt;"",R21/$B$4*1000,IF(Q21&lt;&gt;"",($A21-Q21)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="T21" s="9" t="n">
@@ -2333,7 +2333,7 @@
       <c r="B22" s="7" t="n"/>
       <c r="C22" s="7" t="n"/>
       <c r="D22" s="8">
-        <f>IF(C22="","",C22/$B$4*1000)</f>
+        <f>IF(C22&lt;&gt;"",C22/$B$4*1000,IF(B22&lt;&gt;"",($A22-B22)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="E22" s="9" t="n">
@@ -2345,7 +2345,7 @@
       <c r="G22" s="7" t="n"/>
       <c r="H22" s="7" t="n"/>
       <c r="I22" s="8">
-        <f>IF(H22="","",H22/$B$4*1000)</f>
+        <f>IF(H22&lt;&gt;"",H22/$B$4*1000,IF(G22&lt;&gt;"",($A22-G22)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="J22" s="9" t="n">
@@ -2357,7 +2357,7 @@
       <c r="L22" s="7" t="n"/>
       <c r="M22" s="7" t="n"/>
       <c r="N22" s="8">
-        <f>IF(M22="","",M22/$B$4*1000)</f>
+        <f>IF(M22&lt;&gt;"",M22/$B$4*1000,IF(L22&lt;&gt;"",($A22-L22)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="O22" s="9" t="n">
@@ -2369,7 +2369,7 @@
       <c r="Q22" s="7" t="n"/>
       <c r="R22" s="7" t="n"/>
       <c r="S22" s="8">
-        <f>IF(R22="","",R22/$B$4*1000)</f>
+        <f>IF(R22&lt;&gt;"",R22/$B$4*1000,IF(Q22&lt;&gt;"",($A22-Q22)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="T22" s="9" t="n">
@@ -2386,7 +2386,7 @@
       <c r="B23" s="7" t="n"/>
       <c r="C23" s="7" t="n"/>
       <c r="D23" s="8">
-        <f>IF(C23="","",C23/$B$4*1000)</f>
+        <f>IF(C23&lt;&gt;"",C23/$B$4*1000,IF(B23&lt;&gt;"",($A23-B23)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="E23" s="9" t="n">
@@ -2398,7 +2398,7 @@
       <c r="G23" s="7" t="n"/>
       <c r="H23" s="7" t="n"/>
       <c r="I23" s="8">
-        <f>IF(H23="","",H23/$B$4*1000)</f>
+        <f>IF(H23&lt;&gt;"",H23/$B$4*1000,IF(G23&lt;&gt;"",($A23-G23)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="J23" s="9" t="n">
@@ -2410,7 +2410,7 @@
       <c r="L23" s="7" t="n"/>
       <c r="M23" s="7" t="n"/>
       <c r="N23" s="8">
-        <f>IF(M23="","",M23/$B$4*1000)</f>
+        <f>IF(M23&lt;&gt;"",M23/$B$4*1000,IF(L23&lt;&gt;"",($A23-L23)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="O23" s="9" t="n">
@@ -2422,7 +2422,7 @@
       <c r="Q23" s="7" t="n"/>
       <c r="R23" s="7" t="n"/>
       <c r="S23" s="8">
-        <f>IF(R23="","",R23/$B$4*1000)</f>
+        <f>IF(R23&lt;&gt;"",R23/$B$4*1000,IF(Q23&lt;&gt;"",($A23-Q23)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="T23" s="9" t="n">
@@ -2439,7 +2439,7 @@
       <c r="B24" s="7" t="n"/>
       <c r="C24" s="7" t="n"/>
       <c r="D24" s="8">
-        <f>IF(C24="","",C24/$B$4*1000)</f>
+        <f>IF(C24&lt;&gt;"",C24/$B$4*1000,IF(B24&lt;&gt;"",($A24-B24)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="E24" s="9" t="n">
@@ -2451,7 +2451,7 @@
       <c r="G24" s="7" t="n"/>
       <c r="H24" s="7" t="n"/>
       <c r="I24" s="8">
-        <f>IF(H24="","",H24/$B$4*1000)</f>
+        <f>IF(H24&lt;&gt;"",H24/$B$4*1000,IF(G24&lt;&gt;"",($A24-G24)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="J24" s="9" t="n">
@@ -2463,7 +2463,7 @@
       <c r="L24" s="7" t="n"/>
       <c r="M24" s="7" t="n"/>
       <c r="N24" s="8">
-        <f>IF(M24="","",M24/$B$4*1000)</f>
+        <f>IF(M24&lt;&gt;"",M24/$B$4*1000,IF(L24&lt;&gt;"",($A24-L24)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="O24" s="9" t="n">
@@ -2475,7 +2475,7 @@
       <c r="Q24" s="7" t="n"/>
       <c r="R24" s="7" t="n"/>
       <c r="S24" s="8">
-        <f>IF(R24="","",R24/$B$4*1000)</f>
+        <f>IF(R24&lt;&gt;"",R24/$B$4*1000,IF(Q24&lt;&gt;"",($A24-Q24)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="T24" s="9" t="n">
@@ -2492,7 +2492,7 @@
       <c r="B25" s="7" t="n"/>
       <c r="C25" s="7" t="n"/>
       <c r="D25" s="8">
-        <f>IF(C25="","",C25/$B$4*1000)</f>
+        <f>IF(C25&lt;&gt;"",C25/$B$4*1000,IF(B25&lt;&gt;"",($A25-B25)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="E25" s="9" t="n">
@@ -2504,7 +2504,7 @@
       <c r="G25" s="7" t="n"/>
       <c r="H25" s="7" t="n"/>
       <c r="I25" s="8">
-        <f>IF(H25="","",H25/$B$4*1000)</f>
+        <f>IF(H25&lt;&gt;"",H25/$B$4*1000,IF(G25&lt;&gt;"",($A25-G25)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="J25" s="9" t="n">
@@ -2516,7 +2516,7 @@
       <c r="L25" s="7" t="n"/>
       <c r="M25" s="7" t="n"/>
       <c r="N25" s="8">
-        <f>IF(M25="","",M25/$B$4*1000)</f>
+        <f>IF(M25&lt;&gt;"",M25/$B$4*1000,IF(L25&lt;&gt;"",($A25-L25)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="O25" s="9" t="n">
@@ -2528,7 +2528,7 @@
       <c r="Q25" s="7" t="n"/>
       <c r="R25" s="7" t="n"/>
       <c r="S25" s="8">
-        <f>IF(R25="","",R25/$B$4*1000)</f>
+        <f>IF(R25&lt;&gt;"",R25/$B$4*1000,IF(Q25&lt;&gt;"",($A25-Q25)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="T25" s="9" t="n">
@@ -2545,7 +2545,7 @@
       <c r="B26" s="7" t="n"/>
       <c r="C26" s="7" t="n"/>
       <c r="D26" s="8">
-        <f>IF(C26="","",C26/$B$4*1000)</f>
+        <f>IF(C26&lt;&gt;"",C26/$B$4*1000,IF(B26&lt;&gt;"",($A26-B26)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="E26" s="9" t="n">
@@ -2557,7 +2557,7 @@
       <c r="G26" s="7" t="n"/>
       <c r="H26" s="7" t="n"/>
       <c r="I26" s="8">
-        <f>IF(H26="","",H26/$B$4*1000)</f>
+        <f>IF(H26&lt;&gt;"",H26/$B$4*1000,IF(G26&lt;&gt;"",($A26-G26)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="J26" s="9" t="n">
@@ -2569,7 +2569,7 @@
       <c r="L26" s="7" t="n"/>
       <c r="M26" s="7" t="n"/>
       <c r="N26" s="8">
-        <f>IF(M26="","",M26/$B$4*1000)</f>
+        <f>IF(M26&lt;&gt;"",M26/$B$4*1000,IF(L26&lt;&gt;"",($A26-L26)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="O26" s="9" t="n">
@@ -2581,7 +2581,7 @@
       <c r="Q26" s="7" t="n"/>
       <c r="R26" s="7" t="n"/>
       <c r="S26" s="8">
-        <f>IF(R26="","",R26/$B$4*1000)</f>
+        <f>IF(R26&lt;&gt;"",R26/$B$4*1000,IF(Q26&lt;&gt;"",($A26-Q26)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="T26" s="9" t="n">
@@ -2598,7 +2598,7 @@
       <c r="B27" s="7" t="n"/>
       <c r="C27" s="7" t="n"/>
       <c r="D27" s="8">
-        <f>IF(C27="","",C27/$B$4*1000)</f>
+        <f>IF(C27&lt;&gt;"",C27/$B$4*1000,IF(B27&lt;&gt;"",($A27-B27)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="E27" s="9" t="n">
@@ -2610,7 +2610,7 @@
       <c r="G27" s="7" t="n"/>
       <c r="H27" s="7" t="n"/>
       <c r="I27" s="8">
-        <f>IF(H27="","",H27/$B$4*1000)</f>
+        <f>IF(H27&lt;&gt;"",H27/$B$4*1000,IF(G27&lt;&gt;"",($A27-G27)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="J27" s="9" t="n">
@@ -2622,7 +2622,7 @@
       <c r="L27" s="7" t="n"/>
       <c r="M27" s="7" t="n"/>
       <c r="N27" s="8">
-        <f>IF(M27="","",M27/$B$4*1000)</f>
+        <f>IF(M27&lt;&gt;"",M27/$B$4*1000,IF(L27&lt;&gt;"",($A27-L27)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="O27" s="9" t="n">
@@ -2634,7 +2634,7 @@
       <c r="Q27" s="7" t="n"/>
       <c r="R27" s="7" t="n"/>
       <c r="S27" s="8">
-        <f>IF(R27="","",R27/$B$4*1000)</f>
+        <f>IF(R27&lt;&gt;"",R27/$B$4*1000,IF(Q27&lt;&gt;"",($A27-Q27)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="T27" s="9" t="n">
@@ -2651,7 +2651,7 @@
       <c r="B28" s="7" t="n"/>
       <c r="C28" s="7" t="n"/>
       <c r="D28" s="8">
-        <f>IF(C28="","",C28/$B$4*1000)</f>
+        <f>IF(C28&lt;&gt;"",C28/$B$4*1000,IF(B28&lt;&gt;"",($A28-B28)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="E28" s="9" t="n">
@@ -2663,7 +2663,7 @@
       <c r="G28" s="7" t="n"/>
       <c r="H28" s="7" t="n"/>
       <c r="I28" s="8">
-        <f>IF(H28="","",H28/$B$4*1000)</f>
+        <f>IF(H28&lt;&gt;"",H28/$B$4*1000,IF(G28&lt;&gt;"",($A28-G28)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="J28" s="9" t="n">
@@ -2675,7 +2675,7 @@
       <c r="L28" s="7" t="n"/>
       <c r="M28" s="7" t="n"/>
       <c r="N28" s="8">
-        <f>IF(M28="","",M28/$B$4*1000)</f>
+        <f>IF(M28&lt;&gt;"",M28/$B$4*1000,IF(L28&lt;&gt;"",($A28-L28)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="O28" s="9" t="n">
@@ -2687,7 +2687,7 @@
       <c r="Q28" s="7" t="n"/>
       <c r="R28" s="7" t="n"/>
       <c r="S28" s="8">
-        <f>IF(R28="","",R28/$B$4*1000)</f>
+        <f>IF(R28&lt;&gt;"",R28/$B$4*1000,IF(Q28&lt;&gt;"",($A28-Q28)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="T28" s="9" t="n">
@@ -2704,7 +2704,7 @@
       <c r="B29" s="7" t="n"/>
       <c r="C29" s="7" t="n"/>
       <c r="D29" s="8">
-        <f>IF(C29="","",C29/$B$4*1000)</f>
+        <f>IF(C29&lt;&gt;"",C29/$B$4*1000,IF(B29&lt;&gt;"",($A29-B29)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="E29" s="9" t="n">
@@ -2716,7 +2716,7 @@
       <c r="G29" s="7" t="n"/>
       <c r="H29" s="7" t="n"/>
       <c r="I29" s="8">
-        <f>IF(H29="","",H29/$B$4*1000)</f>
+        <f>IF(H29&lt;&gt;"",H29/$B$4*1000,IF(G29&lt;&gt;"",($A29-G29)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="J29" s="9" t="n">
@@ -2728,7 +2728,7 @@
       <c r="L29" s="7" t="n"/>
       <c r="M29" s="7" t="n"/>
       <c r="N29" s="8">
-        <f>IF(M29="","",M29/$B$4*1000)</f>
+        <f>IF(M29&lt;&gt;"",M29/$B$4*1000,IF(L29&lt;&gt;"",($A29-L29)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="O29" s="9" t="n">
@@ -2740,7 +2740,7 @@
       <c r="Q29" s="7" t="n"/>
       <c r="R29" s="7" t="n"/>
       <c r="S29" s="8">
-        <f>IF(R29="","",R29/$B$4*1000)</f>
+        <f>IF(R29&lt;&gt;"",R29/$B$4*1000,IF(Q29&lt;&gt;"",($A29-Q29)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="T29" s="9" t="n">
@@ -2757,7 +2757,7 @@
       <c r="B30" s="7" t="n"/>
       <c r="C30" s="7" t="n"/>
       <c r="D30" s="8">
-        <f>IF(C30="","",C30/$B$4*1000)</f>
+        <f>IF(C30&lt;&gt;"",C30/$B$4*1000,IF(B30&lt;&gt;"",($A30-B30)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="E30" s="9" t="n">
@@ -2769,7 +2769,7 @@
       <c r="G30" s="7" t="n"/>
       <c r="H30" s="7" t="n"/>
       <c r="I30" s="8">
-        <f>IF(H30="","",H30/$B$4*1000)</f>
+        <f>IF(H30&lt;&gt;"",H30/$B$4*1000,IF(G30&lt;&gt;"",($A30-G30)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="J30" s="9" t="n">
@@ -2781,7 +2781,7 @@
       <c r="L30" s="7" t="n"/>
       <c r="M30" s="7" t="n"/>
       <c r="N30" s="8">
-        <f>IF(M30="","",M30/$B$4*1000)</f>
+        <f>IF(M30&lt;&gt;"",M30/$B$4*1000,IF(L30&lt;&gt;"",($A30-L30)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="O30" s="9" t="n">
@@ -2793,7 +2793,7 @@
       <c r="Q30" s="7" t="n"/>
       <c r="R30" s="7" t="n"/>
       <c r="S30" s="8">
-        <f>IF(R30="","",R30/$B$4*1000)</f>
+        <f>IF(R30&lt;&gt;"",R30/$B$4*1000,IF(Q30&lt;&gt;"",($A30-Q30)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="T30" s="9" t="n">
@@ -2810,7 +2810,7 @@
       <c r="B31" s="7" t="n"/>
       <c r="C31" s="7" t="n"/>
       <c r="D31" s="8">
-        <f>IF(C31="","",C31/$B$4*1000)</f>
+        <f>IF(C31&lt;&gt;"",C31/$B$4*1000,IF(B31&lt;&gt;"",($A31-B31)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="E31" s="9" t="n">
@@ -2822,7 +2822,7 @@
       <c r="G31" s="7" t="n"/>
       <c r="H31" s="7" t="n"/>
       <c r="I31" s="8">
-        <f>IF(H31="","",H31/$B$4*1000)</f>
+        <f>IF(H31&lt;&gt;"",H31/$B$4*1000,IF(G31&lt;&gt;"",($A31-G31)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="J31" s="9" t="n">
@@ -2834,7 +2834,7 @@
       <c r="L31" s="7" t="n"/>
       <c r="M31" s="7" t="n"/>
       <c r="N31" s="8">
-        <f>IF(M31="","",M31/$B$4*1000)</f>
+        <f>IF(M31&lt;&gt;"",M31/$B$4*1000,IF(L31&lt;&gt;"",($A31-L31)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="O31" s="9" t="n">
@@ -2846,7 +2846,7 @@
       <c r="Q31" s="7" t="n"/>
       <c r="R31" s="7" t="n"/>
       <c r="S31" s="8">
-        <f>IF(R31="","",R31/$B$4*1000)</f>
+        <f>IF(R31&lt;&gt;"",R31/$B$4*1000,IF(Q31&lt;&gt;"",($A31-Q31)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="T31" s="9" t="n">
@@ -2863,7 +2863,7 @@
       <c r="B32" s="7" t="n"/>
       <c r="C32" s="7" t="n"/>
       <c r="D32" s="8">
-        <f>IF(C32="","",C32/$B$4*1000)</f>
+        <f>IF(C32&lt;&gt;"",C32/$B$4*1000,IF(B32&lt;&gt;"",($A32-B32)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="E32" s="9" t="n">
@@ -2875,7 +2875,7 @@
       <c r="G32" s="7" t="n"/>
       <c r="H32" s="7" t="n"/>
       <c r="I32" s="8">
-        <f>IF(H32="","",H32/$B$4*1000)</f>
+        <f>IF(H32&lt;&gt;"",H32/$B$4*1000,IF(G32&lt;&gt;"",($A32-G32)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="J32" s="9" t="n">
@@ -2887,7 +2887,7 @@
       <c r="L32" s="7" t="n"/>
       <c r="M32" s="7" t="n"/>
       <c r="N32" s="8">
-        <f>IF(M32="","",M32/$B$4*1000)</f>
+        <f>IF(M32&lt;&gt;"",M32/$B$4*1000,IF(L32&lt;&gt;"",($A32-L32)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="O32" s="9" t="n">
@@ -2899,7 +2899,7 @@
       <c r="Q32" s="7" t="n"/>
       <c r="R32" s="7" t="n"/>
       <c r="S32" s="8">
-        <f>IF(R32="","",R32/$B$4*1000)</f>
+        <f>IF(R32&lt;&gt;"",R32/$B$4*1000,IF(Q32&lt;&gt;"",($A32-Q32)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="T32" s="9" t="n">
@@ -2916,7 +2916,7 @@
       <c r="B33" s="7" t="n"/>
       <c r="C33" s="7" t="n"/>
       <c r="D33" s="8">
-        <f>IF(C33="","",C33/$B$4*1000)</f>
+        <f>IF(C33&lt;&gt;"",C33/$B$4*1000,IF(B33&lt;&gt;"",($A33-B33)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="E33" s="9" t="n">
@@ -2928,7 +2928,7 @@
       <c r="G33" s="7" t="n"/>
       <c r="H33" s="7" t="n"/>
       <c r="I33" s="8">
-        <f>IF(H33="","",H33/$B$4*1000)</f>
+        <f>IF(H33&lt;&gt;"",H33/$B$4*1000,IF(G33&lt;&gt;"",($A33-G33)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="J33" s="9" t="n">
@@ -2940,7 +2940,7 @@
       <c r="L33" s="7" t="n"/>
       <c r="M33" s="7" t="n"/>
       <c r="N33" s="8">
-        <f>IF(M33="","",M33/$B$4*1000)</f>
+        <f>IF(M33&lt;&gt;"",M33/$B$4*1000,IF(L33&lt;&gt;"",($A33-L33)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="O33" s="9" t="n">
@@ -2952,7 +2952,7 @@
       <c r="Q33" s="7" t="n"/>
       <c r="R33" s="7" t="n"/>
       <c r="S33" s="8">
-        <f>IF(R33="","",R33/$B$4*1000)</f>
+        <f>IF(R33&lt;&gt;"",R33/$B$4*1000,IF(Q33&lt;&gt;"",($A33-Q33)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="T33" s="9" t="n">
@@ -2969,7 +2969,7 @@
       <c r="B34" s="7" t="n"/>
       <c r="C34" s="7" t="n"/>
       <c r="D34" s="8">
-        <f>IF(C34="","",C34/$B$4*1000)</f>
+        <f>IF(C34&lt;&gt;"",C34/$B$4*1000,IF(B34&lt;&gt;"",($A34-B34)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="E34" s="9" t="n">
@@ -2981,7 +2981,7 @@
       <c r="G34" s="7" t="n"/>
       <c r="H34" s="7" t="n"/>
       <c r="I34" s="8">
-        <f>IF(H34="","",H34/$B$4*1000)</f>
+        <f>IF(H34&lt;&gt;"",H34/$B$4*1000,IF(G34&lt;&gt;"",($A34-G34)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="J34" s="9" t="n">
@@ -2993,7 +2993,7 @@
       <c r="L34" s="7" t="n"/>
       <c r="M34" s="7" t="n"/>
       <c r="N34" s="8">
-        <f>IF(M34="","",M34/$B$4*1000)</f>
+        <f>IF(M34&lt;&gt;"",M34/$B$4*1000,IF(L34&lt;&gt;"",($A34-L34)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="O34" s="9" t="n">
@@ -3005,7 +3005,7 @@
       <c r="Q34" s="7" t="n"/>
       <c r="R34" s="7" t="n"/>
       <c r="S34" s="8">
-        <f>IF(R34="","",R34/$B$4*1000)</f>
+        <f>IF(R34&lt;&gt;"",R34/$B$4*1000,IF(Q34&lt;&gt;"",($A34-Q34)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="T34" s="9" t="n">
@@ -3022,7 +3022,7 @@
       <c r="B35" s="7" t="n"/>
       <c r="C35" s="7" t="n"/>
       <c r="D35" s="8">
-        <f>IF(C35="","",C35/$B$4*1000)</f>
+        <f>IF(C35&lt;&gt;"",C35/$B$4*1000,IF(B35&lt;&gt;"",($A35-B35)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="E35" s="9" t="n">
@@ -3034,7 +3034,7 @@
       <c r="G35" s="7" t="n"/>
       <c r="H35" s="7" t="n"/>
       <c r="I35" s="8">
-        <f>IF(H35="","",H35/$B$4*1000)</f>
+        <f>IF(H35&lt;&gt;"",H35/$B$4*1000,IF(G35&lt;&gt;"",($A35-G35)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="J35" s="9" t="n">
@@ -3046,7 +3046,7 @@
       <c r="L35" s="7" t="n"/>
       <c r="M35" s="7" t="n"/>
       <c r="N35" s="8">
-        <f>IF(M35="","",M35/$B$4*1000)</f>
+        <f>IF(M35&lt;&gt;"",M35/$B$4*1000,IF(L35&lt;&gt;"",($A35-L35)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="O35" s="9" t="n">
@@ -3058,7 +3058,7 @@
       <c r="Q35" s="7" t="n"/>
       <c r="R35" s="7" t="n"/>
       <c r="S35" s="8">
-        <f>IF(R35="","",R35/$B$4*1000)</f>
+        <f>IF(R35&lt;&gt;"",R35/$B$4*1000,IF(Q35&lt;&gt;"",($A35-Q35)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="T35" s="9" t="n">
@@ -3075,7 +3075,7 @@
       <c r="B36" s="7" t="n"/>
       <c r="C36" s="7" t="n"/>
       <c r="D36" s="8">
-        <f>IF(C36="","",C36/$B$4*1000)</f>
+        <f>IF(C36&lt;&gt;"",C36/$B$4*1000,IF(B36&lt;&gt;"",($A36-B36)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="E36" s="9" t="n">
@@ -3087,7 +3087,7 @@
       <c r="G36" s="7" t="n"/>
       <c r="H36" s="7" t="n"/>
       <c r="I36" s="8">
-        <f>IF(H36="","",H36/$B$4*1000)</f>
+        <f>IF(H36&lt;&gt;"",H36/$B$4*1000,IF(G36&lt;&gt;"",($A36-G36)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="J36" s="9" t="n">
@@ -3099,7 +3099,7 @@
       <c r="L36" s="7" t="n"/>
       <c r="M36" s="7" t="n"/>
       <c r="N36" s="8">
-        <f>IF(M36="","",M36/$B$4*1000)</f>
+        <f>IF(M36&lt;&gt;"",M36/$B$4*1000,IF(L36&lt;&gt;"",($A36-L36)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="O36" s="9" t="n">
@@ -3111,7 +3111,7 @@
       <c r="Q36" s="7" t="n"/>
       <c r="R36" s="7" t="n"/>
       <c r="S36" s="8">
-        <f>IF(R36="","",R36/$B$4*1000)</f>
+        <f>IF(R36&lt;&gt;"",R36/$B$4*1000,IF(Q36&lt;&gt;"",($A36-Q36)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="T36" s="9" t="n">
@@ -3128,7 +3128,7 @@
       <c r="B37" s="7" t="n"/>
       <c r="C37" s="7" t="n"/>
       <c r="D37" s="8">
-        <f>IF(C37="","",C37/$B$4*1000)</f>
+        <f>IF(C37&lt;&gt;"",C37/$B$4*1000,IF(B37&lt;&gt;"",($A37-B37)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="E37" s="9" t="n">
@@ -3140,7 +3140,7 @@
       <c r="G37" s="7" t="n"/>
       <c r="H37" s="7" t="n"/>
       <c r="I37" s="8">
-        <f>IF(H37="","",H37/$B$4*1000)</f>
+        <f>IF(H37&lt;&gt;"",H37/$B$4*1000,IF(G37&lt;&gt;"",($A37-G37)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="J37" s="9" t="n">
@@ -3152,7 +3152,7 @@
       <c r="L37" s="7" t="n"/>
       <c r="M37" s="7" t="n"/>
       <c r="N37" s="8">
-        <f>IF(M37="","",M37/$B$4*1000)</f>
+        <f>IF(M37&lt;&gt;"",M37/$B$4*1000,IF(L37&lt;&gt;"",($A37-L37)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="O37" s="9" t="n">
@@ -3164,7 +3164,7 @@
       <c r="Q37" s="7" t="n"/>
       <c r="R37" s="7" t="n"/>
       <c r="S37" s="8">
-        <f>IF(R37="","",R37/$B$4*1000)</f>
+        <f>IF(R37&lt;&gt;"",R37/$B$4*1000,IF(Q37&lt;&gt;"",($A37-Q37)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="T37" s="9" t="n">
@@ -3181,7 +3181,7 @@
       <c r="B38" s="7" t="n"/>
       <c r="C38" s="7" t="n"/>
       <c r="D38" s="8">
-        <f>IF(C38="","",C38/$B$4*1000)</f>
+        <f>IF(C38&lt;&gt;"",C38/$B$4*1000,IF(B38&lt;&gt;"",($A38-B38)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="E38" s="9" t="n">
@@ -3193,7 +3193,7 @@
       <c r="G38" s="7" t="n"/>
       <c r="H38" s="7" t="n"/>
       <c r="I38" s="8">
-        <f>IF(H38="","",H38/$B$4*1000)</f>
+        <f>IF(H38&lt;&gt;"",H38/$B$4*1000,IF(G38&lt;&gt;"",($A38-G38)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="J38" s="9" t="n">
@@ -3205,7 +3205,7 @@
       <c r="L38" s="7" t="n"/>
       <c r="M38" s="7" t="n"/>
       <c r="N38" s="8">
-        <f>IF(M38="","",M38/$B$4*1000)</f>
+        <f>IF(M38&lt;&gt;"",M38/$B$4*1000,IF(L38&lt;&gt;"",($A38-L38)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="O38" s="9" t="n">
@@ -3217,7 +3217,7 @@
       <c r="Q38" s="7" t="n"/>
       <c r="R38" s="7" t="n"/>
       <c r="S38" s="8">
-        <f>IF(R38="","",R38/$B$4*1000)</f>
+        <f>IF(R38&lt;&gt;"",R38/$B$4*1000,IF(Q38&lt;&gt;"",($A38-Q38)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="T38" s="9" t="n">
@@ -3234,7 +3234,7 @@
       <c r="B39" s="7" t="n"/>
       <c r="C39" s="7" t="n"/>
       <c r="D39" s="8">
-        <f>IF(C39="","",C39/$B$4*1000)</f>
+        <f>IF(C39&lt;&gt;"",C39/$B$4*1000,IF(B39&lt;&gt;"",($A39-B39)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="E39" s="9" t="n">
@@ -3246,7 +3246,7 @@
       <c r="G39" s="7" t="n"/>
       <c r="H39" s="7" t="n"/>
       <c r="I39" s="8">
-        <f>IF(H39="","",H39/$B$4*1000)</f>
+        <f>IF(H39&lt;&gt;"",H39/$B$4*1000,IF(G39&lt;&gt;"",($A39-G39)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="J39" s="9" t="n">
@@ -3258,7 +3258,7 @@
       <c r="L39" s="7" t="n"/>
       <c r="M39" s="7" t="n"/>
       <c r="N39" s="8">
-        <f>IF(M39="","",M39/$B$4*1000)</f>
+        <f>IF(M39&lt;&gt;"",M39/$B$4*1000,IF(L39&lt;&gt;"",($A39-L39)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="O39" s="9" t="n">
@@ -3270,7 +3270,7 @@
       <c r="Q39" s="7" t="n"/>
       <c r="R39" s="7" t="n"/>
       <c r="S39" s="8">
-        <f>IF(R39="","",R39/$B$4*1000)</f>
+        <f>IF(R39&lt;&gt;"",R39/$B$4*1000,IF(Q39&lt;&gt;"",($A39-Q39)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="T39" s="9" t="n">
@@ -3287,7 +3287,7 @@
       <c r="B40" s="7" t="n"/>
       <c r="C40" s="7" t="n"/>
       <c r="D40" s="8">
-        <f>IF(C40="","",C40/$B$4*1000)</f>
+        <f>IF(C40&lt;&gt;"",C40/$B$4*1000,IF(B40&lt;&gt;"",($A40-B40)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="E40" s="9" t="n">
@@ -3299,7 +3299,7 @@
       <c r="G40" s="7" t="n"/>
       <c r="H40" s="7" t="n"/>
       <c r="I40" s="8">
-        <f>IF(H40="","",H40/$B$4*1000)</f>
+        <f>IF(H40&lt;&gt;"",H40/$B$4*1000,IF(G40&lt;&gt;"",($A40-G40)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="J40" s="9" t="n">
@@ -3311,7 +3311,7 @@
       <c r="L40" s="7" t="n"/>
       <c r="M40" s="7" t="n"/>
       <c r="N40" s="8">
-        <f>IF(M40="","",M40/$B$4*1000)</f>
+        <f>IF(M40&lt;&gt;"",M40/$B$4*1000,IF(L40&lt;&gt;"",($A40-L40)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="O40" s="9" t="n">
@@ -3323,7 +3323,7 @@
       <c r="Q40" s="7" t="n"/>
       <c r="R40" s="7" t="n"/>
       <c r="S40" s="8">
-        <f>IF(R40="","",R40/$B$4*1000)</f>
+        <f>IF(R40&lt;&gt;"",R40/$B$4*1000,IF(Q40&lt;&gt;"",($A40-Q40)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="T40" s="9" t="n">
@@ -3340,7 +3340,7 @@
       <c r="B41" s="7" t="n"/>
       <c r="C41" s="7" t="n"/>
       <c r="D41" s="8">
-        <f>IF(C41="","",C41/$B$4*1000)</f>
+        <f>IF(C41&lt;&gt;"",C41/$B$4*1000,IF(B41&lt;&gt;"",($A41-B41)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="E41" s="9" t="n">
@@ -3352,7 +3352,7 @@
       <c r="G41" s="7" t="n"/>
       <c r="H41" s="7" t="n"/>
       <c r="I41" s="8">
-        <f>IF(H41="","",H41/$B$4*1000)</f>
+        <f>IF(H41&lt;&gt;"",H41/$B$4*1000,IF(G41&lt;&gt;"",($A41-G41)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="J41" s="9" t="n">
@@ -3364,7 +3364,7 @@
       <c r="L41" s="7" t="n"/>
       <c r="M41" s="7" t="n"/>
       <c r="N41" s="8">
-        <f>IF(M41="","",M41/$B$4*1000)</f>
+        <f>IF(M41&lt;&gt;"",M41/$B$4*1000,IF(L41&lt;&gt;"",($A41-L41)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="O41" s="9" t="n">
@@ -3376,7 +3376,7 @@
       <c r="Q41" s="7" t="n"/>
       <c r="R41" s="7" t="n"/>
       <c r="S41" s="8">
-        <f>IF(R41="","",R41/$B$4*1000)</f>
+        <f>IF(R41&lt;&gt;"",R41/$B$4*1000,IF(Q41&lt;&gt;"",($A41-Q41)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="T41" s="9" t="n">
@@ -3393,7 +3393,7 @@
       <c r="B42" s="7" t="n"/>
       <c r="C42" s="7" t="n"/>
       <c r="D42" s="8">
-        <f>IF(C42="","",C42/$B$4*1000)</f>
+        <f>IF(C42&lt;&gt;"",C42/$B$4*1000,IF(B42&lt;&gt;"",($A42-B42)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="E42" s="9" t="n">
@@ -3405,7 +3405,7 @@
       <c r="G42" s="7" t="n"/>
       <c r="H42" s="7" t="n"/>
       <c r="I42" s="8">
-        <f>IF(H42="","",H42/$B$4*1000)</f>
+        <f>IF(H42&lt;&gt;"",H42/$B$4*1000,IF(G42&lt;&gt;"",($A42-G42)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="J42" s="9" t="n">
@@ -3417,7 +3417,7 @@
       <c r="L42" s="7" t="n"/>
       <c r="M42" s="7" t="n"/>
       <c r="N42" s="8">
-        <f>IF(M42="","",M42/$B$4*1000)</f>
+        <f>IF(M42&lt;&gt;"",M42/$B$4*1000,IF(L42&lt;&gt;"",($A42-L42)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="O42" s="9" t="n">
@@ -3429,7 +3429,7 @@
       <c r="Q42" s="7" t="n"/>
       <c r="R42" s="7" t="n"/>
       <c r="S42" s="8">
-        <f>IF(R42="","",R42/$B$4*1000)</f>
+        <f>IF(R42&lt;&gt;"",R42/$B$4*1000,IF(Q42&lt;&gt;"",($A42-Q42)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="T42" s="9" t="n">
@@ -3446,7 +3446,7 @@
       <c r="B43" s="7" t="n"/>
       <c r="C43" s="7" t="n"/>
       <c r="D43" s="8">
-        <f>IF(C43="","",C43/$B$4*1000)</f>
+        <f>IF(C43&lt;&gt;"",C43/$B$4*1000,IF(B43&lt;&gt;"",($A43-B43)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="E43" s="9" t="n">
@@ -3458,7 +3458,7 @@
       <c r="G43" s="7" t="n"/>
       <c r="H43" s="7" t="n"/>
       <c r="I43" s="8">
-        <f>IF(H43="","",H43/$B$4*1000)</f>
+        <f>IF(H43&lt;&gt;"",H43/$B$4*1000,IF(G43&lt;&gt;"",($A43-G43)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="J43" s="9" t="n">
@@ -3470,7 +3470,7 @@
       <c r="L43" s="7" t="n"/>
       <c r="M43" s="7" t="n"/>
       <c r="N43" s="8">
-        <f>IF(M43="","",M43/$B$4*1000)</f>
+        <f>IF(M43&lt;&gt;"",M43/$B$4*1000,IF(L43&lt;&gt;"",($A43-L43)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="O43" s="9" t="n">
@@ -3482,7 +3482,7 @@
       <c r="Q43" s="7" t="n"/>
       <c r="R43" s="7" t="n"/>
       <c r="S43" s="8">
-        <f>IF(R43="","",R43/$B$4*1000)</f>
+        <f>IF(R43&lt;&gt;"",R43/$B$4*1000,IF(Q43&lt;&gt;"",($A43-Q43)/$B$4*1000,""))</f>
         <v/>
       </c>
       <c r="T43" s="9" t="n">
@@ -3495,94 +3495,101 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>V_RC 是集極電阻兩端的壓降（量 V_CC 對集極），I_C 由它換算；V_CE 是集極對射極（本電路射極接地，等於集極對地）。兩欄都量，結報才有互相驗證的資料。</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
+          <t>I_C 的分子必須是「集極電阻兩端的壓降」V_RC，不是集極對地電位。本電路射極接地，所以 V_CE 就是集極對地電位，兩者的關係是 V_RC = V_CC − V_CE。</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>因此兩欄只要量一欄就夠：I_C 欄會優先用 V_RC；沒填 V_RC 時自動改用 (V_CC − V_CE) / R_C。兩欄都量的好處是可以當場對帳——V_CE + V_RC 應該等於 V_CC，對不起來就是有一次量錯了。</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>當天拍照檢查表（離開實驗室前逐項打勾）</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="16" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="16" t="inlineStr">
         <is>
           <t>要留的證據</t>
         </is>
       </c>
-      <c r="B48" s="16" t="inlineStr">
+      <c r="B49" s="16" t="inlineStr">
         <is>
           <t>打勾</t>
         </is>
       </c>
-      <c r="C48" s="16" t="inlineStr">
+      <c r="C49" s="16" t="inlineStr">
         <is>
           <t>備註</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="17" t="inlineStr">
-        <is>
-          <t>麵包板全景照 1 張</t>
-        </is>
-      </c>
-      <c r="B49" s="18" t="n"/>
-      <c r="C49" s="19" t="inlineStr">
-        <is>
-          <t>看得出 R1／R2／RC 各插在第幾欄、電晶體三腳的 E／B／C 方向</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="17" t="inlineStr">
         <is>
-          <t>電表接線特寫 1 張</t>
+          <t>麵包板全景照 1 張</t>
         </is>
       </c>
       <c r="B50" s="18" t="n"/>
       <c r="C50" s="19" t="inlineStr">
         <is>
-          <t>左表跨 B-E、中表跨 C-E、右表串在 VCC 與 RC 之間</t>
+          <t>看得出 R1／R2／RC 各插在第幾欄、電晶體三腳的 E／B／C 方向</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="17" t="inlineStr">
         <is>
-          <t>兩台電源面板各 1 張</t>
+          <t>電表接線特寫 1 張</t>
         </is>
       </c>
       <c r="B51" s="18" t="n"/>
       <c r="C51" s="19" t="inlineStr">
         <is>
-          <t>V_BB 與 V_CC 的設定值要和記錄表對得上</t>
+          <t>左表跨 B-E、中表跨 C-E、右表串在 VCC 與 RC 之間</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="17" t="inlineStr">
         <is>
-          <t>四組 V_BB 的 V_BE 都記到</t>
+          <t>兩台電源面板各 1 張</t>
         </is>
       </c>
       <c r="B52" s="18" t="n"/>
       <c r="C52" s="19" t="inlineStr">
         <is>
-          <t>導通後 V_BE 幾乎不動，沒記到就無法回答「ON/OFF 怎麼判定」</t>
+          <t>V_BB 與 V_CC 的設定值要和記錄表對得上</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="17" t="inlineStr">
         <is>
-          <t>特性曲線當場畫一次</t>
+          <t>四組 V_BB 的 V_BE 都記到</t>
         </is>
       </c>
       <c r="B53" s="18" t="n"/>
       <c r="C53" s="19" t="inlineStr">
+        <is>
+          <t>導通後 V_BE 幾乎不動，沒記到就無法回答「ON/OFF 怎麼判定」</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="17" t="inlineStr">
+        <is>
+          <t>特性曲線當場畫一次</t>
+        </is>
+      </c>
+      <c r="B54" s="18" t="n"/>
+      <c r="C54" s="19" t="inlineStr">
         <is>
           <t>四條線要看得出平坦的主動區；不平坦代表還沒離開飽和區</t>
         </is>

--- a/simulations/lab2/measured/Lab2-數據記錄.xlsx
+++ b/simulations/lab2/measured/Lab2-數據記錄.xlsx
@@ -147,7 +147,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -180,6 +180,8 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1423,7 +1425,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>I_C 一律由集極電阻的壓降換算（I_C = V_RC / R_C），電流表只在實驗二串一次；</t>
+          <t>I_C 一律由集極電阻的壓降換算（I_C = V_RC / R_C）——講義第 8 頁與第 9 頁都是這樣要求的，</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1433,7 @@
       <c r="A11" s="4" t="inlineStr"/>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　兩種方法的差異就是誤差來源，結報要寫。</t>
+          <t xml:space="preserve">　　兩個實驗都不必把電流表串進集極迴路，三用電表全程留在電壓檔。</t>
         </is>
       </c>
     </row>
@@ -3945,7 +3947,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3971,10 +3973,33 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>電源設定值</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t>V_BB (V)</t>
+        </is>
+      </c>
+      <c r="C3" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="D3" s="17" t="inlineStr">
+        <is>
+          <t>V_CC (V)</t>
+        </is>
+      </c>
+      <c r="E3" s="22" t="n">
+        <v>15</v>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>電阻值 (Ω)</t>
+          <t>電阻實測值 (Ω)</t>
         </is>
       </c>
       <c r="B4" s="17" t="inlineStr">
@@ -3982,7 +4007,7 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="C4" s="11" t="n">
+      <c r="C4" s="23" t="n">
         <v>10000</v>
       </c>
       <c r="D4" s="17" t="inlineStr">
@@ -3990,7 +4015,7 @@
           <t>R2</t>
         </is>
       </c>
-      <c r="E4" s="11" t="n">
+      <c r="E4" s="23" t="n">
         <v>4700</v>
       </c>
       <c r="F4" s="17" t="inlineStr">
@@ -3998,8 +4023,15 @@
           <t>R_C</t>
         </is>
       </c>
-      <c r="G4" s="11" t="n">
+      <c r="G4" s="23" t="n">
         <v>1000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>↑ 這五格是助教在 Table 2 旁邊特別要求記錄的（V_BB、V_CC、R_C、R1、R2）。電阻先填的是標稱值，開工前用三用電表各量一次改成實測值——±5% 的色環電阻常差到幾百歐姆，下面所有電流與 β 都是用這三格算的。</t>
+        </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
@@ -4139,7 +4171,7 @@
       </c>
       <c r="G10" s="19" t="inlineStr">
         <is>
-          <t>集極對射極；深度飽和時只剩幾十 mV</t>
+          <t>直接量集極對地，不要用 V_CC − V_RC 相減（兩個 15 V 量級的數相減，誤差會和待測值同級）</t>
         </is>
       </c>
     </row>
@@ -4323,7 +4355,7 @@
       </c>
       <c r="G16" s="19" t="inlineStr">
         <is>
-          <t>把電晶體拔下來插 hFE 座；這才是主動區的 β</t>
+          <t>助教把 Table 2 的 β_Meas 欄劃掉了，這格不抄進 Table 2，但仍要量——它是問題 1 的證據</t>
         </is>
       </c>
     </row>
@@ -4361,37 +4393,63 @@
     <row r="22">
       <c r="A22" s="17" t="inlineStr">
         <is>
-          <t>Table 2 五個量都填完</t>
+          <t>四個壓降都量到</t>
         </is>
       </c>
       <c r="B22" s="18" t="n"/>
       <c r="C22" s="19" t="inlineStr">
         <is>
-          <t>V_R1、V_R2、V_RC、V_CE、β_measure</t>
+          <t>V_R1、V_R2、V_RC、V_CE（V_CE 要直接量，不要相減）</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="17" t="inlineStr">
         <is>
-          <t>電晶體 hFE 讀值照片 1 張</t>
+          <t>五個設定值都記下</t>
         </is>
       </c>
       <c r="B23" s="18" t="n"/>
       <c r="C23" s="19" t="inlineStr">
         <is>
-          <t>拔下來插 hFE 座量到的 β，結報要對照</t>
+          <t>V_BB、V_CC 與 R1／R2／R_C 的實測值，助教要求</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="17" t="inlineStr">
         <is>
-          <t>飽和的證據 1 張</t>
+          <t>Table 2 三欄填完</t>
         </is>
       </c>
       <c r="B24" s="18" t="n"/>
       <c r="C24" s="19" t="inlineStr">
+        <is>
+          <t>講義 Table 2 只要 I_B、I_C、β_calculate（β_Meas 已被助教劃掉）</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="17" t="inlineStr">
+        <is>
+          <t>電晶體 hFE 讀值照片 1 張</t>
+        </is>
+      </c>
+      <c r="B25" s="18" t="n"/>
+      <c r="C25" s="19" t="inlineStr">
+        <is>
+          <t>拔下來插 hFE 座量到的 β，寫自己的記錄表、不抄進 Table 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="17" t="inlineStr">
+        <is>
+          <t>飽和的證據 1 張</t>
+        </is>
+      </c>
+      <c r="B26" s="18" t="n"/>
+      <c r="C26" s="19" t="inlineStr">
         <is>
           <t>V_CE 只剩幾十 mV 的電表畫面</t>
         </is>
@@ -4644,13 +4702,13 @@
           <t>RC1 100 Ω、有 C3</t>
         </is>
       </c>
-      <c r="B14" s="22" t="n"/>
-      <c r="C14" s="22" t="n"/>
-      <c r="D14" s="23">
+      <c r="B14" s="24" t="n"/>
+      <c r="C14" s="24" t="n"/>
+      <c r="D14" s="25">
         <f>IF(OR(B14="",B14=0,C14=""),"",C14/B14)</f>
         <v/>
       </c>
-      <c r="E14" s="24" t="n">
+      <c r="E14" s="26" t="n">
         <v>5.54</v>
       </c>
       <c r="F14" s="10">
@@ -4665,13 +4723,13 @@
           <t>RC1 1 kΩ、有 C3</t>
         </is>
       </c>
-      <c r="B15" s="22" t="n"/>
-      <c r="C15" s="22" t="n"/>
-      <c r="D15" s="23">
+      <c r="B15" s="24" t="n"/>
+      <c r="C15" s="24" t="n"/>
+      <c r="D15" s="25">
         <f>IF(OR(B15="",B15=0,C15=""),"",C15/B15)</f>
         <v/>
       </c>
-      <c r="E15" s="24" t="n">
+      <c r="E15" s="26" t="n">
         <v>41.13</v>
       </c>
       <c r="F15" s="10">
@@ -4686,13 +4744,13 @@
           <t>RC1 100 Ω、無 C3</t>
         </is>
       </c>
-      <c r="B16" s="22" t="n"/>
-      <c r="C16" s="22" t="n"/>
-      <c r="D16" s="23">
+      <c r="B16" s="24" t="n"/>
+      <c r="C16" s="24" t="n"/>
+      <c r="D16" s="25">
         <f>IF(OR(B16="",B16=0,C16=""),"",C16/B16)</f>
         <v/>
       </c>
-      <c r="E16" s="24" t="n">
+      <c r="E16" s="26" t="n">
         <v>0.1</v>
       </c>
       <c r="F16" s="10">
@@ -4707,13 +4765,13 @@
           <t>RC1 1 kΩ、無 C3</t>
         </is>
       </c>
-      <c r="B17" s="22" t="n"/>
-      <c r="C17" s="22" t="n"/>
-      <c r="D17" s="23">
+      <c r="B17" s="24" t="n"/>
+      <c r="C17" s="24" t="n"/>
+      <c r="D17" s="25">
         <f>IF(OR(B17="",B17=0,C17=""),"",C17/B17)</f>
         <v/>
       </c>
-      <c r="E17" s="24" t="n">
+      <c r="E17" s="26" t="n">
         <v>0.88</v>
       </c>
       <c r="F17" s="10">

--- a/simulations/lab2/measured/Lab2-數據記錄.xlsx
+++ b/simulations/lab2/measured/Lab2-數據記錄.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="第二部分 CE 放大器" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
 </file>
 
@@ -562,7 +562,7 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <axPos val="b"/>
         <majorGridlines/>
         <title>
           <tx>
@@ -645,6 +645,9 @@
         <ser>
           <idx val="0"/>
           <order val="0"/>
+          <tx>
+            <v>實測</v>
+          </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
@@ -664,6 +667,9 @@
         <ser>
           <idx val="1"/>
           <order val="1"/>
+          <tx>
+            <v>LTspice</v>
+          </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
@@ -757,6 +763,9 @@
         <ser>
           <idx val="0"/>
           <order val="0"/>
+          <tx>
+            <v>β</v>
+          </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
@@ -815,9 +824,6 @@
         <crossAx val="10"/>
       </valAx>
     </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
@@ -850,6 +856,9 @@
         <ser>
           <idx val="0"/>
           <order val="0"/>
+          <tx>
+            <v>實測</v>
+          </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
@@ -869,6 +878,9 @@
         <ser>
           <idx val="1"/>
           <order val="1"/>
+          <tx>
+            <v>LTspice</v>
+          </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
@@ -1016,7 +1028,7 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>8</col>
+      <col>9</col>
       <colOff>0</colOff>
       <row>11</row>
       <rowOff>0</rowOff>
@@ -1369,7 +1381,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>每個實驗一張工作表，只要填**黃底**的格子，其他欄位都是公式或預報值，不要覆蓋。</t>
+          <t>每個實驗一張工作表，只要填黃底的格子，其他欄位都是公式或預報值，不要覆蓋。</t>
         </is>
       </c>
     </row>
@@ -1489,7 +1501,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>→ 差異 (%)</t>
+          <t>→ 相對偏差 (%)</t>
         </is>
       </c>
     </row>
@@ -3554,7 +3566,7 @@
       <c r="B51" s="18" t="n"/>
       <c r="C51" s="19" t="inlineStr">
         <is>
-          <t>左表跨 B-E、中表跨 C-E、右表串在 VCC 與 RC 之間</t>
+          <t>左表跨 B-E、中表跨 C-E、右表設 DC 電壓檔並跨 RC 兩端量 V_RC</t>
         </is>
       </c>
     </row>
@@ -3606,6 +3618,11 @@
     <mergeCell ref="A1:Q1"/>
     <mergeCell ref="G11:I11"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="F11 K11 P11 U11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"ON,OFF"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -3637,7 +3654,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>欄位與版面照 App_Lab2.pdf 第 8 頁；數值自動從「實驗一 特性曲線」工作表抓，不要直接在這裡填</t>
+          <t>版面參照 App_Lab2.pdf 第 8 頁；電流統一標示為 mA，數值自動從「實驗一 特性曲線」抓取</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3683,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>I_C (measure)  ( = V_C / R_C )</t>
+          <t>I_C (mA)  ( = V_RC / R_C )</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -3676,7 +3693,7 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>I_C (measure)  ( = V_C / R_C )</t>
+          <t>I_C (mA)  ( = V_RC / R_C )</t>
         </is>
       </c>
       <c r="H6" s="6" t="n">
@@ -3810,7 +3827,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>I_C (measure)  ( = V_C / R_C )</t>
+          <t>I_C (mA)  ( = V_RC / R_C )</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -3820,7 +3837,7 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>I_C (measure)  ( = V_C / R_C )</t>
+          <t>I_C (mA)  ( = V_RC / R_C )</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3934,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>I_C 的單位是 mA（講義表頭寫 A，抄進報告時記得換算或標註單位）。</t>
+          <t>I_C 已統一使用 mA；若指定報告格式要求 A，請將數值除以 1000 並同步標註單位。</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4079,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>差異 (%)</t>
+          <t>相對偏差 (%)</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -4190,9 +4207,10 @@
           <t>mA</t>
         </is>
       </c>
-      <c r="D11" s="19">
-        <f>IF(B7="","",B7/$C$4*1000)</f>
-        <v/>
+      <c r="D11" s="19" t="inlineStr">
+        <is>
+          <t>V_R1 ÷ R1 × 1000</t>
+        </is>
       </c>
       <c r="E11" s="9" t="n">
         <v>1.425</v>
@@ -4222,9 +4240,10 @@
           <t>mA</t>
         </is>
       </c>
-      <c r="D12" s="19">
-        <f>IF(B8="","",B8/$E$4*1000)</f>
-        <v/>
+      <c r="D12" s="19" t="inlineStr">
+        <is>
+          <t>V_R2 ÷ R2 × 1000</t>
+        </is>
       </c>
       <c r="E12" s="9" t="n">
         <v>0.159</v>
@@ -4254,9 +4273,10 @@
           <t>mA</t>
         </is>
       </c>
-      <c r="D13" s="19">
-        <f>IF(OR(B7="",B8=""),"",B11-B12)</f>
-        <v/>
+      <c r="D13" s="19" t="inlineStr">
+        <is>
+          <t>I_R1 − I_R2</t>
+        </is>
       </c>
       <c r="E13" s="9" t="n">
         <v>1.266</v>
@@ -4286,9 +4306,10 @@
           <t>mA</t>
         </is>
       </c>
-      <c r="D14" s="19">
-        <f>IF(B9="","",B9/$G$4*1000)</f>
-        <v/>
+      <c r="D14" s="19" t="inlineStr">
+        <is>
+          <t>V_RC ÷ R_C × 1000</t>
+        </is>
       </c>
       <c r="E14" s="9" t="n">
         <v>14.946</v>
@@ -4318,9 +4339,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="D15" s="19">
-        <f>IF(OR(B13="",B13=0,B14=""),"",B14/B13)</f>
-        <v/>
+      <c r="D15" s="19" t="inlineStr">
+        <is>
+          <t>I_C ÷ I_B</t>
+        </is>
       </c>
       <c r="E15" s="9" t="n">
         <v>11.81</v>
@@ -4471,7 +4493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4481,6 +4503,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4497,6 +4520,37 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>直流計算設定</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t>V_CC (V)</t>
+        </is>
+      </c>
+      <c r="C3" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="D3" s="17" t="inlineStr">
+        <is>
+          <t>R_C1 100 Ω 實測 (Ω)</t>
+        </is>
+      </c>
+      <c r="E3" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="F3" s="17" t="inlineStr">
+        <is>
+          <t>R_C1 1 kΩ 實測 (Ω)</t>
+        </is>
+      </c>
+      <c r="G3" s="23" t="n">
+        <v>1000</v>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -4512,7 +4566,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>實測 (V)</t>
+          <t>實測 R_C1 = 100 Ω</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -4522,20 +4576,29 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
+          <t>相對偏差 (%)</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>實測 R_C1 = 1 kΩ</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
           <t>LTspice R_C1 = 1 kΩ</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>差異 (%)</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>相對偏差 (%)</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>備註</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="17" t="inlineStr">
@@ -4547,14 +4610,19 @@
       <c r="C6" s="9" t="n">
         <v>5.876</v>
       </c>
-      <c r="D6" s="9" t="n">
+      <c r="D6" s="10">
+        <f>IF(OR(B6="",C6=0),"",(B6-C6)/C6)</f>
+        <v/>
+      </c>
+      <c r="E6" s="7" t="n"/>
+      <c r="F6" s="9" t="n">
         <v>5.87</v>
       </c>
-      <c r="E6" s="10">
-        <f>IF(OR(B6="",C6=0),"",(B6-C6)/C6)</f>
-        <v/>
-      </c>
-      <c r="F6" s="19" t="inlineStr">
+      <c r="G6" s="10">
+        <f>IF(OR(E6="",F6=0),"",(E6-F6)/F6)</f>
+        <v/>
+      </c>
+      <c r="H6" s="19" t="inlineStr">
         <is>
           <t>分壓器給的 6 V 附近</t>
         </is>
@@ -4570,14 +4638,19 @@
       <c r="C7" s="9" t="n">
         <v>5.178</v>
       </c>
-      <c r="D7" s="9" t="n">
+      <c r="D7" s="10">
+        <f>IF(OR(B7="",C7=0),"",(B7-C7)/C7)</f>
+        <v/>
+      </c>
+      <c r="E7" s="7" t="n"/>
+      <c r="F7" s="9" t="n">
         <v>5.171</v>
       </c>
-      <c r="E7" s="10">
-        <f>IF(OR(B7="",C7=0),"",(B7-C7)/C7)</f>
-        <v/>
-      </c>
-      <c r="F7" s="19" t="inlineStr">
+      <c r="G7" s="10">
+        <f>IF(OR(E7="",F7=0),"",(E7-F7)/F7)</f>
+        <v/>
+      </c>
+      <c r="H7" s="19" t="inlineStr">
         <is>
           <t>約 V_B − 0.7</t>
         </is>
@@ -4593,14 +4666,19 @@
       <c r="C8" s="9" t="n">
         <v>11.485</v>
       </c>
-      <c r="D8" s="9" t="n">
+      <c r="D8" s="10">
+        <f>IF(OR(B8="",C8=0),"",(B8-C8)/C8)</f>
+        <v/>
+      </c>
+      <c r="E8" s="7" t="n"/>
+      <c r="F8" s="9" t="n">
         <v>6.854</v>
       </c>
-      <c r="E8" s="10">
-        <f>IF(OR(B8="",C8=0),"",(B8-C8)/C8)</f>
-        <v/>
-      </c>
-      <c r="F8" s="19" t="inlineStr">
+      <c r="G8" s="10">
+        <f>IF(OR(E8="",F8=0),"",(E8-F8)/F8)</f>
+        <v/>
+      </c>
+      <c r="H8" s="19" t="inlineStr">
         <is>
           <t>R_C1 越大這裡越低</t>
         </is>
@@ -4612,20 +4690,31 @@
           <t>V_CE = V_C − V_E</t>
         </is>
       </c>
-      <c r="B9" s="7" t="n"/>
+      <c r="B9" s="8">
+        <f>IF(OR(B7="",B8=""),"",B8-B7)</f>
+        <v/>
+      </c>
       <c r="C9" s="9" t="n">
         <v>6.306</v>
       </c>
-      <c r="D9" s="9" t="n">
+      <c r="D9" s="10">
+        <f>IF(OR(B9="",C9=0),"",(B9-C9)/C9)</f>
+        <v/>
+      </c>
+      <c r="E9" s="8">
+        <f>IF(OR(E7="",E8=""),"",E8-E7)</f>
+        <v/>
+      </c>
+      <c r="F9" s="9" t="n">
         <v>1.683</v>
       </c>
-      <c r="E9" s="10">
-        <f>IF(OR(B9="",C9=0),"",(B9-C9)/C9)</f>
-        <v/>
-      </c>
-      <c r="F9" s="19" t="inlineStr">
-        <is>
-          <t>小於 1 V 就代表快飽和，訊號會削波</t>
+      <c r="G9" s="10">
+        <f>IF(OR(E9="",F9=0),"",(E9-F9)/F9)</f>
+        <v/>
+      </c>
+      <c r="H9" s="19" t="inlineStr">
+        <is>
+          <t>由 V_C − V_E 自動計算；小於 1 V 就代表快飽和，訊號會削波</t>
         </is>
       </c>
     </row>
@@ -4636,19 +4725,30 @@
         </is>
       </c>
       <c r="B10" s="8">
-        <f>IF(B8="","",(12-B8)/100*1000)</f>
+        <f>IF(OR(B8="",$C$3="",$E$3="",$E$3=0),"",($C$3-B8)/$E$3*1000)</f>
         <v/>
       </c>
       <c r="C10" s="9" t="n">
         <v>5.153</v>
       </c>
-      <c r="D10" s="9" t="n">
+      <c r="D10" s="10">
+        <f>IF(OR(B10="",C10=0),"",(B10-C10)/C10)</f>
+        <v/>
+      </c>
+      <c r="E10" s="8">
+        <f>IF(OR(E8="",$C$3="",$G$3="",$G$3=0),"",($C$3-E8)/$G$3*1000)</f>
+        <v/>
+      </c>
+      <c r="F10" s="9" t="n">
         <v>5.146</v>
       </c>
-      <c r="E10" s="17" t="n"/>
-      <c r="F10" s="19" t="inlineStr">
-        <is>
-          <t>單位 mA；式子裡的 100 要跟著實際用的 R_C1 改</t>
+      <c r="G10" s="10">
+        <f>IF(OR(E10="",F10=0),"",(E10-F10)/F10)</f>
+        <v/>
+      </c>
+      <c r="H10" s="19" t="inlineStr">
+        <is>
+          <t>單位 mA；使用上方輸入的 V_CC 與兩顆 R_C1 實測阻值計算</t>
         </is>
       </c>
     </row>
@@ -4677,7 +4777,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>|A_v| = V_out / V_s</t>
+          <t>實測 |A_v| (= V_out/V_s)</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -4687,7 +4787,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>差異 (%)</t>
+          <t>相對偏差 (%)</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -5047,8 +5147,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/simulations/lab2/measured/Lab2-數據記錄.xlsx
+++ b/simulations/lab2/measured/Lab2-數據記錄.xlsx
@@ -1726,8 +1726,8 @@
       </c>
       <c r="C11" s="14" t="n"/>
       <c r="D11" s="14" t="n"/>
-      <c r="E11" s="7" t="n"/>
-      <c r="F11" s="15" t="n"/>
+      <c r="E11" s="7" t="inlineStr"/>
+      <c r="F11" s="15" t="inlineStr"/>
       <c r="G11" s="13" t="inlineStr">
         <is>
           <t>V_BB = 2.0 V　V_BE =</t>
@@ -1735,8 +1735,8 @@
       </c>
       <c r="H11" s="14" t="n"/>
       <c r="I11" s="14" t="n"/>
-      <c r="J11" s="7" t="n"/>
-      <c r="K11" s="15" t="n"/>
+      <c r="J11" s="7" t="inlineStr"/>
+      <c r="K11" s="15" t="inlineStr"/>
       <c r="L11" s="13" t="inlineStr">
         <is>
           <t>V_BB = 2.2 V　V_BE =</t>
@@ -1744,8 +1744,8 @@
       </c>
       <c r="M11" s="14" t="n"/>
       <c r="N11" s="14" t="n"/>
-      <c r="O11" s="7" t="n"/>
-      <c r="P11" s="15" t="n"/>
+      <c r="O11" s="7" t="inlineStr"/>
+      <c r="P11" s="15" t="inlineStr"/>
       <c r="Q11" s="13" t="inlineStr">
         <is>
           <t>V_BB = 2.4 V　V_BE =</t>
@@ -1753,8 +1753,8 @@
       </c>
       <c r="R11" s="14" t="n"/>
       <c r="S11" s="14" t="n"/>
-      <c r="T11" s="7" t="n"/>
-      <c r="U11" s="15" t="n"/>
+      <c r="T11" s="7" t="inlineStr"/>
+      <c r="U11" s="15" t="inlineStr"/>
     </row>
     <row r="12" ht="34" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
@@ -1867,8 +1867,8 @@
       <c r="A13" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="7" t="n"/>
+      <c r="B13" s="7" t="inlineStr"/>
+      <c r="C13" s="7" t="inlineStr"/>
       <c r="D13" s="8">
         <f>IF(C13&lt;&gt;"",C13/$B$4*1000,IF(B13&lt;&gt;"",($A13-B13)/$B$4*1000,""))</f>
         <v/>
@@ -1879,8 +1879,8 @@
       <c r="F13" s="9" t="n">
         <v>-0.0003</v>
       </c>
-      <c r="G13" s="7" t="n"/>
-      <c r="H13" s="7" t="n"/>
+      <c r="G13" s="7" t="inlineStr"/>
+      <c r="H13" s="7" t="inlineStr"/>
       <c r="I13" s="8">
         <f>IF(H13&lt;&gt;"",H13/$B$4*1000,IF(G13&lt;&gt;"",($A13-G13)/$B$4*1000,""))</f>
         <v/>
@@ -1891,8 +1891,8 @@
       <c r="K13" s="9" t="n">
         <v>-0.0054</v>
       </c>
-      <c r="L13" s="7" t="n"/>
-      <c r="M13" s="7" t="n"/>
+      <c r="L13" s="7" t="inlineStr"/>
+      <c r="M13" s="7" t="inlineStr"/>
       <c r="N13" s="8">
         <f>IF(M13&lt;&gt;"",M13/$B$4*1000,IF(L13&lt;&gt;"",($A13-L13)/$B$4*1000,""))</f>
         <v/>
@@ -1903,8 +1903,8 @@
       <c r="P13" s="9" t="n">
         <v>-0.0062</v>
       </c>
-      <c r="Q13" s="7" t="n"/>
-      <c r="R13" s="7" t="n"/>
+      <c r="Q13" s="7" t="inlineStr"/>
+      <c r="R13" s="7" t="inlineStr"/>
       <c r="S13" s="8">
         <f>IF(R13&lt;&gt;"",R13/$B$4*1000,IF(Q13&lt;&gt;"",($A13-Q13)/$B$4*1000,""))</f>
         <v/>
@@ -1920,8 +1920,8 @@
       <c r="A14" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="B14" s="7" t="n"/>
-      <c r="C14" s="7" t="n"/>
+      <c r="B14" s="7" t="inlineStr"/>
+      <c r="C14" s="7" t="inlineStr"/>
       <c r="D14" s="8">
         <f>IF(C14&lt;&gt;"",C14/$B$4*1000,IF(B14&lt;&gt;"",($A14-B14)/$B$4*1000,""))</f>
         <v/>
@@ -1932,8 +1932,8 @@
       <c r="F14" s="9" t="n">
         <v>0.0011</v>
       </c>
-      <c r="G14" s="7" t="n"/>
-      <c r="H14" s="7" t="n"/>
+      <c r="G14" s="7" t="inlineStr"/>
+      <c r="H14" s="7" t="inlineStr"/>
       <c r="I14" s="8">
         <f>IF(H14&lt;&gt;"",H14/$B$4*1000,IF(G14&lt;&gt;"",($A14-G14)/$B$4*1000,""))</f>
         <v/>
@@ -1944,8 +1944,8 @@
       <c r="K14" s="9" t="n">
         <v>0.3741</v>
       </c>
-      <c r="L14" s="7" t="n"/>
-      <c r="M14" s="7" t="n"/>
+      <c r="L14" s="7" t="inlineStr"/>
+      <c r="M14" s="7" t="inlineStr"/>
       <c r="N14" s="8">
         <f>IF(M14&lt;&gt;"",M14/$B$4*1000,IF(L14&lt;&gt;"",($A14-L14)/$B$4*1000,""))</f>
         <v/>
@@ -1956,8 +1956,8 @@
       <c r="P14" s="9" t="n">
         <v>0.4411</v>
       </c>
-      <c r="Q14" s="7" t="n"/>
-      <c r="R14" s="7" t="n"/>
+      <c r="Q14" s="7" t="inlineStr"/>
+      <c r="R14" s="7" t="inlineStr"/>
       <c r="S14" s="8">
         <f>IF(R14&lt;&gt;"",R14/$B$4*1000,IF(Q14&lt;&gt;"",($A14-Q14)/$B$4*1000,""))</f>
         <v/>
@@ -1973,8 +1973,8 @@
       <c r="A15" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B15" s="7" t="n"/>
-      <c r="C15" s="7" t="n"/>
+      <c r="B15" s="7" t="inlineStr"/>
+      <c r="C15" s="7" t="inlineStr"/>
       <c r="D15" s="8">
         <f>IF(C15&lt;&gt;"",C15/$B$4*1000,IF(B15&lt;&gt;"",($A15-B15)/$B$4*1000,""))</f>
         <v/>
@@ -1985,8 +1985,8 @@
       <c r="F15" s="9" t="n">
         <v>0.0011</v>
       </c>
-      <c r="G15" s="7" t="n"/>
-      <c r="H15" s="7" t="n"/>
+      <c r="G15" s="7" t="inlineStr"/>
+      <c r="H15" s="7" t="inlineStr"/>
       <c r="I15" s="8">
         <f>IF(H15&lt;&gt;"",H15/$B$4*1000,IF(G15&lt;&gt;"",($A15-G15)/$B$4*1000,""))</f>
         <v/>
@@ -1997,8 +1997,8 @@
       <c r="K15" s="9" t="n">
         <v>0.4186</v>
       </c>
-      <c r="L15" s="7" t="n"/>
-      <c r="M15" s="7" t="n"/>
+      <c r="L15" s="7" t="inlineStr"/>
+      <c r="M15" s="7" t="inlineStr"/>
       <c r="N15" s="8">
         <f>IF(M15&lt;&gt;"",M15/$B$4*1000,IF(L15&lt;&gt;"",($A15-L15)/$B$4*1000,""))</f>
         <v/>
@@ -2009,8 +2009,8 @@
       <c r="P15" s="9" t="n">
         <v>0.9111</v>
       </c>
-      <c r="Q15" s="7" t="n"/>
-      <c r="R15" s="7" t="n"/>
+      <c r="Q15" s="7" t="inlineStr"/>
+      <c r="R15" s="7" t="inlineStr"/>
       <c r="S15" s="8">
         <f>IF(R15&lt;&gt;"",R15/$B$4*1000,IF(Q15&lt;&gt;"",($A15-Q15)/$B$4*1000,""))</f>
         <v/>
@@ -2026,8 +2026,8 @@
       <c r="A16" s="6" t="n">
         <v>1.5</v>
       </c>
-      <c r="B16" s="7" t="n"/>
-      <c r="C16" s="7" t="n"/>
+      <c r="B16" s="7" t="inlineStr"/>
+      <c r="C16" s="7" t="inlineStr"/>
       <c r="D16" s="8">
         <f>IF(C16&lt;&gt;"",C16/$B$4*1000,IF(B16&lt;&gt;"",($A16-B16)/$B$4*1000,""))</f>
         <v/>
@@ -2038,8 +2038,8 @@
       <c r="F16" s="9" t="n">
         <v>0.0011</v>
       </c>
-      <c r="G16" s="7" t="n"/>
-      <c r="H16" s="7" t="n"/>
+      <c r="G16" s="7" t="inlineStr"/>
+      <c r="H16" s="7" t="inlineStr"/>
       <c r="I16" s="8">
         <f>IF(H16&lt;&gt;"",H16/$B$4*1000,IF(G16&lt;&gt;"",($A16-G16)/$B$4*1000,""))</f>
         <v/>
@@ -2050,8 +2050,8 @@
       <c r="K16" s="9" t="n">
         <v>0.4207</v>
       </c>
-      <c r="L16" s="7" t="n"/>
-      <c r="M16" s="7" t="n"/>
+      <c r="L16" s="7" t="inlineStr"/>
+      <c r="M16" s="7" t="inlineStr"/>
       <c r="N16" s="8">
         <f>IF(M16&lt;&gt;"",M16/$B$4*1000,IF(L16&lt;&gt;"",($A16-L16)/$B$4*1000,""))</f>
         <v/>
@@ -2062,8 +2062,8 @@
       <c r="P16" s="9" t="n">
         <v>1.3821</v>
       </c>
-      <c r="Q16" s="7" t="n"/>
-      <c r="R16" s="7" t="n"/>
+      <c r="Q16" s="7" t="inlineStr"/>
+      <c r="R16" s="7" t="inlineStr"/>
       <c r="S16" s="8">
         <f>IF(R16&lt;&gt;"",R16/$B$4*1000,IF(Q16&lt;&gt;"",($A16-Q16)/$B$4*1000,""))</f>
         <v/>
@@ -2079,8 +2079,8 @@
       <c r="A17" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B17" s="7" t="n"/>
-      <c r="C17" s="7" t="n"/>
+      <c r="B17" s="7" t="inlineStr"/>
+      <c r="C17" s="7" t="inlineStr"/>
       <c r="D17" s="8">
         <f>IF(C17&lt;&gt;"",C17/$B$4*1000,IF(B17&lt;&gt;"",($A17-B17)/$B$4*1000,""))</f>
         <v/>
@@ -2091,8 +2091,8 @@
       <c r="F17" s="9" t="n">
         <v>0.0011</v>
       </c>
-      <c r="G17" s="7" t="n"/>
-      <c r="H17" s="7" t="n"/>
+      <c r="G17" s="7" t="inlineStr"/>
+      <c r="H17" s="7" t="inlineStr"/>
       <c r="I17" s="8">
         <f>IF(H17&lt;&gt;"",H17/$B$4*1000,IF(G17&lt;&gt;"",($A17-G17)/$B$4*1000,""))</f>
         <v/>
@@ -2103,8 +2103,8 @@
       <c r="K17" s="9" t="n">
         <v>0.4228</v>
       </c>
-      <c r="L17" s="7" t="n"/>
-      <c r="M17" s="7" t="n"/>
+      <c r="L17" s="7" t="inlineStr"/>
+      <c r="M17" s="7" t="inlineStr"/>
       <c r="N17" s="8">
         <f>IF(M17&lt;&gt;"",M17/$B$4*1000,IF(L17&lt;&gt;"",($A17-L17)/$B$4*1000,""))</f>
         <v/>
@@ -2115,8 +2115,8 @@
       <c r="P17" s="9" t="n">
         <v>1.8252</v>
       </c>
-      <c r="Q17" s="7" t="n"/>
-      <c r="R17" s="7" t="n"/>
+      <c r="Q17" s="7" t="inlineStr"/>
+      <c r="R17" s="7" t="inlineStr"/>
       <c r="S17" s="8">
         <f>IF(R17&lt;&gt;"",R17/$B$4*1000,IF(Q17&lt;&gt;"",($A17-Q17)/$B$4*1000,""))</f>
         <v/>
@@ -2132,8 +2132,8 @@
       <c r="A18" s="6" t="n">
         <v>2.5</v>
       </c>
-      <c r="B18" s="7" t="n"/>
-      <c r="C18" s="7" t="n"/>
+      <c r="B18" s="7" t="inlineStr"/>
+      <c r="C18" s="7" t="inlineStr"/>
       <c r="D18" s="8">
         <f>IF(C18&lt;&gt;"",C18/$B$4*1000,IF(B18&lt;&gt;"",($A18-B18)/$B$4*1000,""))</f>
         <v/>
@@ -2144,8 +2144,8 @@
       <c r="F18" s="9" t="n">
         <v>0.0012</v>
       </c>
-      <c r="G18" s="7" t="n"/>
-      <c r="H18" s="7" t="n"/>
+      <c r="G18" s="7" t="inlineStr"/>
+      <c r="H18" s="7" t="inlineStr"/>
       <c r="I18" s="8">
         <f>IF(H18&lt;&gt;"",H18/$B$4*1000,IF(G18&lt;&gt;"",($A18-G18)/$B$4*1000,""))</f>
         <v/>
@@ -2156,8 +2156,8 @@
       <c r="K18" s="9" t="n">
         <v>0.4249</v>
       </c>
-      <c r="L18" s="7" t="n"/>
-      <c r="M18" s="7" t="n"/>
+      <c r="L18" s="7" t="inlineStr"/>
+      <c r="M18" s="7" t="inlineStr"/>
       <c r="N18" s="8">
         <f>IF(M18&lt;&gt;"",M18/$B$4*1000,IF(L18&lt;&gt;"",($A18-L18)/$B$4*1000,""))</f>
         <v/>
@@ -2168,8 +2168,8 @@
       <c r="P18" s="9" t="n">
         <v>1.9141</v>
       </c>
-      <c r="Q18" s="7" t="n"/>
-      <c r="R18" s="7" t="n"/>
+      <c r="Q18" s="7" t="inlineStr"/>
+      <c r="R18" s="7" t="inlineStr"/>
       <c r="S18" s="8">
         <f>IF(R18&lt;&gt;"",R18/$B$4*1000,IF(Q18&lt;&gt;"",($A18-Q18)/$B$4*1000,""))</f>
         <v/>
@@ -2185,8 +2185,8 @@
       <c r="A19" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B19" s="7" t="n"/>
-      <c r="C19" s="7" t="n"/>
+      <c r="B19" s="7" t="inlineStr"/>
+      <c r="C19" s="7" t="inlineStr"/>
       <c r="D19" s="8">
         <f>IF(C19&lt;&gt;"",C19/$B$4*1000,IF(B19&lt;&gt;"",($A19-B19)/$B$4*1000,""))</f>
         <v/>
@@ -2197,8 +2197,8 @@
       <c r="F19" s="9" t="n">
         <v>0.0012</v>
       </c>
-      <c r="G19" s="7" t="n"/>
-      <c r="H19" s="7" t="n"/>
+      <c r="G19" s="7" t="inlineStr"/>
+      <c r="H19" s="7" t="inlineStr"/>
       <c r="I19" s="8">
         <f>IF(H19&lt;&gt;"",H19/$B$4*1000,IF(G19&lt;&gt;"",($A19-G19)/$B$4*1000,""))</f>
         <v/>
@@ -2209,8 +2209,8 @@
       <c r="K19" s="9" t="n">
         <v>0.4269</v>
       </c>
-      <c r="L19" s="7" t="n"/>
-      <c r="M19" s="7" t="n"/>
+      <c r="L19" s="7" t="inlineStr"/>
+      <c r="M19" s="7" t="inlineStr"/>
       <c r="N19" s="8">
         <f>IF(M19&lt;&gt;"",M19/$B$4*1000,IF(L19&lt;&gt;"",($A19-L19)/$B$4*1000,""))</f>
         <v/>
@@ -2221,8 +2221,8 @@
       <c r="P19" s="9" t="n">
         <v>1.9234</v>
       </c>
-      <c r="Q19" s="7" t="n"/>
-      <c r="R19" s="7" t="n"/>
+      <c r="Q19" s="7" t="inlineStr"/>
+      <c r="R19" s="7" t="inlineStr"/>
       <c r="S19" s="8">
         <f>IF(R19&lt;&gt;"",R19/$B$4*1000,IF(Q19&lt;&gt;"",($A19-Q19)/$B$4*1000,""))</f>
         <v/>
@@ -2238,8 +2238,8 @@
       <c r="A20" s="6" t="n">
         <v>3.5</v>
       </c>
-      <c r="B20" s="7" t="n"/>
-      <c r="C20" s="7" t="n"/>
+      <c r="B20" s="7" t="inlineStr"/>
+      <c r="C20" s="7" t="inlineStr"/>
       <c r="D20" s="8">
         <f>IF(C20&lt;&gt;"",C20/$B$4*1000,IF(B20&lt;&gt;"",($A20-B20)/$B$4*1000,""))</f>
         <v/>
@@ -2250,8 +2250,8 @@
       <c r="F20" s="9" t="n">
         <v>0.0012</v>
       </c>
-      <c r="G20" s="7" t="n"/>
-      <c r="H20" s="7" t="n"/>
+      <c r="G20" s="7" t="inlineStr"/>
+      <c r="H20" s="7" t="inlineStr"/>
       <c r="I20" s="8">
         <f>IF(H20&lt;&gt;"",H20/$B$4*1000,IF(G20&lt;&gt;"",($A20-G20)/$B$4*1000,""))</f>
         <v/>
@@ -2262,8 +2262,8 @@
       <c r="K20" s="9" t="n">
         <v>0.429</v>
       </c>
-      <c r="L20" s="7" t="n"/>
-      <c r="M20" s="7" t="n"/>
+      <c r="L20" s="7" t="inlineStr"/>
+      <c r="M20" s="7" t="inlineStr"/>
       <c r="N20" s="8">
         <f>IF(M20&lt;&gt;"",M20/$B$4*1000,IF(L20&lt;&gt;"",($A20-L20)/$B$4*1000,""))</f>
         <v/>
@@ -2274,8 +2274,8 @@
       <c r="P20" s="9" t="n">
         <v>1.9328</v>
       </c>
-      <c r="Q20" s="7" t="n"/>
-      <c r="R20" s="7" t="n"/>
+      <c r="Q20" s="7" t="inlineStr"/>
+      <c r="R20" s="7" t="inlineStr"/>
       <c r="S20" s="8">
         <f>IF(R20&lt;&gt;"",R20/$B$4*1000,IF(Q20&lt;&gt;"",($A20-Q20)/$B$4*1000,""))</f>
         <v/>
@@ -2291,8 +2291,8 @@
       <c r="A21" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B21" s="7" t="n"/>
-      <c r="C21" s="7" t="n"/>
+      <c r="B21" s="7" t="inlineStr"/>
+      <c r="C21" s="7" t="inlineStr"/>
       <c r="D21" s="8">
         <f>IF(C21&lt;&gt;"",C21/$B$4*1000,IF(B21&lt;&gt;"",($A21-B21)/$B$4*1000,""))</f>
         <v/>
@@ -2303,8 +2303,8 @@
       <c r="F21" s="9" t="n">
         <v>0.0012</v>
       </c>
-      <c r="G21" s="7" t="n"/>
-      <c r="H21" s="7" t="n"/>
+      <c r="G21" s="7" t="inlineStr"/>
+      <c r="H21" s="7" t="inlineStr"/>
       <c r="I21" s="8">
         <f>IF(H21&lt;&gt;"",H21/$B$4*1000,IF(G21&lt;&gt;"",($A21-G21)/$B$4*1000,""))</f>
         <v/>
@@ -2315,8 +2315,8 @@
       <c r="K21" s="9" t="n">
         <v>0.4311</v>
       </c>
-      <c r="L21" s="7" t="n"/>
-      <c r="M21" s="7" t="n"/>
+      <c r="L21" s="7" t="inlineStr"/>
+      <c r="M21" s="7" t="inlineStr"/>
       <c r="N21" s="8">
         <f>IF(M21&lt;&gt;"",M21/$B$4*1000,IF(L21&lt;&gt;"",($A21-L21)/$B$4*1000,""))</f>
         <v/>
@@ -2327,8 +2327,8 @@
       <c r="P21" s="9" t="n">
         <v>1.9421</v>
       </c>
-      <c r="Q21" s="7" t="n"/>
-      <c r="R21" s="7" t="n"/>
+      <c r="Q21" s="7" t="inlineStr"/>
+      <c r="R21" s="7" t="inlineStr"/>
       <c r="S21" s="8">
         <f>IF(R21&lt;&gt;"",R21/$B$4*1000,IF(Q21&lt;&gt;"",($A21-Q21)/$B$4*1000,""))</f>
         <v/>
@@ -2344,8 +2344,8 @@
       <c r="A22" s="6" t="n">
         <v>4.5</v>
       </c>
-      <c r="B22" s="7" t="n"/>
-      <c r="C22" s="7" t="n"/>
+      <c r="B22" s="7" t="inlineStr"/>
+      <c r="C22" s="7" t="inlineStr"/>
       <c r="D22" s="8">
         <f>IF(C22&lt;&gt;"",C22/$B$4*1000,IF(B22&lt;&gt;"",($A22-B22)/$B$4*1000,""))</f>
         <v/>
@@ -2356,8 +2356,8 @@
       <c r="F22" s="9" t="n">
         <v>0.0012</v>
       </c>
-      <c r="G22" s="7" t="n"/>
-      <c r="H22" s="7" t="n"/>
+      <c r="G22" s="7" t="inlineStr"/>
+      <c r="H22" s="7" t="inlineStr"/>
       <c r="I22" s="8">
         <f>IF(H22&lt;&gt;"",H22/$B$4*1000,IF(G22&lt;&gt;"",($A22-G22)/$B$4*1000,""))</f>
         <v/>
@@ -2368,8 +2368,8 @@
       <c r="K22" s="9" t="n">
         <v>0.4332</v>
       </c>
-      <c r="L22" s="7" t="n"/>
-      <c r="M22" s="7" t="n"/>
+      <c r="L22" s="7" t="inlineStr"/>
+      <c r="M22" s="7" t="inlineStr"/>
       <c r="N22" s="8">
         <f>IF(M22&lt;&gt;"",M22/$B$4*1000,IF(L22&lt;&gt;"",($A22-L22)/$B$4*1000,""))</f>
         <v/>
@@ -2380,8 +2380,8 @@
       <c r="P22" s="9" t="n">
         <v>1.9514</v>
       </c>
-      <c r="Q22" s="7" t="n"/>
-      <c r="R22" s="7" t="n"/>
+      <c r="Q22" s="7" t="inlineStr"/>
+      <c r="R22" s="7" t="inlineStr"/>
       <c r="S22" s="8">
         <f>IF(R22&lt;&gt;"",R22/$B$4*1000,IF(Q22&lt;&gt;"",($A22-Q22)/$B$4*1000,""))</f>
         <v/>
@@ -2397,8 +2397,8 @@
       <c r="A23" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B23" s="7" t="n"/>
-      <c r="C23" s="7" t="n"/>
+      <c r="B23" s="7" t="inlineStr"/>
+      <c r="C23" s="7" t="inlineStr"/>
       <c r="D23" s="8">
         <f>IF(C23&lt;&gt;"",C23/$B$4*1000,IF(B23&lt;&gt;"",($A23-B23)/$B$4*1000,""))</f>
         <v/>
@@ -2409,8 +2409,8 @@
       <c r="F23" s="9" t="n">
         <v>0.0012</v>
       </c>
-      <c r="G23" s="7" t="n"/>
-      <c r="H23" s="7" t="n"/>
+      <c r="G23" s="7" t="inlineStr"/>
+      <c r="H23" s="7" t="inlineStr"/>
       <c r="I23" s="8">
         <f>IF(H23&lt;&gt;"",H23/$B$4*1000,IF(G23&lt;&gt;"",($A23-G23)/$B$4*1000,""))</f>
         <v/>
@@ -2421,8 +2421,8 @@
       <c r="K23" s="9" t="n">
         <v>0.4353</v>
       </c>
-      <c r="L23" s="7" t="n"/>
-      <c r="M23" s="7" t="n"/>
+      <c r="L23" s="7" t="inlineStr"/>
+      <c r="M23" s="7" t="inlineStr"/>
       <c r="N23" s="8">
         <f>IF(M23&lt;&gt;"",M23/$B$4*1000,IF(L23&lt;&gt;"",($A23-L23)/$B$4*1000,""))</f>
         <v/>
@@ -2433,8 +2433,8 @@
       <c r="P23" s="9" t="n">
         <v>1.9608</v>
       </c>
-      <c r="Q23" s="7" t="n"/>
-      <c r="R23" s="7" t="n"/>
+      <c r="Q23" s="7" t="inlineStr"/>
+      <c r="R23" s="7" t="inlineStr"/>
       <c r="S23" s="8">
         <f>IF(R23&lt;&gt;"",R23/$B$4*1000,IF(Q23&lt;&gt;"",($A23-Q23)/$B$4*1000,""))</f>
         <v/>
@@ -2450,8 +2450,8 @@
       <c r="A24" s="6" t="n">
         <v>5.5</v>
       </c>
-      <c r="B24" s="7" t="n"/>
-      <c r="C24" s="7" t="n"/>
+      <c r="B24" s="7" t="inlineStr"/>
+      <c r="C24" s="7" t="inlineStr"/>
       <c r="D24" s="8">
         <f>IF(C24&lt;&gt;"",C24/$B$4*1000,IF(B24&lt;&gt;"",($A24-B24)/$B$4*1000,""))</f>
         <v/>
@@ -2462,8 +2462,8 @@
       <c r="F24" s="9" t="n">
         <v>0.0012</v>
       </c>
-      <c r="G24" s="7" t="n"/>
-      <c r="H24" s="7" t="n"/>
+      <c r="G24" s="7" t="inlineStr"/>
+      <c r="H24" s="7" t="inlineStr"/>
       <c r="I24" s="8">
         <f>IF(H24&lt;&gt;"",H24/$B$4*1000,IF(G24&lt;&gt;"",($A24-G24)/$B$4*1000,""))</f>
         <v/>
@@ -2474,8 +2474,8 @@
       <c r="K24" s="9" t="n">
         <v>0.4373</v>
       </c>
-      <c r="L24" s="7" t="n"/>
-      <c r="M24" s="7" t="n"/>
+      <c r="L24" s="7" t="inlineStr"/>
+      <c r="M24" s="7" t="inlineStr"/>
       <c r="N24" s="8">
         <f>IF(M24&lt;&gt;"",M24/$B$4*1000,IF(L24&lt;&gt;"",($A24-L24)/$B$4*1000,""))</f>
         <v/>
@@ -2486,8 +2486,8 @@
       <c r="P24" s="9" t="n">
         <v>1.9701</v>
       </c>
-      <c r="Q24" s="7" t="n"/>
-      <c r="R24" s="7" t="n"/>
+      <c r="Q24" s="7" t="inlineStr"/>
+      <c r="R24" s="7" t="inlineStr"/>
       <c r="S24" s="8">
         <f>IF(R24&lt;&gt;"",R24/$B$4*1000,IF(Q24&lt;&gt;"",($A24-Q24)/$B$4*1000,""))</f>
         <v/>
@@ -2503,8 +2503,8 @@
       <c r="A25" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B25" s="7" t="n"/>
-      <c r="C25" s="7" t="n"/>
+      <c r="B25" s="7" t="inlineStr"/>
+      <c r="C25" s="7" t="inlineStr"/>
       <c r="D25" s="8">
         <f>IF(C25&lt;&gt;"",C25/$B$4*1000,IF(B25&lt;&gt;"",($A25-B25)/$B$4*1000,""))</f>
         <v/>
@@ -2515,8 +2515,8 @@
       <c r="F25" s="9" t="n">
         <v>0.0012</v>
       </c>
-      <c r="G25" s="7" t="n"/>
-      <c r="H25" s="7" t="n"/>
+      <c r="G25" s="7" t="inlineStr"/>
+      <c r="H25" s="7" t="inlineStr"/>
       <c r="I25" s="8">
         <f>IF(H25&lt;&gt;"",H25/$B$4*1000,IF(G25&lt;&gt;"",($A25-G25)/$B$4*1000,""))</f>
         <v/>
@@ -2527,8 +2527,8 @@
       <c r="K25" s="9" t="n">
         <v>0.4394</v>
       </c>
-      <c r="L25" s="7" t="n"/>
-      <c r="M25" s="7" t="n"/>
+      <c r="L25" s="7" t="inlineStr"/>
+      <c r="M25" s="7" t="inlineStr"/>
       <c r="N25" s="8">
         <f>IF(M25&lt;&gt;"",M25/$B$4*1000,IF(L25&lt;&gt;"",($A25-L25)/$B$4*1000,""))</f>
         <v/>
@@ -2539,8 +2539,8 @@
       <c r="P25" s="9" t="n">
         <v>1.9794</v>
       </c>
-      <c r="Q25" s="7" t="n"/>
-      <c r="R25" s="7" t="n"/>
+      <c r="Q25" s="7" t="inlineStr"/>
+      <c r="R25" s="7" t="inlineStr"/>
       <c r="S25" s="8">
         <f>IF(R25&lt;&gt;"",R25/$B$4*1000,IF(Q25&lt;&gt;"",($A25-Q25)/$B$4*1000,""))</f>
         <v/>
@@ -2556,8 +2556,8 @@
       <c r="A26" s="6" t="n">
         <v>6.5</v>
       </c>
-      <c r="B26" s="7" t="n"/>
-      <c r="C26" s="7" t="n"/>
+      <c r="B26" s="7" t="inlineStr"/>
+      <c r="C26" s="7" t="inlineStr"/>
       <c r="D26" s="8">
         <f>IF(C26&lt;&gt;"",C26/$B$4*1000,IF(B26&lt;&gt;"",($A26-B26)/$B$4*1000,""))</f>
         <v/>
@@ -2568,8 +2568,8 @@
       <c r="F26" s="9" t="n">
         <v>0.0012</v>
       </c>
-      <c r="G26" s="7" t="n"/>
-      <c r="H26" s="7" t="n"/>
+      <c r="G26" s="7" t="inlineStr"/>
+      <c r="H26" s="7" t="inlineStr"/>
       <c r="I26" s="8">
         <f>IF(H26&lt;&gt;"",H26/$B$4*1000,IF(G26&lt;&gt;"",($A26-G26)/$B$4*1000,""))</f>
         <v/>
@@ -2580,8 +2580,8 @@
       <c r="K26" s="9" t="n">
         <v>0.4415</v>
       </c>
-      <c r="L26" s="7" t="n"/>
-      <c r="M26" s="7" t="n"/>
+      <c r="L26" s="7" t="inlineStr"/>
+      <c r="M26" s="7" t="inlineStr"/>
       <c r="N26" s="8">
         <f>IF(M26&lt;&gt;"",M26/$B$4*1000,IF(L26&lt;&gt;"",($A26-L26)/$B$4*1000,""))</f>
         <v/>
@@ -2592,8 +2592,8 @@
       <c r="P26" s="9" t="n">
         <v>1.9888</v>
       </c>
-      <c r="Q26" s="7" t="n"/>
-      <c r="R26" s="7" t="n"/>
+      <c r="Q26" s="7" t="inlineStr"/>
+      <c r="R26" s="7" t="inlineStr"/>
       <c r="S26" s="8">
         <f>IF(R26&lt;&gt;"",R26/$B$4*1000,IF(Q26&lt;&gt;"",($A26-Q26)/$B$4*1000,""))</f>
         <v/>
@@ -2609,8 +2609,8 @@
       <c r="A27" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B27" s="7" t="n"/>
-      <c r="C27" s="7" t="n"/>
+      <c r="B27" s="7" t="inlineStr"/>
+      <c r="C27" s="7" t="inlineStr"/>
       <c r="D27" s="8">
         <f>IF(C27&lt;&gt;"",C27/$B$4*1000,IF(B27&lt;&gt;"",($A27-B27)/$B$4*1000,""))</f>
         <v/>
@@ -2621,8 +2621,8 @@
       <c r="F27" s="9" t="n">
         <v>0.0012</v>
       </c>
-      <c r="G27" s="7" t="n"/>
-      <c r="H27" s="7" t="n"/>
+      <c r="G27" s="7" t="inlineStr"/>
+      <c r="H27" s="7" t="inlineStr"/>
       <c r="I27" s="8">
         <f>IF(H27&lt;&gt;"",H27/$B$4*1000,IF(G27&lt;&gt;"",($A27-G27)/$B$4*1000,""))</f>
         <v/>
@@ -2633,8 +2633,8 @@
       <c r="K27" s="9" t="n">
         <v>0.4436</v>
       </c>
-      <c r="L27" s="7" t="n"/>
-      <c r="M27" s="7" t="n"/>
+      <c r="L27" s="7" t="inlineStr"/>
+      <c r="M27" s="7" t="inlineStr"/>
       <c r="N27" s="8">
         <f>IF(M27&lt;&gt;"",M27/$B$4*1000,IF(L27&lt;&gt;"",($A27-L27)/$B$4*1000,""))</f>
         <v/>
@@ -2645,8 +2645,8 @@
       <c r="P27" s="9" t="n">
         <v>1.9981</v>
       </c>
-      <c r="Q27" s="7" t="n"/>
-      <c r="R27" s="7" t="n"/>
+      <c r="Q27" s="7" t="inlineStr"/>
+      <c r="R27" s="7" t="inlineStr"/>
       <c r="S27" s="8">
         <f>IF(R27&lt;&gt;"",R27/$B$4*1000,IF(Q27&lt;&gt;"",($A27-Q27)/$B$4*1000,""))</f>
         <v/>
@@ -2662,8 +2662,8 @@
       <c r="A28" s="6" t="n">
         <v>7.5</v>
       </c>
-      <c r="B28" s="7" t="n"/>
-      <c r="C28" s="7" t="n"/>
+      <c r="B28" s="7" t="inlineStr"/>
+      <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="8">
         <f>IF(C28&lt;&gt;"",C28/$B$4*1000,IF(B28&lt;&gt;"",($A28-B28)/$B$4*1000,""))</f>
         <v/>
@@ -2674,8 +2674,8 @@
       <c r="F28" s="9" t="n">
         <v>0.0012</v>
       </c>
-      <c r="G28" s="7" t="n"/>
-      <c r="H28" s="7" t="n"/>
+      <c r="G28" s="7" t="inlineStr"/>
+      <c r="H28" s="7" t="inlineStr"/>
       <c r="I28" s="8">
         <f>IF(H28&lt;&gt;"",H28/$B$4*1000,IF(G28&lt;&gt;"",($A28-G28)/$B$4*1000,""))</f>
         <v/>
@@ -2686,8 +2686,8 @@
       <c r="K28" s="9" t="n">
         <v>0.4457</v>
       </c>
-      <c r="L28" s="7" t="n"/>
-      <c r="M28" s="7" t="n"/>
+      <c r="L28" s="7" t="inlineStr"/>
+      <c r="M28" s="7" t="inlineStr"/>
       <c r="N28" s="8">
         <f>IF(M28&lt;&gt;"",M28/$B$4*1000,IF(L28&lt;&gt;"",($A28-L28)/$B$4*1000,""))</f>
         <v/>
@@ -2698,8 +2698,8 @@
       <c r="P28" s="9" t="n">
         <v>2.0074</v>
       </c>
-      <c r="Q28" s="7" t="n"/>
-      <c r="R28" s="7" t="n"/>
+      <c r="Q28" s="7" t="inlineStr"/>
+      <c r="R28" s="7" t="inlineStr"/>
       <c r="S28" s="8">
         <f>IF(R28&lt;&gt;"",R28/$B$4*1000,IF(Q28&lt;&gt;"",($A28-Q28)/$B$4*1000,""))</f>
         <v/>
@@ -2715,8 +2715,8 @@
       <c r="A29" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B29" s="7" t="n"/>
-      <c r="C29" s="7" t="n"/>
+      <c r="B29" s="7" t="inlineStr"/>
+      <c r="C29" s="7" t="inlineStr"/>
       <c r="D29" s="8">
         <f>IF(C29&lt;&gt;"",C29/$B$4*1000,IF(B29&lt;&gt;"",($A29-B29)/$B$4*1000,""))</f>
         <v/>
@@ -2727,8 +2727,8 @@
       <c r="F29" s="9" t="n">
         <v>0.0012</v>
       </c>
-      <c r="G29" s="7" t="n"/>
-      <c r="H29" s="7" t="n"/>
+      <c r="G29" s="7" t="inlineStr"/>
+      <c r="H29" s="7" t="inlineStr"/>
       <c r="I29" s="8">
         <f>IF(H29&lt;&gt;"",H29/$B$4*1000,IF(G29&lt;&gt;"",($A29-G29)/$B$4*1000,""))</f>
         <v/>
@@ -2739,8 +2739,8 @@
       <c r="K29" s="9" t="n">
         <v>0.4477</v>
       </c>
-      <c r="L29" s="7" t="n"/>
-      <c r="M29" s="7" t="n"/>
+      <c r="L29" s="7" t="inlineStr"/>
+      <c r="M29" s="7" t="inlineStr"/>
       <c r="N29" s="8">
         <f>IF(M29&lt;&gt;"",M29/$B$4*1000,IF(L29&lt;&gt;"",($A29-L29)/$B$4*1000,""))</f>
         <v/>
@@ -2751,8 +2751,8 @@
       <c r="P29" s="9" t="n">
         <v>2.0168</v>
       </c>
-      <c r="Q29" s="7" t="n"/>
-      <c r="R29" s="7" t="n"/>
+      <c r="Q29" s="7" t="inlineStr"/>
+      <c r="R29" s="7" t="inlineStr"/>
       <c r="S29" s="8">
         <f>IF(R29&lt;&gt;"",R29/$B$4*1000,IF(Q29&lt;&gt;"",($A29-Q29)/$B$4*1000,""))</f>
         <v/>
@@ -2768,8 +2768,8 @@
       <c r="A30" s="6" t="n">
         <v>8.5</v>
       </c>
-      <c r="B30" s="7" t="n"/>
-      <c r="C30" s="7" t="n"/>
+      <c r="B30" s="7" t="inlineStr"/>
+      <c r="C30" s="7" t="inlineStr"/>
       <c r="D30" s="8">
         <f>IF(C30&lt;&gt;"",C30/$B$4*1000,IF(B30&lt;&gt;"",($A30-B30)/$B$4*1000,""))</f>
         <v/>
@@ -2780,8 +2780,8 @@
       <c r="F30" s="9" t="n">
         <v>0.0012</v>
       </c>
-      <c r="G30" s="7" t="n"/>
-      <c r="H30" s="7" t="n"/>
+      <c r="G30" s="7" t="inlineStr"/>
+      <c r="H30" s="7" t="inlineStr"/>
       <c r="I30" s="8">
         <f>IF(H30&lt;&gt;"",H30/$B$4*1000,IF(G30&lt;&gt;"",($A30-G30)/$B$4*1000,""))</f>
         <v/>
@@ -2792,8 +2792,8 @@
       <c r="K30" s="9" t="n">
         <v>0.4498</v>
       </c>
-      <c r="L30" s="7" t="n"/>
-      <c r="M30" s="7" t="n"/>
+      <c r="L30" s="7" t="inlineStr"/>
+      <c r="M30" s="7" t="inlineStr"/>
       <c r="N30" s="8">
         <f>IF(M30&lt;&gt;"",M30/$B$4*1000,IF(L30&lt;&gt;"",($A30-L30)/$B$4*1000,""))</f>
         <v/>
@@ -2804,8 +2804,8 @@
       <c r="P30" s="9" t="n">
         <v>2.0261</v>
       </c>
-      <c r="Q30" s="7" t="n"/>
-      <c r="R30" s="7" t="n"/>
+      <c r="Q30" s="7" t="inlineStr"/>
+      <c r="R30" s="7" t="inlineStr"/>
       <c r="S30" s="8">
         <f>IF(R30&lt;&gt;"",R30/$B$4*1000,IF(Q30&lt;&gt;"",($A30-Q30)/$B$4*1000,""))</f>
         <v/>
@@ -2821,8 +2821,8 @@
       <c r="A31" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="B31" s="7" t="n"/>
-      <c r="C31" s="7" t="n"/>
+      <c r="B31" s="7" t="inlineStr"/>
+      <c r="C31" s="7" t="inlineStr"/>
       <c r="D31" s="8">
         <f>IF(C31&lt;&gt;"",C31/$B$4*1000,IF(B31&lt;&gt;"",($A31-B31)/$B$4*1000,""))</f>
         <v/>
@@ -2833,8 +2833,8 @@
       <c r="F31" s="9" t="n">
         <v>0.0012</v>
       </c>
-      <c r="G31" s="7" t="n"/>
-      <c r="H31" s="7" t="n"/>
+      <c r="G31" s="7" t="inlineStr"/>
+      <c r="H31" s="7" t="inlineStr"/>
       <c r="I31" s="8">
         <f>IF(H31&lt;&gt;"",H31/$B$4*1000,IF(G31&lt;&gt;"",($A31-G31)/$B$4*1000,""))</f>
         <v/>
@@ -2845,8 +2845,8 @@
       <c r="K31" s="9" t="n">
         <v>0.4519</v>
       </c>
-      <c r="L31" s="7" t="n"/>
-      <c r="M31" s="7" t="n"/>
+      <c r="L31" s="7" t="inlineStr"/>
+      <c r="M31" s="7" t="inlineStr"/>
       <c r="N31" s="8">
         <f>IF(M31&lt;&gt;"",M31/$B$4*1000,IF(L31&lt;&gt;"",($A31-L31)/$B$4*1000,""))</f>
         <v/>
@@ -2857,8 +2857,8 @@
       <c r="P31" s="9" t="n">
         <v>2.0354</v>
       </c>
-      <c r="Q31" s="7" t="n"/>
-      <c r="R31" s="7" t="n"/>
+      <c r="Q31" s="7" t="inlineStr"/>
+      <c r="R31" s="7" t="inlineStr"/>
       <c r="S31" s="8">
         <f>IF(R31&lt;&gt;"",R31/$B$4*1000,IF(Q31&lt;&gt;"",($A31-Q31)/$B$4*1000,""))</f>
         <v/>
@@ -2874,8 +2874,8 @@
       <c r="A32" s="6" t="n">
         <v>9.5</v>
       </c>
-      <c r="B32" s="7" t="n"/>
-      <c r="C32" s="7" t="n"/>
+      <c r="B32" s="7" t="inlineStr"/>
+      <c r="C32" s="7" t="inlineStr"/>
       <c r="D32" s="8">
         <f>IF(C32&lt;&gt;"",C32/$B$4*1000,IF(B32&lt;&gt;"",($A32-B32)/$B$4*1000,""))</f>
         <v/>
@@ -2886,8 +2886,8 @@
       <c r="F32" s="9" t="n">
         <v>0.0012</v>
       </c>
-      <c r="G32" s="7" t="n"/>
-      <c r="H32" s="7" t="n"/>
+      <c r="G32" s="7" t="inlineStr"/>
+      <c r="H32" s="7" t="inlineStr"/>
       <c r="I32" s="8">
         <f>IF(H32&lt;&gt;"",H32/$B$4*1000,IF(G32&lt;&gt;"",($A32-G32)/$B$4*1000,""))</f>
         <v/>
@@ -2898,8 +2898,8 @@
       <c r="K32" s="9" t="n">
         <v>0.454</v>
       </c>
-      <c r="L32" s="7" t="n"/>
-      <c r="M32" s="7" t="n"/>
+      <c r="L32" s="7" t="inlineStr"/>
+      <c r="M32" s="7" t="inlineStr"/>
       <c r="N32" s="8">
         <f>IF(M32&lt;&gt;"",M32/$B$4*1000,IF(L32&lt;&gt;"",($A32-L32)/$B$4*1000,""))</f>
         <v/>
@@ -2910,8 +2910,8 @@
       <c r="P32" s="9" t="n">
         <v>2.0448</v>
       </c>
-      <c r="Q32" s="7" t="n"/>
-      <c r="R32" s="7" t="n"/>
+      <c r="Q32" s="7" t="inlineStr"/>
+      <c r="R32" s="7" t="inlineStr"/>
       <c r="S32" s="8">
         <f>IF(R32&lt;&gt;"",R32/$B$4*1000,IF(Q32&lt;&gt;"",($A32-Q32)/$B$4*1000,""))</f>
         <v/>
@@ -2927,8 +2927,8 @@
       <c r="A33" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B33" s="7" t="n"/>
-      <c r="C33" s="7" t="n"/>
+      <c r="B33" s="7" t="inlineStr"/>
+      <c r="C33" s="7" t="inlineStr"/>
       <c r="D33" s="8">
         <f>IF(C33&lt;&gt;"",C33/$B$4*1000,IF(B33&lt;&gt;"",($A33-B33)/$B$4*1000,""))</f>
         <v/>
@@ -2939,8 +2939,8 @@
       <c r="F33" s="9" t="n">
         <v>0.0012</v>
       </c>
-      <c r="G33" s="7" t="n"/>
-      <c r="H33" s="7" t="n"/>
+      <c r="G33" s="7" t="inlineStr"/>
+      <c r="H33" s="7" t="inlineStr"/>
       <c r="I33" s="8">
         <f>IF(H33&lt;&gt;"",H33/$B$4*1000,IF(G33&lt;&gt;"",($A33-G33)/$B$4*1000,""))</f>
         <v/>
@@ -2951,8 +2951,8 @@
       <c r="K33" s="9" t="n">
         <v>0.4561</v>
       </c>
-      <c r="L33" s="7" t="n"/>
-      <c r="M33" s="7" t="n"/>
+      <c r="L33" s="7" t="inlineStr"/>
+      <c r="M33" s="7" t="inlineStr"/>
       <c r="N33" s="8">
         <f>IF(M33&lt;&gt;"",M33/$B$4*1000,IF(L33&lt;&gt;"",($A33-L33)/$B$4*1000,""))</f>
         <v/>
@@ -2963,8 +2963,8 @@
       <c r="P33" s="9" t="n">
         <v>2.0541</v>
       </c>
-      <c r="Q33" s="7" t="n"/>
-      <c r="R33" s="7" t="n"/>
+      <c r="Q33" s="7" t="inlineStr"/>
+      <c r="R33" s="7" t="inlineStr"/>
       <c r="S33" s="8">
         <f>IF(R33&lt;&gt;"",R33/$B$4*1000,IF(Q33&lt;&gt;"",($A33-Q33)/$B$4*1000,""))</f>
         <v/>
@@ -2980,8 +2980,8 @@
       <c r="A34" s="6" t="n">
         <v>10.5</v>
       </c>
-      <c r="B34" s="7" t="n"/>
-      <c r="C34" s="7" t="n"/>
+      <c r="B34" s="7" t="inlineStr"/>
+      <c r="C34" s="7" t="inlineStr"/>
       <c r="D34" s="8">
         <f>IF(C34&lt;&gt;"",C34/$B$4*1000,IF(B34&lt;&gt;"",($A34-B34)/$B$4*1000,""))</f>
         <v/>
@@ -2992,8 +2992,8 @@
       <c r="F34" s="9" t="n">
         <v>0.0012</v>
       </c>
-      <c r="G34" s="7" t="n"/>
-      <c r="H34" s="7" t="n"/>
+      <c r="G34" s="7" t="inlineStr"/>
+      <c r="H34" s="7" t="inlineStr"/>
       <c r="I34" s="8">
         <f>IF(H34&lt;&gt;"",H34/$B$4*1000,IF(G34&lt;&gt;"",($A34-G34)/$B$4*1000,""))</f>
         <v/>
@@ -3004,8 +3004,8 @@
       <c r="K34" s="9" t="n">
         <v>0.4581</v>
       </c>
-      <c r="L34" s="7" t="n"/>
-      <c r="M34" s="7" t="n"/>
+      <c r="L34" s="7" t="inlineStr"/>
+      <c r="M34" s="7" t="inlineStr"/>
       <c r="N34" s="8">
         <f>IF(M34&lt;&gt;"",M34/$B$4*1000,IF(L34&lt;&gt;"",($A34-L34)/$B$4*1000,""))</f>
         <v/>
@@ -3016,8 +3016,8 @@
       <c r="P34" s="9" t="n">
         <v>2.0634</v>
       </c>
-      <c r="Q34" s="7" t="n"/>
-      <c r="R34" s="7" t="n"/>
+      <c r="Q34" s="7" t="inlineStr"/>
+      <c r="R34" s="7" t="inlineStr"/>
       <c r="S34" s="8">
         <f>IF(R34&lt;&gt;"",R34/$B$4*1000,IF(Q34&lt;&gt;"",($A34-Q34)/$B$4*1000,""))</f>
         <v/>
@@ -3033,8 +3033,8 @@
       <c r="A35" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B35" s="7" t="n"/>
-      <c r="C35" s="7" t="n"/>
+      <c r="B35" s="7" t="inlineStr"/>
+      <c r="C35" s="7" t="inlineStr"/>
       <c r="D35" s="8">
         <f>IF(C35&lt;&gt;"",C35/$B$4*1000,IF(B35&lt;&gt;"",($A35-B35)/$B$4*1000,""))</f>
         <v/>
@@ -3045,8 +3045,8 @@
       <c r="F35" s="9" t="n">
         <v>0.0012</v>
       </c>
-      <c r="G35" s="7" t="n"/>
-      <c r="H35" s="7" t="n"/>
+      <c r="G35" s="7" t="inlineStr"/>
+      <c r="H35" s="7" t="inlineStr"/>
       <c r="I35" s="8">
         <f>IF(H35&lt;&gt;"",H35/$B$4*1000,IF(G35&lt;&gt;"",($A35-G35)/$B$4*1000,""))</f>
         <v/>
@@ -3057,8 +3057,8 @@
       <c r="K35" s="9" t="n">
         <v>0.4602</v>
       </c>
-      <c r="L35" s="7" t="n"/>
-      <c r="M35" s="7" t="n"/>
+      <c r="L35" s="7" t="inlineStr"/>
+      <c r="M35" s="7" t="inlineStr"/>
       <c r="N35" s="8">
         <f>IF(M35&lt;&gt;"",M35/$B$4*1000,IF(L35&lt;&gt;"",($A35-L35)/$B$4*1000,""))</f>
         <v/>
@@ -3069,8 +3069,8 @@
       <c r="P35" s="9" t="n">
         <v>2.0727</v>
       </c>
-      <c r="Q35" s="7" t="n"/>
-      <c r="R35" s="7" t="n"/>
+      <c r="Q35" s="7" t="inlineStr"/>
+      <c r="R35" s="7" t="inlineStr"/>
       <c r="S35" s="8">
         <f>IF(R35&lt;&gt;"",R35/$B$4*1000,IF(Q35&lt;&gt;"",($A35-Q35)/$B$4*1000,""))</f>
         <v/>
@@ -3086,8 +3086,8 @@
       <c r="A36" s="6" t="n">
         <v>11.5</v>
       </c>
-      <c r="B36" s="7" t="n"/>
-      <c r="C36" s="7" t="n"/>
+      <c r="B36" s="7" t="inlineStr"/>
+      <c r="C36" s="7" t="inlineStr"/>
       <c r="D36" s="8">
         <f>IF(C36&lt;&gt;"",C36/$B$4*1000,IF(B36&lt;&gt;"",($A36-B36)/$B$4*1000,""))</f>
         <v/>
@@ -3098,8 +3098,8 @@
       <c r="F36" s="9" t="n">
         <v>0.0013</v>
       </c>
-      <c r="G36" s="7" t="n"/>
-      <c r="H36" s="7" t="n"/>
+      <c r="G36" s="7" t="inlineStr"/>
+      <c r="H36" s="7" t="inlineStr"/>
       <c r="I36" s="8">
         <f>IF(H36&lt;&gt;"",H36/$B$4*1000,IF(G36&lt;&gt;"",($A36-G36)/$B$4*1000,""))</f>
         <v/>
@@ -3110,8 +3110,8 @@
       <c r="K36" s="9" t="n">
         <v>0.4623</v>
       </c>
-      <c r="L36" s="7" t="n"/>
-      <c r="M36" s="7" t="n"/>
+      <c r="L36" s="7" t="inlineStr"/>
+      <c r="M36" s="7" t="inlineStr"/>
       <c r="N36" s="8">
         <f>IF(M36&lt;&gt;"",M36/$B$4*1000,IF(L36&lt;&gt;"",($A36-L36)/$B$4*1000,""))</f>
         <v/>
@@ -3122,8 +3122,8 @@
       <c r="P36" s="9" t="n">
         <v>2.0821</v>
       </c>
-      <c r="Q36" s="7" t="n"/>
-      <c r="R36" s="7" t="n"/>
+      <c r="Q36" s="7" t="inlineStr"/>
+      <c r="R36" s="7" t="inlineStr"/>
       <c r="S36" s="8">
         <f>IF(R36&lt;&gt;"",R36/$B$4*1000,IF(Q36&lt;&gt;"",($A36-Q36)/$B$4*1000,""))</f>
         <v/>
@@ -3139,8 +3139,8 @@
       <c r="A37" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="B37" s="7" t="n"/>
-      <c r="C37" s="7" t="n"/>
+      <c r="B37" s="7" t="inlineStr"/>
+      <c r="C37" s="7" t="inlineStr"/>
       <c r="D37" s="8">
         <f>IF(C37&lt;&gt;"",C37/$B$4*1000,IF(B37&lt;&gt;"",($A37-B37)/$B$4*1000,""))</f>
         <v/>
@@ -3151,8 +3151,8 @@
       <c r="F37" s="9" t="n">
         <v>0.0013</v>
       </c>
-      <c r="G37" s="7" t="n"/>
-      <c r="H37" s="7" t="n"/>
+      <c r="G37" s="7" t="inlineStr"/>
+      <c r="H37" s="7" t="inlineStr"/>
       <c r="I37" s="8">
         <f>IF(H37&lt;&gt;"",H37/$B$4*1000,IF(G37&lt;&gt;"",($A37-G37)/$B$4*1000,""))</f>
         <v/>
@@ -3163,8 +3163,8 @@
       <c r="K37" s="9" t="n">
         <v>0.4644</v>
       </c>
-      <c r="L37" s="7" t="n"/>
-      <c r="M37" s="7" t="n"/>
+      <c r="L37" s="7" t="inlineStr"/>
+      <c r="M37" s="7" t="inlineStr"/>
       <c r="N37" s="8">
         <f>IF(M37&lt;&gt;"",M37/$B$4*1000,IF(L37&lt;&gt;"",($A37-L37)/$B$4*1000,""))</f>
         <v/>
@@ -3175,8 +3175,8 @@
       <c r="P37" s="9" t="n">
         <v>2.0914</v>
       </c>
-      <c r="Q37" s="7" t="n"/>
-      <c r="R37" s="7" t="n"/>
+      <c r="Q37" s="7" t="inlineStr"/>
+      <c r="R37" s="7" t="inlineStr"/>
       <c r="S37" s="8">
         <f>IF(R37&lt;&gt;"",R37/$B$4*1000,IF(Q37&lt;&gt;"",($A37-Q37)/$B$4*1000,""))</f>
         <v/>
@@ -3192,8 +3192,8 @@
       <c r="A38" s="6" t="n">
         <v>12.5</v>
       </c>
-      <c r="B38" s="7" t="n"/>
-      <c r="C38" s="7" t="n"/>
+      <c r="B38" s="7" t="inlineStr"/>
+      <c r="C38" s="7" t="inlineStr"/>
       <c r="D38" s="8">
         <f>IF(C38&lt;&gt;"",C38/$B$4*1000,IF(B38&lt;&gt;"",($A38-B38)/$B$4*1000,""))</f>
         <v/>
@@ -3204,8 +3204,8 @@
       <c r="F38" s="9" t="n">
         <v>0.0013</v>
       </c>
-      <c r="G38" s="7" t="n"/>
-      <c r="H38" s="7" t="n"/>
+      <c r="G38" s="7" t="inlineStr"/>
+      <c r="H38" s="7" t="inlineStr"/>
       <c r="I38" s="8">
         <f>IF(H38&lt;&gt;"",H38/$B$4*1000,IF(G38&lt;&gt;"",($A38-G38)/$B$4*1000,""))</f>
         <v/>
@@ -3216,8 +3216,8 @@
       <c r="K38" s="9" t="n">
         <v>0.4665</v>
       </c>
-      <c r="L38" s="7" t="n"/>
-      <c r="M38" s="7" t="n"/>
+      <c r="L38" s="7" t="inlineStr"/>
+      <c r="M38" s="7" t="inlineStr"/>
       <c r="N38" s="8">
         <f>IF(M38&lt;&gt;"",M38/$B$4*1000,IF(L38&lt;&gt;"",($A38-L38)/$B$4*1000,""))</f>
         <v/>
@@ -3228,8 +3228,8 @@
       <c r="P38" s="9" t="n">
         <v>2.1007</v>
       </c>
-      <c r="Q38" s="7" t="n"/>
-      <c r="R38" s="7" t="n"/>
+      <c r="Q38" s="7" t="inlineStr"/>
+      <c r="R38" s="7" t="inlineStr"/>
       <c r="S38" s="8">
         <f>IF(R38&lt;&gt;"",R38/$B$4*1000,IF(Q38&lt;&gt;"",($A38-Q38)/$B$4*1000,""))</f>
         <v/>
@@ -3245,8 +3245,8 @@
       <c r="A39" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="B39" s="7" t="n"/>
-      <c r="C39" s="7" t="n"/>
+      <c r="B39" s="7" t="inlineStr"/>
+      <c r="C39" s="7" t="inlineStr"/>
       <c r="D39" s="8">
         <f>IF(C39&lt;&gt;"",C39/$B$4*1000,IF(B39&lt;&gt;"",($A39-B39)/$B$4*1000,""))</f>
         <v/>
@@ -3257,8 +3257,8 @@
       <c r="F39" s="9" t="n">
         <v>0.0013</v>
       </c>
-      <c r="G39" s="7" t="n"/>
-      <c r="H39" s="7" t="n"/>
+      <c r="G39" s="7" t="inlineStr"/>
+      <c r="H39" s="7" t="inlineStr"/>
       <c r="I39" s="8">
         <f>IF(H39&lt;&gt;"",H39/$B$4*1000,IF(G39&lt;&gt;"",($A39-G39)/$B$4*1000,""))</f>
         <v/>
@@ -3269,8 +3269,8 @@
       <c r="K39" s="9" t="n">
         <v>0.4685</v>
       </c>
-      <c r="L39" s="7" t="n"/>
-      <c r="M39" s="7" t="n"/>
+      <c r="L39" s="7" t="inlineStr"/>
+      <c r="M39" s="7" t="inlineStr"/>
       <c r="N39" s="8">
         <f>IF(M39&lt;&gt;"",M39/$B$4*1000,IF(L39&lt;&gt;"",($A39-L39)/$B$4*1000,""))</f>
         <v/>
@@ -3281,8 +3281,8 @@
       <c r="P39" s="9" t="n">
         <v>2.11</v>
       </c>
-      <c r="Q39" s="7" t="n"/>
-      <c r="R39" s="7" t="n"/>
+      <c r="Q39" s="7" t="inlineStr"/>
+      <c r="R39" s="7" t="inlineStr"/>
       <c r="S39" s="8">
         <f>IF(R39&lt;&gt;"",R39/$B$4*1000,IF(Q39&lt;&gt;"",($A39-Q39)/$B$4*1000,""))</f>
         <v/>
@@ -3298,8 +3298,8 @@
       <c r="A40" s="6" t="n">
         <v>13.5</v>
       </c>
-      <c r="B40" s="7" t="n"/>
-      <c r="C40" s="7" t="n"/>
+      <c r="B40" s="7" t="inlineStr"/>
+      <c r="C40" s="7" t="inlineStr"/>
       <c r="D40" s="8">
         <f>IF(C40&lt;&gt;"",C40/$B$4*1000,IF(B40&lt;&gt;"",($A40-B40)/$B$4*1000,""))</f>
         <v/>
@@ -3310,8 +3310,8 @@
       <c r="F40" s="9" t="n">
         <v>0.0013</v>
       </c>
-      <c r="G40" s="7" t="n"/>
-      <c r="H40" s="7" t="n"/>
+      <c r="G40" s="7" t="inlineStr"/>
+      <c r="H40" s="7" t="inlineStr"/>
       <c r="I40" s="8">
         <f>IF(H40&lt;&gt;"",H40/$B$4*1000,IF(G40&lt;&gt;"",($A40-G40)/$B$4*1000,""))</f>
         <v/>
@@ -3322,8 +3322,8 @@
       <c r="K40" s="9" t="n">
         <v>0.4706</v>
       </c>
-      <c r="L40" s="7" t="n"/>
-      <c r="M40" s="7" t="n"/>
+      <c r="L40" s="7" t="inlineStr"/>
+      <c r="M40" s="7" t="inlineStr"/>
       <c r="N40" s="8">
         <f>IF(M40&lt;&gt;"",M40/$B$4*1000,IF(L40&lt;&gt;"",($A40-L40)/$B$4*1000,""))</f>
         <v/>
@@ -3334,8 +3334,8 @@
       <c r="P40" s="9" t="n">
         <v>2.1194</v>
       </c>
-      <c r="Q40" s="7" t="n"/>
-      <c r="R40" s="7" t="n"/>
+      <c r="Q40" s="7" t="inlineStr"/>
+      <c r="R40" s="7" t="inlineStr"/>
       <c r="S40" s="8">
         <f>IF(R40&lt;&gt;"",R40/$B$4*1000,IF(Q40&lt;&gt;"",($A40-Q40)/$B$4*1000,""))</f>
         <v/>
@@ -3351,8 +3351,8 @@
       <c r="A41" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="B41" s="7" t="n"/>
-      <c r="C41" s="7" t="n"/>
+      <c r="B41" s="7" t="inlineStr"/>
+      <c r="C41" s="7" t="inlineStr"/>
       <c r="D41" s="8">
         <f>IF(C41&lt;&gt;"",C41/$B$4*1000,IF(B41&lt;&gt;"",($A41-B41)/$B$4*1000,""))</f>
         <v/>
@@ -3363,8 +3363,8 @@
       <c r="F41" s="9" t="n">
         <v>0.0013</v>
       </c>
-      <c r="G41" s="7" t="n"/>
-      <c r="H41" s="7" t="n"/>
+      <c r="G41" s="7" t="inlineStr"/>
+      <c r="H41" s="7" t="inlineStr"/>
       <c r="I41" s="8">
         <f>IF(H41&lt;&gt;"",H41/$B$4*1000,IF(G41&lt;&gt;"",($A41-G41)/$B$4*1000,""))</f>
         <v/>
@@ -3375,8 +3375,8 @@
       <c r="K41" s="9" t="n">
         <v>0.4727</v>
       </c>
-      <c r="L41" s="7" t="n"/>
-      <c r="M41" s="7" t="n"/>
+      <c r="L41" s="7" t="inlineStr"/>
+      <c r="M41" s="7" t="inlineStr"/>
       <c r="N41" s="8">
         <f>IF(M41&lt;&gt;"",M41/$B$4*1000,IF(L41&lt;&gt;"",($A41-L41)/$B$4*1000,""))</f>
         <v/>
@@ -3387,8 +3387,8 @@
       <c r="P41" s="9" t="n">
         <v>2.1287</v>
       </c>
-      <c r="Q41" s="7" t="n"/>
-      <c r="R41" s="7" t="n"/>
+      <c r="Q41" s="7" t="inlineStr"/>
+      <c r="R41" s="7" t="inlineStr"/>
       <c r="S41" s="8">
         <f>IF(R41&lt;&gt;"",R41/$B$4*1000,IF(Q41&lt;&gt;"",($A41-Q41)/$B$4*1000,""))</f>
         <v/>
@@ -3404,8 +3404,8 @@
       <c r="A42" s="6" t="n">
         <v>14.5</v>
       </c>
-      <c r="B42" s="7" t="n"/>
-      <c r="C42" s="7" t="n"/>
+      <c r="B42" s="7" t="inlineStr"/>
+      <c r="C42" s="7" t="inlineStr"/>
       <c r="D42" s="8">
         <f>IF(C42&lt;&gt;"",C42/$B$4*1000,IF(B42&lt;&gt;"",($A42-B42)/$B$4*1000,""))</f>
         <v/>
@@ -3416,8 +3416,8 @@
       <c r="F42" s="9" t="n">
         <v>0.0013</v>
       </c>
-      <c r="G42" s="7" t="n"/>
-      <c r="H42" s="7" t="n"/>
+      <c r="G42" s="7" t="inlineStr"/>
+      <c r="H42" s="7" t="inlineStr"/>
       <c r="I42" s="8">
         <f>IF(H42&lt;&gt;"",H42/$B$4*1000,IF(G42&lt;&gt;"",($A42-G42)/$B$4*1000,""))</f>
         <v/>
@@ -3428,8 +3428,8 @@
       <c r="K42" s="9" t="n">
         <v>0.4748</v>
       </c>
-      <c r="L42" s="7" t="n"/>
-      <c r="M42" s="7" t="n"/>
+      <c r="L42" s="7" t="inlineStr"/>
+      <c r="M42" s="7" t="inlineStr"/>
       <c r="N42" s="8">
         <f>IF(M42&lt;&gt;"",M42/$B$4*1000,IF(L42&lt;&gt;"",($A42-L42)/$B$4*1000,""))</f>
         <v/>
@@ -3440,8 +3440,8 @@
       <c r="P42" s="9" t="n">
         <v>2.138</v>
       </c>
-      <c r="Q42" s="7" t="n"/>
-      <c r="R42" s="7" t="n"/>
+      <c r="Q42" s="7" t="inlineStr"/>
+      <c r="R42" s="7" t="inlineStr"/>
       <c r="S42" s="8">
         <f>IF(R42&lt;&gt;"",R42/$B$4*1000,IF(Q42&lt;&gt;"",($A42-Q42)/$B$4*1000,""))</f>
         <v/>
@@ -3457,8 +3457,8 @@
       <c r="A43" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="B43" s="7" t="n"/>
-      <c r="C43" s="7" t="n"/>
+      <c r="B43" s="7" t="inlineStr"/>
+      <c r="C43" s="7" t="inlineStr"/>
       <c r="D43" s="8">
         <f>IF(C43&lt;&gt;"",C43/$B$4*1000,IF(B43&lt;&gt;"",($A43-B43)/$B$4*1000,""))</f>
         <v/>
@@ -3469,8 +3469,8 @@
       <c r="F43" s="9" t="n">
         <v>0.0013</v>
       </c>
-      <c r="G43" s="7" t="n"/>
-      <c r="H43" s="7" t="n"/>
+      <c r="G43" s="7" t="inlineStr"/>
+      <c r="H43" s="7" t="inlineStr"/>
       <c r="I43" s="8">
         <f>IF(H43&lt;&gt;"",H43/$B$4*1000,IF(G43&lt;&gt;"",($A43-G43)/$B$4*1000,""))</f>
         <v/>
@@ -3481,8 +3481,8 @@
       <c r="K43" s="9" t="n">
         <v>0.4768</v>
       </c>
-      <c r="L43" s="7" t="n"/>
-      <c r="M43" s="7" t="n"/>
+      <c r="L43" s="7" t="inlineStr"/>
+      <c r="M43" s="7" t="inlineStr"/>
       <c r="N43" s="8">
         <f>IF(M43&lt;&gt;"",M43/$B$4*1000,IF(L43&lt;&gt;"",($A43-L43)/$B$4*1000,""))</f>
         <v/>
@@ -3493,8 +3493,8 @@
       <c r="P43" s="9" t="n">
         <v>2.1473</v>
       </c>
-      <c r="Q43" s="7" t="n"/>
-      <c r="R43" s="7" t="n"/>
+      <c r="Q43" s="7" t="inlineStr"/>
+      <c r="R43" s="7" t="inlineStr"/>
       <c r="S43" s="8">
         <f>IF(R43&lt;&gt;"",R43/$B$4*1000,IF(Q43&lt;&gt;"",($A43-Q43)/$B$4*1000,""))</f>
         <v/>
@@ -3550,7 +3550,7 @@
           <t>麵包板全景照 1 張</t>
         </is>
       </c>
-      <c r="B50" s="18" t="n"/>
+      <c r="B50" s="18" t="inlineStr"/>
       <c r="C50" s="19" t="inlineStr">
         <is>
           <t>看得出 R1／R2／RC 各插在第幾欄、電晶體三腳的 E／B／C 方向</t>
@@ -3563,7 +3563,7 @@
           <t>電表接線特寫 1 張</t>
         </is>
       </c>
-      <c r="B51" s="18" t="n"/>
+      <c r="B51" s="18" t="inlineStr"/>
       <c r="C51" s="19" t="inlineStr">
         <is>
           <t>左表跨 B-E、中表跨 C-E、右表設 DC 電壓檔並跨 RC 兩端量 V_RC</t>
@@ -3576,7 +3576,7 @@
           <t>兩台電源面板各 1 張</t>
         </is>
       </c>
-      <c r="B52" s="18" t="n"/>
+      <c r="B52" s="18" t="inlineStr"/>
       <c r="C52" s="19" t="inlineStr">
         <is>
           <t>V_BB 與 V_CC 的設定值要和記錄表對得上</t>
@@ -3589,7 +3589,7 @@
           <t>四組 V_BB 的 V_BE 都記到</t>
         </is>
       </c>
-      <c r="B53" s="18" t="n"/>
+      <c r="B53" s="18" t="inlineStr"/>
       <c r="C53" s="19" t="inlineStr">
         <is>
           <t>導通後 V_BE 幾乎不動，沒記到就無法回答「ON/OFF 怎麼判定」</t>
@@ -3602,7 +3602,7 @@
           <t>特性曲線當場畫一次</t>
         </is>
       </c>
-      <c r="B54" s="18" t="n"/>
+      <c r="B54" s="18" t="inlineStr"/>
       <c r="C54" s="19" t="inlineStr">
         <is>
           <t>四條線要看得出平坦的主動區；不平坦代表還沒離開飽和區</t>
@@ -4094,7 +4094,7 @@
           <t>R1 兩端壓降 V_R1</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n"/>
+      <c r="B7" s="7" t="inlineStr"/>
       <c r="C7" s="17" t="inlineStr">
         <is>
           <t>V</t>
@@ -4120,7 +4120,7 @@
           <t>R2 兩端壓降 V_R2</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n"/>
+      <c r="B8" s="7" t="inlineStr"/>
       <c r="C8" s="17" t="inlineStr">
         <is>
           <t>V</t>
@@ -4146,7 +4146,7 @@
           <t>R_C 兩端壓降 V_RC</t>
         </is>
       </c>
-      <c r="B9" s="7" t="n"/>
+      <c r="B9" s="7" t="inlineStr"/>
       <c r="C9" s="17" t="inlineStr">
         <is>
           <t>V</t>
@@ -4172,7 +4172,7 @@
           <t>V_CE</t>
         </is>
       </c>
-      <c r="B10" s="7" t="n"/>
+      <c r="B10" s="7" t="inlineStr"/>
       <c r="C10" s="17" t="inlineStr">
         <is>
           <t>V</t>
@@ -4363,7 +4363,7 @@
           <t>β_measure（三用電表 hFE 檔）</t>
         </is>
       </c>
-      <c r="B16" s="7" t="n"/>
+      <c r="B16" s="7" t="inlineStr"/>
       <c r="C16" s="17" t="inlineStr">
         <is>
           <t>—</t>
@@ -4418,7 +4418,7 @@
           <t>四個壓降都量到</t>
         </is>
       </c>
-      <c r="B22" s="18" t="n"/>
+      <c r="B22" s="18" t="inlineStr"/>
       <c r="C22" s="19" t="inlineStr">
         <is>
           <t>V_R1、V_R2、V_RC、V_CE（V_CE 要直接量，不要相減）</t>
@@ -4431,7 +4431,7 @@
           <t>五個設定值都記下</t>
         </is>
       </c>
-      <c r="B23" s="18" t="n"/>
+      <c r="B23" s="18" t="inlineStr"/>
       <c r="C23" s="19" t="inlineStr">
         <is>
           <t>V_BB、V_CC 與 R1／R2／R_C 的實測值，助教要求</t>
@@ -4444,7 +4444,7 @@
           <t>Table 2 三欄填完</t>
         </is>
       </c>
-      <c r="B24" s="18" t="n"/>
+      <c r="B24" s="18" t="inlineStr"/>
       <c r="C24" s="19" t="inlineStr">
         <is>
           <t>講義 Table 2 只要 I_B、I_C、β_calculate（β_Meas 已被助教劃掉）</t>
@@ -4457,7 +4457,7 @@
           <t>電晶體 hFE 讀值照片 1 張</t>
         </is>
       </c>
-      <c r="B25" s="18" t="n"/>
+      <c r="B25" s="18" t="inlineStr"/>
       <c r="C25" s="19" t="inlineStr">
         <is>
           <t>拔下來插 hFE 座量到的 β，寫自己的記錄表、不抄進 Table 2</t>
@@ -4470,7 +4470,7 @@
           <t>飽和的證據 1 張</t>
         </is>
       </c>
-      <c r="B26" s="18" t="n"/>
+      <c r="B26" s="18" t="inlineStr"/>
       <c r="C26" s="19" t="inlineStr">
         <is>
           <t>V_CE 只剩幾十 mV 的電表畫面</t>
@@ -4606,7 +4606,7 @@
           <t>V_B（基極對地）</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n"/>
+      <c r="B6" s="7" t="inlineStr"/>
       <c r="C6" s="9" t="n">
         <v>5.876</v>
       </c>
@@ -4614,7 +4614,7 @@
         <f>IF(OR(B6="",C6=0),"",(B6-C6)/C6)</f>
         <v/>
       </c>
-      <c r="E6" s="7" t="n"/>
+      <c r="E6" s="7" t="inlineStr"/>
       <c r="F6" s="9" t="n">
         <v>5.87</v>
       </c>
@@ -4634,7 +4634,7 @@
           <t>V_E（射極對地）</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n"/>
+      <c r="B7" s="7" t="inlineStr"/>
       <c r="C7" s="9" t="n">
         <v>5.178</v>
       </c>
@@ -4642,7 +4642,7 @@
         <f>IF(OR(B7="",C7=0),"",(B7-C7)/C7)</f>
         <v/>
       </c>
-      <c r="E7" s="7" t="n"/>
+      <c r="E7" s="7" t="inlineStr"/>
       <c r="F7" s="9" t="n">
         <v>5.171</v>
       </c>
@@ -4662,7 +4662,7 @@
           <t>V_C（集極對地）</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n"/>
+      <c r="B8" s="7" t="inlineStr"/>
       <c r="C8" s="9" t="n">
         <v>11.485</v>
       </c>
@@ -4670,7 +4670,7 @@
         <f>IF(OR(B8="",C8=0),"",(B8-C8)/C8)</f>
         <v/>
       </c>
-      <c r="E8" s="7" t="n"/>
+      <c r="E8" s="7" t="inlineStr"/>
       <c r="F8" s="9" t="n">
         <v>6.854</v>
       </c>
@@ -4802,8 +4802,8 @@
           <t>RC1 100 Ω、有 C3</t>
         </is>
       </c>
-      <c r="B14" s="24" t="n"/>
-      <c r="C14" s="24" t="n"/>
+      <c r="B14" s="24" t="inlineStr"/>
+      <c r="C14" s="24" t="inlineStr"/>
       <c r="D14" s="25">
         <f>IF(OR(B14="",B14=0,C14=""),"",C14/B14)</f>
         <v/>
@@ -4815,7 +4815,7 @@
         <f>IF(OR(D14="",E14=0),"",(D14-E14)/E14)</f>
         <v/>
       </c>
-      <c r="G14" s="18" t="n"/>
+      <c r="G14" s="18" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="17" t="inlineStr">
@@ -4823,8 +4823,8 @@
           <t>RC1 1 kΩ、有 C3</t>
         </is>
       </c>
-      <c r="B15" s="24" t="n"/>
-      <c r="C15" s="24" t="n"/>
+      <c r="B15" s="24" t="inlineStr"/>
+      <c r="C15" s="24" t="inlineStr"/>
       <c r="D15" s="25">
         <f>IF(OR(B15="",B15=0,C15=""),"",C15/B15)</f>
         <v/>
@@ -4836,7 +4836,7 @@
         <f>IF(OR(D15="",E15=0),"",(D15-E15)/E15)</f>
         <v/>
       </c>
-      <c r="G15" s="18" t="n"/>
+      <c r="G15" s="18" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
@@ -4844,8 +4844,8 @@
           <t>RC1 100 Ω、無 C3</t>
         </is>
       </c>
-      <c r="B16" s="24" t="n"/>
-      <c r="C16" s="24" t="n"/>
+      <c r="B16" s="24" t="inlineStr"/>
+      <c r="C16" s="24" t="inlineStr"/>
       <c r="D16" s="25">
         <f>IF(OR(B16="",B16=0,C16=""),"",C16/B16)</f>
         <v/>
@@ -4857,7 +4857,7 @@
         <f>IF(OR(D16="",E16=0),"",(D16-E16)/E16)</f>
         <v/>
       </c>
-      <c r="G16" s="18" t="n"/>
+      <c r="G16" s="18" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="17" t="inlineStr">
@@ -4865,8 +4865,8 @@
           <t>RC1 1 kΩ、無 C3</t>
         </is>
       </c>
-      <c r="B17" s="24" t="n"/>
-      <c r="C17" s="24" t="n"/>
+      <c r="B17" s="24" t="inlineStr"/>
+      <c r="C17" s="24" t="inlineStr"/>
       <c r="D17" s="25">
         <f>IF(OR(B17="",B17=0,C17=""),"",C17/B17)</f>
         <v/>
@@ -4878,7 +4878,7 @@
         <f>IF(OR(D17="",E17=0),"",(D17-E17)/E17)</f>
         <v/>
       </c>
-      <c r="G17" s="18" t="n"/>
+      <c r="G17" s="18" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4939,7 +4939,7 @@
           <t>增益正比於集極端總電阻；620 Ω 剛好把 |A_v| 拉到 20</t>
         </is>
       </c>
-      <c r="D22" s="18" t="n"/>
+      <c r="D22" s="18" t="inlineStr"/>
       <c r="E22" s="12" t="n"/>
     </row>
     <row r="23">
@@ -4958,7 +4958,7 @@
           <t>留一小段不被旁路，增益改由電阻比決定，對 β 與溫度不敏感</t>
         </is>
       </c>
-      <c r="D23" s="18" t="n"/>
+      <c r="D23" s="18" t="inlineStr"/>
       <c r="E23" s="12" t="n"/>
     </row>
     <row r="24">
@@ -4977,7 +4977,7 @@
           <t>直流偏壓照舊由它決定，工作點不動</t>
         </is>
       </c>
-      <c r="D24" s="18" t="n"/>
+      <c r="D24" s="18" t="inlineStr"/>
       <c r="E24" s="12" t="n"/>
     </row>
     <row r="25">
@@ -4996,7 +4996,7 @@
           <t>10 kHz 時容抗 0.16 Ω，遠小於 R_E1a，才算真的旁路掉</t>
         </is>
       </c>
-      <c r="D25" s="18" t="n"/>
+      <c r="D25" s="18" t="inlineStr"/>
       <c r="E25" s="12" t="n"/>
     </row>
     <row r="26">
@@ -5015,7 +5015,7 @@
           <t>耦合電容維持講義原值即可，截止頻率遠低於 10 kHz</t>
         </is>
       </c>
-      <c r="D26" s="18" t="n"/>
+      <c r="D26" s="18" t="inlineStr"/>
       <c r="E26" s="12" t="n"/>
     </row>
     <row r="27">
@@ -5034,7 +5034,7 @@
           <t>工作點</t>
         </is>
       </c>
-      <c r="D27" s="18" t="n"/>
+      <c r="D27" s="18" t="inlineStr"/>
       <c r="E27" s="12" t="inlineStr">
         <is>
           <t>5.88 / 5.18 / 8.87 V</t>
@@ -5057,7 +5057,7 @@
           <t>目標 20，±10% 以內都算達標</t>
         </is>
       </c>
-      <c r="D28" s="18" t="n"/>
+      <c r="D28" s="18" t="inlineStr"/>
       <c r="E28" s="12" t="n">
         <v>20.13</v>
       </c>
@@ -5099,7 +5099,7 @@
           <t>示波器雙軌畫面 4 張</t>
         </is>
       </c>
-      <c r="B33" s="18" t="n"/>
+      <c r="B33" s="18" t="inlineStr"/>
       <c r="C33" s="19" t="inlineStr">
         <is>
           <t>四種組合各一張，CH1／CH2 同時入鏡才看得出反相</t>
@@ -5112,7 +5112,7 @@
           <t>削波的那張要放大</t>
         </is>
       </c>
-      <c r="B34" s="18" t="n"/>
+      <c r="B34" s="18" t="inlineStr"/>
       <c r="C34" s="19" t="inlineStr">
         <is>
           <t>R_C1 = 1 kΩ 的輸出，削平的一邊要看得清楚</t>
@@ -5125,7 +5125,7 @@
           <t>直流工作點電表照片 1 張</t>
         </is>
       </c>
-      <c r="B35" s="18" t="n"/>
+      <c r="B35" s="18" t="inlineStr"/>
       <c r="C35" s="19" t="inlineStr">
         <is>
           <t>V_B、V_E、V_C 三個讀值</t>
@@ -5138,7 +5138,7 @@
           <t>Bonus 電路的接線照與波形各 1 張</t>
         </is>
       </c>
-      <c r="B36" s="18" t="n"/>
+      <c r="B36" s="18" t="inlineStr"/>
       <c r="C36" s="19" t="inlineStr">
         <is>
           <t>元件值改了要拍，結報要對照</t>
